--- a/database/event/2306/event_2306_evp_summary.xlsx
+++ b/database/event/2306/event_2306_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.297000000000001</v>
+        <v>9.1379</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5557</v>
+        <v>3.9161</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9304</v>
+        <v>3.1966</v>
       </c>
       <c r="E2" t="n">
-        <v>8.297000000000001</v>
+        <v>9.1379</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7762</v>
+        <v>2.6171</v>
       </c>
       <c r="G2" t="n">
         <v>6.5208</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7762</v>
+        <v>2.6171</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7928</v>
+        <v>2.6613</v>
       </c>
       <c r="J2" t="n">
         <v>6.8565</v>
@@ -529,7 +529,7 @@
         <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>8.6493</v>
+        <v>9.517799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5814</v>
+        <v>6.0638</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3919</v>
+        <v>2.5987</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8334</v>
+        <v>1.9719</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5814</v>
+        <v>6.0638</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9286</v>
+        <v>2.2454</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6528</v>
+        <v>3.8184</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9286</v>
+        <v>2.2454</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9466</v>
+        <v>2.2834</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6528</v>
+        <v>3.8184</v>
       </c>
       <c r="K3" t="n">
         <v>131</v>
@@ -575,7 +575,7 @@
         <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5994</v>
+        <v>6.1018</v>
       </c>
       <c r="N3" t="n">
         <v>307</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5176</v>
+        <v>6.0209</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3646</v>
+        <v>2.5803</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8076</v>
+        <v>1.9548</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5176</v>
+        <v>6.0209</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6992</v>
+        <v>2.3681</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8184</v>
+        <v>3.6528</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6992</v>
+        <v>2.3681</v>
       </c>
       <c r="I4" t="n">
-        <v>1.715</v>
+        <v>2.4081</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8184</v>
+        <v>3.6528</v>
       </c>
       <c r="K4" t="n">
         <v>131</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5334</v>
+        <v>6.0609</v>
       </c>
       <c r="N4" t="n">
         <v>307</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8313</v>
+        <v>5.6266</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0705</v>
+        <v>2.4113</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5304</v>
+        <v>1.7977</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8313</v>
+        <v>5.6266</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4748</v>
+        <v>3.2701</v>
       </c>
       <c r="G5" t="n">
         <v>2.3565</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4748</v>
+        <v>3.2701</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4863</v>
+        <v>3.2976</v>
       </c>
       <c r="J5" t="n">
         <v>2.3565</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8428</v>
+        <v>5.6541</v>
       </c>
       <c r="N5" t="n">
         <v>270</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1589</v>
+        <v>4.9495</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7823</v>
+        <v>2.1211</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2587</v>
+        <v>1.528</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1589</v>
+        <v>4.9495</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3649</v>
+        <v>4.1555</v>
       </c>
       <c r="G6" t="n">
         <v>0.794</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3649</v>
+        <v>4.158</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7274</v>
+        <v>3.3702</v>
       </c>
       <c r="J6" t="n">
         <v>0.794</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5214</v>
+        <v>4.1642</v>
       </c>
       <c r="N6" t="n">
         <v>269</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0003</v>
+        <v>4.3413</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7144</v>
+        <v>1.8605</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1947</v>
+        <v>1.2857</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0003</v>
+        <v>4.3413</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3543</v>
+        <v>2.6953</v>
       </c>
       <c r="G7" t="n">
         <v>1.646</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3543</v>
+        <v>2.6953</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9082</v>
+        <v>2.1846</v>
       </c>
       <c r="J7" t="n">
         <v>1.646</v>
@@ -759,7 +759,7 @@
         <v>154</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5542</v>
+        <v>3.8306</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -768,127 +768,127 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6276</v>
+        <v>4.0483</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5546</v>
+        <v>1.7349</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0441</v>
+        <v>1.1689</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6276</v>
+        <v>4.0483</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1808</v>
+        <v>3.4497</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5532</v>
+        <v>0.5986</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2599</v>
+        <v>3.4497</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4527</v>
+        <v>3.4787</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5532</v>
+        <v>0.5986</v>
       </c>
       <c r="K8" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8995</v>
+        <v>4.0773</v>
       </c>
       <c r="N8" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1619</v>
+        <v>3.9235</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3551</v>
+        <v>1.6814</v>
       </c>
       <c r="D9" t="n">
-        <v>0.856</v>
+        <v>1.1192</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1619</v>
+        <v>3.9235</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3062</v>
+        <v>4.4767</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8557</v>
+        <v>-0.5532</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3062</v>
+        <v>5.4502</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3277</v>
+        <v>4.4176</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8557</v>
+        <v>-0.5532</v>
       </c>
       <c r="K9" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="L9" t="n">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1834</v>
+        <v>3.8644</v>
       </c>
       <c r="N9" t="n">
-        <v>307</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1271</v>
+        <v>3.7589</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3401</v>
+        <v>1.6109</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8419</v>
+        <v>1.0536</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1271</v>
+        <v>3.7589</v>
       </c>
       <c r="F10" t="n">
-        <v>4.266</v>
+        <v>2.8723</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1389</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6027</v>
+        <v>2.8723</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7307</v>
+        <v>2.3281</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1389</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>115</v>
@@ -897,7 +897,7 @@
         <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5918</v>
+        <v>3.2147</v>
       </c>
       <c r="N10" t="n">
         <v>269</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0786</v>
+        <v>3.5028</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3194</v>
+        <v>1.5011</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8223</v>
+        <v>0.9516</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0786</v>
+        <v>3.5028</v>
       </c>
       <c r="F11" t="n">
-        <v>2.192</v>
+        <v>4.6417</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8866000000000001</v>
+        <v>-1.1389</v>
       </c>
       <c r="H11" t="n">
-        <v>2.192</v>
+        <v>6.1143</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7767</v>
+        <v>4.9558</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8866000000000001</v>
+        <v>-1.1389</v>
       </c>
       <c r="K11" t="n">
         <v>115</v>
@@ -943,7 +943,7 @@
         <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6633</v>
+        <v>3.8169</v>
       </c>
       <c r="N11" t="n">
         <v>269</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9121</v>
+        <v>3.4841</v>
       </c>
       <c r="C12" t="n">
-        <v>1.248</v>
+        <v>1.4931</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7551</v>
+        <v>0.9442</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9121</v>
+        <v>3.4841</v>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>3.4841</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1221</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.79</v>
+        <v>3.4841</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4508</v>
+        <v>3.4841</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1221</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="L12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5729</v>
+        <v>3.4841</v>
       </c>
       <c r="N12" t="n">
-        <v>269</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8626</v>
+        <v>3.2425</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2268</v>
+        <v>1.3896</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7351</v>
+        <v>0.8479</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8626</v>
+        <v>3.2425</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3539</v>
+        <v>2.3868</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5087</v>
+        <v>0.8557</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3539</v>
+        <v>2.3868</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3572</v>
+        <v>2.4271</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5087</v>
+        <v>0.8557</v>
       </c>
       <c r="K13" t="n">
         <v>131</v>
@@ -1035,7 +1035,7 @@
         <v>176</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8659</v>
+        <v>3.2828</v>
       </c>
       <c r="N13" t="n">
         <v>307</v>
@@ -1044,369 +1044,369 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8424</v>
+        <v>2.9798</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2181</v>
+        <v>1.277</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7269</v>
+        <v>0.7432</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8424</v>
+        <v>2.9798</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2438</v>
+        <v>0.4711</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5986</v>
+        <v>2.5087</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2438</v>
+        <v>0.4711</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2543</v>
+        <v>0.4791</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5986</v>
+        <v>2.5087</v>
       </c>
       <c r="K14" t="n">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8529</v>
+        <v>2.9878</v>
       </c>
       <c r="N14" t="n">
-        <v>148</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2208</v>
+        <v>2.9583</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9517</v>
+        <v>1.2678</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4758</v>
+        <v>0.7347</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2208</v>
+        <v>2.9583</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9491</v>
+        <v>1.8362</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2717</v>
+        <v>1.1221</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9491</v>
+        <v>1.8362</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5798</v>
+        <v>1.4883</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2717</v>
+        <v>1.1221</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8515</v>
+        <v>2.6104</v>
       </c>
       <c r="N15" t="n">
-        <v>160</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1836</v>
+        <v>2.941</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9358</v>
+        <v>1.2604</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4608</v>
+        <v>0.7278</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1836</v>
+        <v>2.941</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9945</v>
+        <v>3.5048</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1891</v>
+        <v>-0.5638</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9945</v>
+        <v>3.5048</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6166</v>
+        <v>3.5343</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1891</v>
+        <v>-0.5638</v>
       </c>
       <c r="K16" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8057</v>
+        <v>2.9705</v>
       </c>
       <c r="N16" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9917</v>
+        <v>2.4415</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8536</v>
+        <v>1.0463</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3832</v>
+        <v>0.5288</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9917</v>
+        <v>2.4415</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9917</v>
+        <v>2.1698</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2717</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9917</v>
+        <v>2.1698</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9917</v>
+        <v>1.7587</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2717</v>
       </c>
       <c r="K17" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9917</v>
+        <v>2.0304</v>
       </c>
       <c r="N17" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5999</v>
+        <v>2.3185</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6856</v>
+        <v>0.9936</v>
       </c>
       <c r="D18" t="n">
-        <v>0.225</v>
+        <v>0.4798</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5999</v>
+        <v>2.3185</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1637</v>
+        <v>2.7087</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5638</v>
+        <v>-0.3902</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1637</v>
+        <v>2.7087</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1738</v>
+        <v>2.7087</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5638</v>
+        <v>-0.3902</v>
       </c>
       <c r="K18" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M18" t="n">
-        <v>1.61</v>
+        <v>2.3185</v>
       </c>
       <c r="N18" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3998</v>
+        <v>2.3181</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5999</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1441</v>
+        <v>0.4796</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3998</v>
+        <v>2.3181</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3998</v>
+        <v>2.129</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3998</v>
+        <v>2.129</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3998</v>
+        <v>1.7256</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="K19" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3998</v>
+        <v>1.9147</v>
       </c>
       <c r="N19" t="n">
-        <v>101</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.394</v>
+        <v>1.6406</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5974</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1418</v>
+        <v>0.2097</v>
       </c>
       <c r="E20" t="n">
-        <v>1.394</v>
+        <v>1.6406</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7842</v>
+        <v>1.4892</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3902</v>
+        <v>0.1514</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7842</v>
+        <v>1.4892</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7842</v>
+        <v>1.207</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3902</v>
+        <v>0.1514</v>
       </c>
       <c r="K20" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.394</v>
+        <v>1.3584</v>
       </c>
       <c r="N20" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2948</v>
+        <v>1.6339</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.7002</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1017</v>
+        <v>0.207</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2948</v>
+        <v>1.6339</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1434</v>
+        <v>1.6339</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1514</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1434</v>
+        <v>1.6339</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9267</v>
+        <v>1.6339</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1514</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0781</v>
+        <v>1.6339</v>
       </c>
       <c r="N21" t="n">
-        <v>160</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.262</v>
+        <v>1.6324</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.6996</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0885</v>
+        <v>0.2064</v>
       </c>
       <c r="E22" t="n">
-        <v>1.262</v>
+        <v>1.6324</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9153</v>
+        <v>2.2857</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6533</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9153</v>
+        <v>2.2857</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9242</v>
+        <v>2.3049</v>
       </c>
       <c r="J22" t="n">
         <v>-0.6533</v>
@@ -1449,7 +1449,7 @@
         <v>61</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2709</v>
+        <v>1.6516</v>
       </c>
       <c r="N22" t="n">
         <v>148</v>
@@ -1458,81 +1458,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1112</v>
+        <v>1.5586</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4762</v>
+        <v>0.6679</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0275</v>
+        <v>0.177</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1112</v>
+        <v>1.5586</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2705</v>
+        <v>1.3768</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1593</v>
+        <v>0.1818</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2705</v>
+        <v>1.3768</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2764</v>
+        <v>1.3884</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1593</v>
+        <v>0.1818</v>
       </c>
       <c r="K23" t="n">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="L23" t="n">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1171</v>
+        <v>1.5702</v>
       </c>
       <c r="N23" t="n">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9746</v>
+        <v>1.5222</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4177</v>
+        <v>0.6523</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0276</v>
+        <v>0.1625</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9746</v>
+        <v>1.5222</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9768</v>
+        <v>1.8265</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0022</v>
+        <v>-0.3043</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9768</v>
+        <v>1.8265</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9768</v>
+        <v>1.8265</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0022</v>
+        <v>-0.3043</v>
       </c>
       <c r="K24" t="n">
         <v>85</v>
@@ -1541,7 +1541,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9746</v>
+        <v>1.5222</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9674</v>
+        <v>1.4116</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4146</v>
+        <v>0.6049</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0306</v>
+        <v>0.1185</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9674</v>
+        <v>1.4116</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9674</v>
+        <v>1.4138</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.0022</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9674</v>
+        <v>1.4138</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9674</v>
+        <v>1.4138</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.0022</v>
       </c>
       <c r="K25" t="n">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9674</v>
+        <v>1.4116</v>
       </c>
       <c r="N25" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3518</v>
+        <v>0.5697</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0897</v>
+        <v>0.0857</v>
       </c>
       <c r="E26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="F26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="I26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.821</v>
+        <v>1.3293</v>
       </c>
       <c r="N26" t="n">
         <v>101</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8001</v>
+        <v>1.2765</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3429</v>
+        <v>0.5471</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.0646</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8001</v>
+        <v>1.2765</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6829</v>
+        <v>1.4358</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1172</v>
+        <v>-0.1593</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6829</v>
+        <v>1.4358</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.4479</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1172</v>
+        <v>-0.1593</v>
       </c>
       <c r="K27" t="n">
         <v>134</v>
@@ -1679,7 +1679,7 @@
         <v>136</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8032</v>
+        <v>1.2886</v>
       </c>
       <c r="N27" t="n">
         <v>270</v>
@@ -1688,127 +1688,127 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7831</v>
+        <v>1.0991</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3356</v>
+        <v>0.471</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.105</v>
+        <v>-0.006</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7831</v>
+        <v>1.0991</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6012999999999999</v>
+        <v>1.0991</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1818</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6012999999999999</v>
+        <v>1.0991</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6041</v>
+        <v>1.0991</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1818</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7858999999999999</v>
+        <v>1.0991</v>
       </c>
       <c r="N28" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.0909</v>
       </c>
       <c r="C29" t="n">
-        <v>0.313</v>
+        <v>0.4675</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1263</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.0909</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1799</v>
+        <v>1.2704</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5504</v>
+        <v>-0.1795</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1799</v>
+        <v>1.2704</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1808</v>
+        <v>1.2811</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5504</v>
+        <v>-0.1795</v>
       </c>
       <c r="K29" t="n">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="L29" t="n">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7312</v>
+        <v>1.1016</v>
       </c>
       <c r="N29" t="n">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6185</v>
+        <v>0.9989</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2651</v>
+        <v>0.4281</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1715</v>
+        <v>-0.0459</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6185</v>
+        <v>0.9989</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9228</v>
+        <v>1.0216</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3043</v>
+        <v>-0.0227</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9228</v>
+        <v>1.0216</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9228</v>
+        <v>1.0216</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3043</v>
+        <v>-0.0227</v>
       </c>
       <c r="K30" t="n">
         <v>85</v>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6184999999999999</v>
+        <v>0.9989</v>
       </c>
       <c r="N30" t="n">
         <v>131</v>
@@ -1826,507 +1826,507 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4851</v>
+        <v>0.9297</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2079</v>
+        <v>0.3984</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2254</v>
+        <v>-0.0735</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4851</v>
+        <v>0.9297</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6646</v>
+        <v>0.8125</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1795</v>
+        <v>0.1172</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6646</v>
+        <v>0.8125</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6677</v>
+        <v>0.8193</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1795</v>
+        <v>0.1172</v>
       </c>
       <c r="K31" t="n">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="L31" t="n">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4882</v>
+        <v>0.9365</v>
       </c>
       <c r="N31" t="n">
-        <v>148</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4368</v>
+        <v>0.8704</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1872</v>
+        <v>0.373</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2449</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4368</v>
+        <v>0.8704</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4595</v>
+        <v>0.32</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0227</v>
+        <v>0.5504</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4595</v>
+        <v>0.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4595</v>
+        <v>0.3227</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0227</v>
+        <v>0.5504</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="L32" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4368</v>
+        <v>0.8731</v>
       </c>
       <c r="N32" t="n">
-        <v>131</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1344</v>
+        <v>0.2574</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2947</v>
+        <v>-0.2046</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3136</v>
+        <v>0.6007</v>
       </c>
       <c r="N33" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2951</v>
+        <v>0.5726</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1265</v>
+        <v>0.2454</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3021</v>
+        <v>-0.2158</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2951</v>
+        <v>0.5726</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2951</v>
+        <v>1.5726</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2951</v>
+        <v>1.5726</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2951</v>
+        <v>1.5726</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2951</v>
+        <v>0.5726</v>
       </c>
       <c r="N34" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.2386</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3324</v>
+        <v>-0.2221</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="L35" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2201</v>
+        <v>0.5568</v>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0517</v>
+        <v>0.5001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0222</v>
+        <v>0.2143</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4005</v>
+        <v>-0.2447</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0517</v>
+        <v>0.5001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.092</v>
+        <v>0.5001</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.092</v>
+        <v>0.5001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0924</v>
+        <v>0.5001</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L36" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.05209999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="N36" t="n">
-        <v>270</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0335</v>
+        <v>0.4065</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0144</v>
+        <v>0.1742</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4078</v>
+        <v>-0.282</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0335</v>
+        <v>0.4065</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0335</v>
+        <v>0.4468</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.0403</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0335</v>
+        <v>0.4468</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0335</v>
+        <v>0.4506</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.0403</v>
       </c>
       <c r="K37" t="n">
+        <v>134</v>
+      </c>
+      <c r="L37" t="n">
         <v>136</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
-        <v>0.0335</v>
+        <v>0.4103</v>
       </c>
       <c r="N37" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1296</v>
+        <v>0.1583</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.5435</v>
+        <v>-0.2968</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.3023</v>
+        <v>0.3693</v>
       </c>
       <c r="N38" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1368</v>
+        <v>-0.1296</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5503</v>
+        <v>-0.5643</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.3192</v>
+        <v>-0.3023</v>
       </c>
       <c r="N39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1741</v>
+        <v>-0.1368</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5855</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3192</v>
       </c>
       <c r="N40" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1766</v>
+        <v>-0.174</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5878</v>
+        <v>-0.6057</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.412</v>
+        <v>-0.4061</v>
       </c>
       <c r="N41" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2269</v>
+        <v>-0.2083</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6352</v>
+        <v>-0.6375</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.5294</v>
+        <v>-0.486</v>
       </c>
       <c r="N42" t="n">
         <v>142</v>
@@ -2378,231 +2378,231 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3242</v>
+        <v>-0.2956</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.727</v>
+        <v>-0.7187</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.7565</v>
+        <v>-0.6898</v>
       </c>
       <c r="N43" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3553</v>
+        <v>-0.3242</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7563</v>
+        <v>-0.7453</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7565</v>
       </c>
       <c r="N44" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.3613</v>
+        <v>-0.3553</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.762</v>
+        <v>-0.7742</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.8431</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3753</v>
+        <v>-0.3613</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.7752</v>
+        <v>-0.7798</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.8758</v>
+        <v>-0.8431</v>
       </c>
       <c r="N46" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.5185</v>
+        <v>-0.3753</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9101</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-1.2099</v>
+        <v>-0.8758</v>
       </c>
       <c r="N47" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48">
@@ -2618,7 +2618,7 @@
         <v>-0.5223</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9137</v>
+        <v>-0.9294</v>
       </c>
       <c r="E48" t="n">
         <v>-1.2187</v>
@@ -2664,7 +2664,7 @@
         <v>-0.5321</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.923</v>
+        <v>-0.9386</v>
       </c>
       <c r="E49" t="n">
         <v>-1.2417</v>
@@ -2710,7 +2710,7 @@
         <v>-0.5382</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9287</v>
+        <v>-0.9443</v>
       </c>
       <c r="E50" t="n">
         <v>-1.2559</v>
@@ -2756,7 +2756,7 @@
         <v>-0.6103</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.9967</v>
+        <v>-1.0113</v>
       </c>
       <c r="E51" t="n">
         <v>-1.4241</v>
@@ -2802,7 +2802,7 @@
         <v>-0.6298</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0151</v>
+        <v>-1.0294</v>
       </c>
       <c r="E52" t="n">
         <v>-1.4697</v>
@@ -2848,7 +2848,7 @@
         <v>-0.694</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0756</v>
+        <v>-1.0891</v>
       </c>
       <c r="E53" t="n">
         <v>-1.6194</v>
@@ -2894,7 +2894,7 @@
         <v>-0.8958</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.2658</v>
+        <v>-1.2767</v>
       </c>
       <c r="E54" t="n">
         <v>-2.0903</v>
@@ -2940,7 +2940,7 @@
         <v>-0.9813</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.3464</v>
+        <v>-1.3561</v>
       </c>
       <c r="E55" t="n">
         <v>-2.2897</v>
@@ -2986,7 +2986,7 @@
         <v>-1.288</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.6355</v>
+        <v>-1.6413</v>
       </c>
       <c r="E56" t="n">
         <v>-3.0054</v>

--- a/database/event/2306/event_2306_evp_summary.xlsx
+++ b/database/event/2306/event_2306_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.1379</v>
+        <v>8.3605</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9161</v>
+        <v>3.5829</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1966</v>
+        <v>3.1363</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1379</v>
+        <v>8.3605</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6171</v>
+        <v>2.5039</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5208</v>
+        <v>5.8566</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6171</v>
+        <v>2.5039</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6613</v>
+        <v>2.7141</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8565</v>
+        <v>5.8566</v>
       </c>
       <c r="K2" t="n">
         <v>131</v>
@@ -529,7 +529,7 @@
         <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>9.517799999999999</v>
+        <v>8.5707</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0638</v>
+        <v>5.8694</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5987</v>
+        <v>2.5154</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9719</v>
+        <v>2.0117</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0638</v>
+        <v>5.8694</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2454</v>
+        <v>2.5692</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8184</v>
+        <v>3.3002</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2454</v>
+        <v>2.5692</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2834</v>
+        <v>2.7849</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8184</v>
+        <v>3.3002</v>
       </c>
       <c r="K3" t="n">
         <v>131</v>
@@ -575,7 +575,7 @@
         <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1018</v>
+        <v>6.0851</v>
       </c>
       <c r="N3" t="n">
         <v>307</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0209</v>
+        <v>5.7366</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5803</v>
+        <v>2.4585</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9548</v>
+        <v>1.9518</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0209</v>
+        <v>5.7366</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3681</v>
+        <v>2.3012</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6528</v>
+        <v>3.4354</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3681</v>
+        <v>2.3012</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4081</v>
+        <v>2.4944</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6528</v>
+        <v>3.4354</v>
       </c>
       <c r="K4" t="n">
         <v>131</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0609</v>
+        <v>5.9298</v>
       </c>
       <c r="N4" t="n">
         <v>307</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6266</v>
+        <v>4.8238</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4113</v>
+        <v>2.0673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7977</v>
+        <v>1.5397</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6266</v>
+        <v>4.8238</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2701</v>
+        <v>2.9747</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3565</v>
+        <v>1.8491</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2701</v>
+        <v>3.1722</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2976</v>
+        <v>3.3027</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3565</v>
+        <v>1.8491</v>
       </c>
       <c r="K5" t="n">
         <v>134</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6541</v>
+        <v>5.1518</v>
       </c>
       <c r="N5" t="n">
         <v>270</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9495</v>
+        <v>4.3801</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1211</v>
+        <v>1.8771</v>
       </c>
       <c r="D6" t="n">
-        <v>1.528</v>
+        <v>1.3394</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9495</v>
+        <v>4.3801</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1555</v>
+        <v>2.9163</v>
       </c>
       <c r="G6" t="n">
-        <v>0.794</v>
+        <v>1.4638</v>
       </c>
       <c r="H6" t="n">
-        <v>4.158</v>
+        <v>4.7889</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3702</v>
+        <v>2.49</v>
       </c>
       <c r="J6" t="n">
-        <v>0.794</v>
+        <v>1.4638</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1642</v>
+        <v>3.9538</v>
       </c>
       <c r="N6" t="n">
         <v>269</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3413</v>
+        <v>4.163</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8605</v>
+        <v>1.7841</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2857</v>
+        <v>1.2414</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3413</v>
+        <v>4.163</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6953</v>
+        <v>3.462</v>
       </c>
       <c r="G7" t="n">
-        <v>1.646</v>
+        <v>0.701</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6953</v>
+        <v>6.7117</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1846</v>
+        <v>3.4898</v>
       </c>
       <c r="J7" t="n">
-        <v>1.646</v>
+        <v>0.701</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>154</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8306</v>
+        <v>4.190799999999999</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0483</v>
+        <v>3.8042</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7349</v>
+        <v>1.6303</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1689</v>
+        <v>1.0794</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0483</v>
+        <v>3.8042</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4497</v>
+        <v>2.972</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5986</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4497</v>
+        <v>4.9852</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4787</v>
+        <v>2.5921</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5986</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0773</v>
+        <v>3.4243</v>
       </c>
       <c r="N8" t="n">
-        <v>148</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9235</v>
+        <v>3.62</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6814</v>
+        <v>1.5514</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1192</v>
+        <v>0.9962</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9235</v>
+        <v>3.62</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4767</v>
+        <v>3.0129</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5532</v>
+        <v>0.6071</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4502</v>
+        <v>3.256</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4176</v>
+        <v>3.3899</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5532</v>
+        <v>0.6071</v>
       </c>
       <c r="K9" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="L9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8644</v>
+        <v>3.997</v>
       </c>
       <c r="N9" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7589</v>
+        <v>3.5252</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6109</v>
+        <v>1.5107</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0536</v>
+        <v>0.9534</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7589</v>
+        <v>3.5252</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8723</v>
+        <v>2.4677</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8866000000000001</v>
+        <v>1.0575</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8723</v>
+        <v>2.4677</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3281</v>
+        <v>2.6749</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8866000000000001</v>
+        <v>1.0575</v>
       </c>
       <c r="K10" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2147</v>
+        <v>3.7324</v>
       </c>
       <c r="N10" t="n">
-        <v>269</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5028</v>
+        <v>3.4669</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5011</v>
+        <v>1.4858</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9516</v>
+        <v>0.9271</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5028</v>
+        <v>3.4669</v>
       </c>
       <c r="F11" t="n">
-        <v>4.6417</v>
+        <v>4.084</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1389</v>
+        <v>-0.6171</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1143</v>
+        <v>8.9032</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9558</v>
+        <v>4.6292</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1389</v>
+        <v>-0.6171</v>
       </c>
       <c r="K11" t="n">
         <v>115</v>
@@ -943,7 +943,7 @@
         <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8169</v>
+        <v>4.0121</v>
       </c>
       <c r="N11" t="n">
         <v>269</v>
@@ -952,265 +952,265 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4841</v>
+        <v>3.3829</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4931</v>
+        <v>1.4498</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9442</v>
+        <v>0.8892</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4841</v>
+        <v>3.3829</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4841</v>
+        <v>3.7576</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.3747</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4841</v>
+        <v>7.7533</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4841</v>
+        <v>4.0313</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.3747</v>
       </c>
       <c r="K12" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4841</v>
+        <v>3.6566</v>
       </c>
       <c r="N12" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2425</v>
+        <v>3.3455</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3896</v>
+        <v>1.4337</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8479</v>
+        <v>0.8723</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2425</v>
+        <v>3.3455</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3868</v>
+        <v>2.5512</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8557</v>
+        <v>0.7943</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3868</v>
+        <v>3.5024</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4271</v>
+        <v>1.8211</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8557</v>
+        <v>0.7943</v>
       </c>
       <c r="K13" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="L13" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2828</v>
+        <v>2.6154</v>
       </c>
       <c r="N13" t="n">
-        <v>307</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9798</v>
+        <v>3.0572</v>
       </c>
       <c r="C14" t="n">
-        <v>1.277</v>
+        <v>1.3102</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7432</v>
+        <v>0.7422</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9798</v>
+        <v>3.0572</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4711</v>
+        <v>3.0572</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5087</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4711</v>
+        <v>3.3533</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4791</v>
+        <v>3.3533</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5087</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="L14" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9878</v>
+        <v>3.3533</v>
       </c>
       <c r="N14" t="n">
-        <v>307</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9583</v>
+        <v>2.9218</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2678</v>
+        <v>1.2522</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7347</v>
+        <v>0.681</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9583</v>
+        <v>2.9218</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8362</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1221</v>
+        <v>2.1471</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8362</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4883</v>
+        <v>0.8397</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1221</v>
+        <v>2.1471</v>
       </c>
       <c r="K15" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="L15" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6104</v>
+        <v>2.9868</v>
       </c>
       <c r="N15" t="n">
-        <v>269</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.941</v>
+        <v>2.9209</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2604</v>
+        <v>1.2518</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7278</v>
+        <v>0.6806</v>
       </c>
       <c r="E16" t="n">
-        <v>2.941</v>
+        <v>2.9209</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5048</v>
+        <v>2.6452</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5638</v>
+        <v>0.2757</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5048</v>
+        <v>3.8338</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5343</v>
+        <v>1.9934</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5638</v>
+        <v>0.2757</v>
       </c>
       <c r="K16" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9705</v>
+        <v>2.2691</v>
       </c>
       <c r="N16" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4415</v>
+        <v>2.8917</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0463</v>
+        <v>1.2393</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5288</v>
+        <v>0.6674</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4415</v>
+        <v>2.8917</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1698</v>
+        <v>2.6145</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2717</v>
+        <v>0.2772</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1698</v>
+        <v>3.7257</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7587</v>
+        <v>1.9372</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2717</v>
+        <v>0.2772</v>
       </c>
       <c r="K17" t="n">
         <v>109</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0304</v>
+        <v>2.2144</v>
       </c>
       <c r="N17" t="n">
         <v>160</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3185</v>
+        <v>2.6681</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9936</v>
+        <v>1.1434</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4798</v>
+        <v>0.5665</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3185</v>
+        <v>2.6681</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7087</v>
+        <v>3.0156</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3902</v>
+        <v>-0.3475</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7087</v>
+        <v>3.2619</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7087</v>
+        <v>3.3961</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3902</v>
+        <v>-0.3475</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3185</v>
+        <v>3.0486</v>
       </c>
       <c r="N18" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3181</v>
+        <v>2.5771</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9933999999999999</v>
+        <v>1.1044</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4796</v>
+        <v>0.5254</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3181</v>
+        <v>2.5771</v>
       </c>
       <c r="F19" t="n">
-        <v>2.129</v>
+        <v>2.8429</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1891</v>
+        <v>-0.2658</v>
       </c>
       <c r="H19" t="n">
-        <v>2.129</v>
+        <v>2.8827</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7256</v>
+        <v>2.8827</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1891</v>
+        <v>-0.2658</v>
       </c>
       <c r="K19" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="L19" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9147</v>
+        <v>2.6169</v>
       </c>
       <c r="N19" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6406</v>
+        <v>2.4983</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.0707</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2097</v>
+        <v>0.4898</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6406</v>
+        <v>2.4983</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4892</v>
+        <v>2.2265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1514</v>
+        <v>0.2718</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4892</v>
+        <v>2.3585</v>
       </c>
       <c r="I20" t="n">
-        <v>1.207</v>
+        <v>1.2263</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1514</v>
+        <v>0.2718</v>
       </c>
       <c r="K20" t="n">
         <v>109</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3584</v>
+        <v>1.4981</v>
       </c>
       <c r="N20" t="n">
         <v>160</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6339</v>
+        <v>2.125</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7002</v>
+        <v>0.9107</v>
       </c>
       <c r="D21" t="n">
-        <v>0.207</v>
+        <v>0.3213</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6339</v>
+        <v>2.125</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6339</v>
+        <v>2.5329</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4079</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6339</v>
+        <v>2.5329</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6339</v>
+        <v>2.6371</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4079</v>
       </c>
       <c r="K21" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6339</v>
+        <v>2.2292</v>
       </c>
       <c r="N21" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6324</v>
+        <v>1.9015</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6996</v>
+        <v>0.8149</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2064</v>
+        <v>0.2204</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6324</v>
+        <v>1.9015</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2857</v>
+        <v>1.9015</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6533</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2857</v>
+        <v>1.9015</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3049</v>
+        <v>1.9015</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6533</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6516</v>
+        <v>1.9015</v>
       </c>
       <c r="N22" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5586</v>
+        <v>1.803</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6679</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5586</v>
+        <v>1.803</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3768</v>
+        <v>1.7644</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1818</v>
+        <v>0.0386</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3768</v>
+        <v>1.7644</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3884</v>
+        <v>1.837</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1818</v>
+        <v>0.0386</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="L23" t="n">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5702</v>
+        <v>1.8756</v>
       </c>
       <c r="N23" t="n">
-        <v>148</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5222</v>
+        <v>1.7849</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6523</v>
+        <v>0.7649</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1625</v>
+        <v>0.1678</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5222</v>
+        <v>1.7849</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8265</v>
+        <v>1.9776</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3043</v>
+        <v>-0.1927</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8265</v>
+        <v>1.9776</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8265</v>
+        <v>1.9776</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3043</v>
+        <v>-0.1927</v>
       </c>
       <c r="K24" t="n">
         <v>85</v>
@@ -1541,7 +1541,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5222</v>
+        <v>1.7849</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4116</v>
+        <v>1.7312</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6049</v>
+        <v>0.7419</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1185</v>
+        <v>0.1435</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4116</v>
+        <v>1.7312</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4138</v>
+        <v>1.5229</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0022</v>
+        <v>0.2083</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4138</v>
+        <v>1.5229</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4138</v>
+        <v>1.5855</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0022</v>
+        <v>0.2083</v>
       </c>
       <c r="K25" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L25" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4116</v>
+        <v>1.7938</v>
       </c>
       <c r="N25" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3293</v>
+        <v>1.7285</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5697</v>
+        <v>0.7408</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0857</v>
+        <v>0.1423</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3293</v>
+        <v>1.7285</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3293</v>
+        <v>1.7296</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.0011</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3293</v>
+        <v>1.7296</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3293</v>
+        <v>1.7296</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.0011</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3293</v>
+        <v>1.7285</v>
       </c>
       <c r="N26" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2765</v>
+        <v>1.6447</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5471</v>
+        <v>0.7048</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0646</v>
+        <v>0.1045</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2765</v>
+        <v>1.6447</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4358</v>
+        <v>1.6447</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1593</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4358</v>
+        <v>1.6447</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4479</v>
+        <v>1.6447</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1593</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2886</v>
+        <v>1.6447</v>
       </c>
       <c r="N27" t="n">
-        <v>270</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0991</v>
+        <v>1.5254</v>
       </c>
       <c r="C28" t="n">
-        <v>0.471</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.006</v>
+        <v>0.0506</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0991</v>
+        <v>1.5254</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0991</v>
+        <v>1.2281</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.2973</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0991</v>
+        <v>1.2281</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0991</v>
+        <v>1.2786</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2973</v>
       </c>
       <c r="K28" t="n">
+        <v>134</v>
+      </c>
+      <c r="L28" t="n">
         <v>136</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
-        <v>1.0991</v>
+        <v>1.5759</v>
       </c>
       <c r="N28" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0909</v>
+        <v>1.2842</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4675</v>
+        <v>0.5504</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0583</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0909</v>
+        <v>1.2842</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2704</v>
+        <v>1.3993</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1795</v>
+        <v>-0.1151</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2704</v>
+        <v>1.3993</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2811</v>
+        <v>1.4569</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1795</v>
+        <v>-0.1151</v>
       </c>
       <c r="K29" t="n">
         <v>87</v>
@@ -1771,7 +1771,7 @@
         <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1016</v>
+        <v>1.3418</v>
       </c>
       <c r="N29" t="n">
         <v>148</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9989</v>
+        <v>1.2811</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4281</v>
+        <v>0.549</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0459</v>
+        <v>-0.0597</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9989</v>
+        <v>1.2811</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0216</v>
+        <v>1.2811</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0227</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0216</v>
+        <v>1.2811</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0216</v>
+        <v>1.2811</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0227</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9989</v>
+        <v>1.2811</v>
       </c>
       <c r="N30" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9297</v>
+        <v>1.2579</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3984</v>
+        <v>0.5391</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0735</v>
+        <v>-0.0701</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9297</v>
+        <v>1.2579</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8125</v>
+        <v>1.2748</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1172</v>
+        <v>-0.0169</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8125</v>
+        <v>1.2748</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8193</v>
+        <v>1.2748</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1172</v>
+        <v>-0.0169</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="L31" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9365</v>
+        <v>1.2579</v>
       </c>
       <c r="N31" t="n">
-        <v>270</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8704</v>
+        <v>1.1455</v>
       </c>
       <c r="C32" t="n">
-        <v>0.373</v>
+        <v>0.4909</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1209</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8704</v>
+        <v>1.1455</v>
       </c>
       <c r="F32" t="n">
-        <v>0.32</v>
+        <v>0.5117</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5504</v>
+        <v>0.6338</v>
       </c>
       <c r="H32" t="n">
-        <v>0.32</v>
+        <v>0.5117</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3227</v>
+        <v>0.5327</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5504</v>
+        <v>0.6338</v>
       </c>
       <c r="K32" t="n">
         <v>134</v>
@@ -1909,7 +1909,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8731</v>
+        <v>1.1665</v>
       </c>
       <c r="N32" t="n">
         <v>270</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2574</v>
+        <v>0.4518</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2046</v>
+        <v>-0.1621</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6007</v>
+        <v>1.0542</v>
       </c>
       <c r="N33" t="n">
         <v>124</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5726</v>
+        <v>1.035</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2454</v>
+        <v>0.4436</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2158</v>
+        <v>-0.1708</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5726</v>
+        <v>1.035</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5726</v>
+        <v>1.8938</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-0.8588</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5726</v>
+        <v>1.8938</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5726</v>
+        <v>1.8938</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.8588</v>
       </c>
       <c r="K34" t="n">
         <v>85</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5726</v>
+        <v>1.035</v>
       </c>
       <c r="N34" t="n">
         <v>131</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5568</v>
+        <v>1.0227</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2386</v>
+        <v>0.4383</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2221</v>
+        <v>-0.1763</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5568</v>
+        <v>1.0227</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5568</v>
+        <v>0.7301</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.2926</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5568</v>
+        <v>0.7301</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5568</v>
+        <v>0.7601</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.2926</v>
       </c>
       <c r="K35" t="n">
+        <v>134</v>
+      </c>
+      <c r="L35" t="n">
         <v>136</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
-        <v>0.5568</v>
+        <v>1.0527</v>
       </c>
       <c r="N35" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2143</v>
+        <v>0.4001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2447</v>
+        <v>-0.2165</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5001</v>
+        <v>0.9337</v>
       </c>
       <c r="N36" t="n">
         <v>124</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4065</v>
+        <v>0.7129</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1742</v>
+        <v>0.3055</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.282</v>
+        <v>-0.3162</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4065</v>
+        <v>0.7129</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4468</v>
+        <v>0.7129</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4468</v>
+        <v>0.7129</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4506</v>
+        <v>0.7129</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.7129</v>
+      </c>
+      <c r="N37" t="n">
         <v>136</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="N37" t="n">
-        <v>270</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1583</v>
+        <v>0.2534</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2968</v>
+        <v>-0.371</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3693</v>
+        <v>0.5914</v>
       </c>
       <c r="N38" t="n">
         <v>136</v>
@@ -2194,185 +2194,185 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>ptr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1296</v>
+        <v>0.0788</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5643</v>
+        <v>-0.555</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.3023</v>
+        <v>0.1838</v>
       </c>
       <c r="N39" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1368</v>
+        <v>0.0228</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.614</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.3192</v>
+        <v>0.0531</v>
       </c>
       <c r="N40" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.174</v>
+        <v>0.0066</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6057</v>
+        <v>-0.631</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="N41" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ptr</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2083</v>
+        <v>0.0007</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6375</v>
+        <v>-0.6372</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.486</v>
+        <v>0.0017</v>
       </c>
       <c r="N42" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2956</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7187</v>
+        <v>-0.7123</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.6898</v>
+        <v>-0.1646</v>
       </c>
       <c r="N43" t="n">
         <v>96</v>
@@ -2424,170 +2424,170 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3242</v>
+        <v>-0.1552</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7453</v>
+        <v>-0.8015</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.7565</v>
+        <v>-0.3622</v>
       </c>
       <c r="N44" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.3553</v>
+        <v>-0.2022</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7742</v>
+        <v>-0.8511</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.4719</v>
       </c>
       <c r="N45" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3613</v>
+        <v>-0.2473</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.7798</v>
+        <v>-0.8985</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.8431</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3753</v>
+        <v>-0.2894</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.9429</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.8758</v>
+        <v>-0.6753</v>
       </c>
       <c r="N47" t="n">
         <v>136</v>
@@ -2608,139 +2608,139 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.5223</v>
+        <v>-0.2972</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9294</v>
+        <v>-0.951</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.2187</v>
+        <v>-0.6934</v>
       </c>
       <c r="N48" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.5321</v>
+        <v>-0.3629</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9386</v>
+        <v>-1.0203</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.2417</v>
+        <v>-0.8468</v>
       </c>
       <c r="N49" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5382</v>
+        <v>-0.372</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9443</v>
+        <v>-1.0299</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.2559</v>
+        <v>-0.8681</v>
       </c>
       <c r="N50" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.6103</v>
+        <v>-0.4215</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.0113</v>
+        <v>-1.082</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.4241</v>
+        <v>-0.9835</v>
       </c>
       <c r="N51" t="n">
         <v>142</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.6298</v>
+        <v>-0.4245</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0294</v>
+        <v>-1.0852</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.4697</v>
+        <v>-0.9905</v>
       </c>
       <c r="N52" t="n">
         <v>96</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.694</v>
+        <v>-0.4406</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0891</v>
+        <v>-1.1021</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.6194</v>
+        <v>-1.028</v>
       </c>
       <c r="N53" t="n">
         <v>101</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.8958</v>
+        <v>-0.6408</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.2767</v>
+        <v>-1.313</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-2.0903</v>
+        <v>-1.4952</v>
       </c>
       <c r="N54" t="n">
         <v>142</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.2897</v>
+        <v>-2.3818</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.9813</v>
+        <v>-1.0207</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.3561</v>
+        <v>-1.7133</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.2897</v>
+        <v>-2.3818</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2897</v>
+        <v>-1.5244</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.2897</v>
+        <v>-1.5244</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.0453</v>
+        <v>-0.7926</v>
       </c>
       <c r="J55" t="n">
-        <v>-1</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="K55" t="n">
         <v>109</v>
@@ -2967,7 +2967,7 @@
         <v>51</v>
       </c>
       <c r="M55" t="n">
-        <v>-2.0453</v>
+        <v>-1.65</v>
       </c>
       <c r="N55" t="n">
         <v>160</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.288</v>
+        <v>-1.0284</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.6413</v>
+        <v>-1.7214</v>
       </c>
       <c r="E56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-3.0054</v>
+        <v>-2.3997</v>
       </c>
       <c r="N56" t="n">
         <v>101</v>
@@ -3119,10 +3119,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.642</v>
+        <v>0.5618</v>
       </c>
       <c r="J2" t="n">
-        <v>23.112</v>
+        <v>20.2248</v>
       </c>
     </row>
     <row r="3">
@@ -3159,10 +3159,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.439</v>
+        <v>0.3751</v>
       </c>
       <c r="J3" t="n">
-        <v>15.804</v>
+        <v>13.5036</v>
       </c>
     </row>
     <row r="4">
@@ -3199,10 +3199,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1617</v>
+        <v>0.1604</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8212</v>
+        <v>5.7744</v>
       </c>
     </row>
     <row r="5">
@@ -3239,10 +3239,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2267</v>
+        <v>-0.1251</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.161199999999999</v>
+        <v>-4.5036</v>
       </c>
     </row>
     <row r="6">
@@ -3279,10 +3279,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2435</v>
+        <v>-0.1366</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.766</v>
+        <v>-4.9176</v>
       </c>
     </row>
     <row r="7">
@@ -3319,10 +3319,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3127</v>
+        <v>0.2662</v>
       </c>
       <c r="J7" t="n">
-        <v>11.2572</v>
+        <v>9.5832</v>
       </c>
     </row>
     <row r="8">
@@ -3359,10 +3359,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0466</v>
+        <v>0.03</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6776</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="9">
@@ -3399,10 +3399,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9564</v>
+        <v>-2.2428</v>
       </c>
     </row>
     <row r="10">
@@ -3439,10 +3439,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1513</v>
+        <v>-0.0871</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.4468</v>
+        <v>-3.1356</v>
       </c>
     </row>
     <row r="11">
@@ -3479,10 +3479,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2417</v>
+        <v>-0.1441</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.7012</v>
+        <v>-5.1876</v>
       </c>
     </row>
     <row r="12">
@@ -3519,10 +3519,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2204</v>
+        <v>-0.1846</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.8488</v>
+        <v>-4.0612</v>
       </c>
     </row>
     <row r="13">
@@ -3559,10 +3559,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2204</v>
+        <v>-0.1846</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.8488</v>
+        <v>-4.0612</v>
       </c>
     </row>
     <row r="14">
@@ -3599,10 +3599,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2859</v>
+        <v>-0.2256</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.2898</v>
+        <v>-4.9632</v>
       </c>
     </row>
     <row r="15">
@@ -3639,10 +3639,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4521</v>
+        <v>-0.3094</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.946199999999999</v>
+        <v>-6.8068</v>
       </c>
     </row>
     <row r="16">
@@ -3679,10 +3679,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6929</v>
+        <v>-0.4682</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.2438</v>
+        <v>-10.3004</v>
       </c>
     </row>
     <row r="17">
@@ -3719,10 +3719,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1209</v>
+        <v>1.0908</v>
       </c>
       <c r="J17" t="n">
-        <v>24.6598</v>
+        <v>23.9976</v>
       </c>
     </row>
     <row r="18">
@@ -3759,10 +3759,10 @@
         <v>1.47</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1002</v>
+        <v>1.0784</v>
       </c>
       <c r="J18" t="n">
-        <v>24.2044</v>
+        <v>23.7248</v>
       </c>
     </row>
     <row r="19">
@@ -3799,10 +3799,10 @@
         <v>1.44</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0369</v>
+        <v>1.0397</v>
       </c>
       <c r="J19" t="n">
-        <v>22.8118</v>
+        <v>22.8734</v>
       </c>
     </row>
     <row r="20">
@@ -3839,10 +3839,10 @@
         <v>1.15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3195</v>
+        <v>0.4096</v>
       </c>
       <c r="J20" t="n">
-        <v>7.029</v>
+        <v>9.011200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3879,10 +3879,10 @@
         <v>1.08</v>
       </c>
       <c r="I21" t="n">
-        <v>0.13</v>
+        <v>0.2155</v>
       </c>
       <c r="J21" t="n">
-        <v>2.86</v>
+        <v>4.741</v>
       </c>
     </row>
     <row r="22">
@@ -3919,10 +3919,10 @@
         <v>0.84</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1847</v>
+        <v>-0.1619</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.8787</v>
+        <v>-3.3999</v>
       </c>
     </row>
     <row r="23">
@@ -3959,10 +3959,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.201</v>
+        <v>-0.1727</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.221</v>
+        <v>-3.6267</v>
       </c>
     </row>
     <row r="24">
@@ -3999,10 +3999,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.299</v>
+        <v>-0.2346</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.279</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="25">
@@ -4039,10 +4039,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4316</v>
+        <v>-0.2995</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.063599999999999</v>
+        <v>-6.2895</v>
       </c>
     </row>
     <row r="26">
@@ -4079,10 +4079,10 @@
         <v>0.46</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7678</v>
+        <v>-0.5232</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.1238</v>
+        <v>-10.9872</v>
       </c>
     </row>
     <row r="27">
@@ -4119,10 +4119,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3604</v>
+        <v>1.2468</v>
       </c>
       <c r="J27" t="n">
-        <v>28.5684</v>
+        <v>26.1828</v>
       </c>
     </row>
     <row r="28">
@@ -4159,10 +4159,10 @@
         <v>1.59</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3024</v>
+        <v>1.2111</v>
       </c>
       <c r="J28" t="n">
-        <v>27.3504</v>
+        <v>25.4331</v>
       </c>
     </row>
     <row r="29">
@@ -4199,10 +4199,10 @@
         <v>1.48</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0786</v>
+        <v>1.079</v>
       </c>
       <c r="J29" t="n">
-        <v>22.6506</v>
+        <v>22.659</v>
       </c>
     </row>
     <row r="30">
@@ -4239,10 +4239,10 @@
         <v>1.32</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6931</v>
+        <v>0.7996</v>
       </c>
       <c r="J30" t="n">
-        <v>14.5551</v>
+        <v>16.7916</v>
       </c>
     </row>
     <row r="31">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0003</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.785</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="32">
@@ -4319,10 +4319,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4204</v>
+        <v>0.418</v>
       </c>
       <c r="J32" t="n">
-        <v>10.51</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="33">
@@ -4359,10 +4359,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2815</v>
+        <v>0.2933</v>
       </c>
       <c r="J33" t="n">
-        <v>7.0375</v>
+        <v>7.3325</v>
       </c>
     </row>
     <row r="34">
@@ -4399,10 +4399,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1505</v>
+        <v>-0.1205</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.7625</v>
+        <v>-3.0125</v>
       </c>
     </row>
     <row r="35">
@@ -4439,10 +4439,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4464</v>
+        <v>-0.2901</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.16</v>
+        <v>-7.2525</v>
       </c>
     </row>
     <row r="36">
@@ -4479,10 +4479,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8845</v>
+        <v>-0.6132</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.1125</v>
+        <v>-15.33</v>
       </c>
     </row>
     <row r="37">
@@ -4519,10 +4519,10 @@
         <v>1.73</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6166</v>
+        <v>1.1299</v>
       </c>
       <c r="J37" t="n">
-        <v>40.415</v>
+        <v>28.2475</v>
       </c>
     </row>
     <row r="38">
@@ -4559,10 +4559,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9474</v>
+        <v>0.7094</v>
       </c>
       <c r="J38" t="n">
-        <v>23.685</v>
+        <v>17.735</v>
       </c>
     </row>
     <row r="39">
@@ -4599,10 +4599,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5632</v>
+        <v>0.5142</v>
       </c>
       <c r="J39" t="n">
-        <v>14.08</v>
+        <v>12.855</v>
       </c>
     </row>
     <row r="40">
@@ -4639,10 +4639,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3597</v>
+        <v>0.3986</v>
       </c>
       <c r="J40" t="n">
-        <v>8.9925</v>
+        <v>9.965</v>
       </c>
     </row>
     <row r="41">
@@ -4679,10 +4679,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4443</v>
+        <v>-0.3655</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.1075</v>
+        <v>-9.137499999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4719,10 +4719,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5978</v>
+        <v>0.5619</v>
       </c>
       <c r="J42" t="n">
-        <v>15.5428</v>
+        <v>14.6094</v>
       </c>
     </row>
     <row r="43">
@@ -4759,10 +4759,10 @@
         <v>0.99</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0098</v>
+        <v>-0.0176</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2548</v>
+        <v>-0.4576</v>
       </c>
     </row>
     <row r="44">
@@ -4799,10 +4799,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2313</v>
+        <v>-0.1408</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.0138</v>
+        <v>-3.6608</v>
       </c>
     </row>
     <row r="45">
@@ -4839,10 +4839,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3883</v>
+        <v>-0.2442</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.0958</v>
+        <v>-6.3492</v>
       </c>
     </row>
     <row r="46">
@@ -4879,10 +4879,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4027</v>
+        <v>-0.2542</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4702</v>
+        <v>-6.6092</v>
       </c>
     </row>
     <row r="47">
@@ -4919,10 +4919,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4095</v>
+        <v>0.9866</v>
       </c>
       <c r="J47" t="n">
-        <v>36.647</v>
+        <v>25.6516</v>
       </c>
     </row>
     <row r="48">
@@ -4959,10 +4959,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5759</v>
+        <v>0.4573</v>
       </c>
       <c r="J48" t="n">
-        <v>14.9734</v>
+        <v>11.8898</v>
       </c>
     </row>
     <row r="49">
@@ -4999,10 +4999,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3995</v>
+        <v>-0.3385</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.387</v>
+        <v>-8.801</v>
       </c>
     </row>
     <row r="50">
@@ -5039,10 +5039,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5653</v>
+        <v>-0.5077</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.6978</v>
+        <v>-13.2002</v>
       </c>
     </row>
     <row r="51">
@@ -5079,10 +5079,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6169</v>
+        <v>-0.5615</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.0394</v>
+        <v>-14.599</v>
       </c>
     </row>
     <row r="52">
@@ -5119,10 +5119,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3382</v>
+        <v>0.2844</v>
       </c>
       <c r="J52" t="n">
-        <v>8.793200000000001</v>
+        <v>7.3944</v>
       </c>
     </row>
     <row r="53">
@@ -5159,10 +5159,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3071</v>
+        <v>0.2539</v>
       </c>
       <c r="J53" t="n">
-        <v>7.9846</v>
+        <v>6.6014</v>
       </c>
     </row>
     <row r="54">
@@ -5199,10 +5199,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2142</v>
+        <v>-0.1366</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.5692</v>
+        <v>-3.5516</v>
       </c>
     </row>
     <row r="55">
@@ -5239,10 +5239,10 @@
         <v>0.75</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4351</v>
+        <v>-0.2786</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.3126</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="56">
@@ -5279,10 +5279,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5306</v>
+        <v>-0.3457</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.7956</v>
+        <v>-8.988200000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5319,10 +5319,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4562</v>
+        <v>0.3694</v>
       </c>
       <c r="J57" t="n">
-        <v>11.8612</v>
+        <v>9.6044</v>
       </c>
     </row>
     <row r="58">
@@ -5359,10 +5359,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3273</v>
+        <v>0.2856</v>
       </c>
       <c r="J58" t="n">
-        <v>8.5098</v>
+        <v>7.4256</v>
       </c>
     </row>
     <row r="59">
@@ -5399,10 +5399,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2784</v>
+        <v>0.2486</v>
       </c>
       <c r="J59" t="n">
-        <v>7.2384</v>
+        <v>6.4636</v>
       </c>
     </row>
     <row r="60">
@@ -5439,10 +5439,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1842</v>
+        <v>0.1847</v>
       </c>
       <c r="J60" t="n">
-        <v>4.7892</v>
+        <v>4.8022</v>
       </c>
     </row>
     <row r="61">
@@ -5479,10 +5479,10 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0609</v>
+        <v>-0.0144</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.5834</v>
+        <v>-0.3744</v>
       </c>
     </row>
     <row r="62">
@@ -5519,10 +5519,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1474</v>
+        <v>0.8317</v>
       </c>
       <c r="J62" t="n">
-        <v>26.3902</v>
+        <v>19.1291</v>
       </c>
     </row>
     <row r="63">
@@ -5559,10 +5559,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9113</v>
+        <v>0.6933</v>
       </c>
       <c r="J63" t="n">
-        <v>20.9599</v>
+        <v>15.9459</v>
       </c>
     </row>
     <row r="64">
@@ -5599,10 +5599,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8411</v>
+        <v>0.6551</v>
       </c>
       <c r="J64" t="n">
-        <v>19.3453</v>
+        <v>15.0673</v>
       </c>
     </row>
     <row r="65">
@@ -5639,10 +5639,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3753</v>
+        <v>0.4106</v>
       </c>
       <c r="J65" t="n">
-        <v>8.6319</v>
+        <v>9.4438</v>
       </c>
     </row>
     <row r="66">
@@ -5679,10 +5679,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3753</v>
+        <v>0.4106</v>
       </c>
       <c r="J66" t="n">
-        <v>8.6319</v>
+        <v>9.4438</v>
       </c>
     </row>
     <row r="67">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1856</v>
+        <v>0.1687</v>
       </c>
       <c r="J67" t="n">
-        <v>4.2688</v>
+        <v>3.8801</v>
       </c>
     </row>
     <row r="68">
@@ -5759,10 +5759,10 @@
         <v>1.02</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1425</v>
+        <v>0.1153</v>
       </c>
       <c r="J68" t="n">
-        <v>3.2775</v>
+        <v>2.6519</v>
       </c>
     </row>
     <row r="69">
@@ -5799,10 +5799,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1703</v>
+        <v>-0.1381</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.9169</v>
+        <v>-3.1763</v>
       </c>
     </row>
     <row r="70">
@@ -5839,10 +5839,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3423</v>
+        <v>-0.2279</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.8729</v>
+        <v>-5.2417</v>
       </c>
     </row>
     <row r="71">
@@ -5879,10 +5879,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.5829</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.4649</v>
+        <v>-13.4067</v>
       </c>
     </row>
     <row r="72">
@@ -5919,10 +5919,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.379</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>35.854</v>
+        <v>25.2538</v>
       </c>
     </row>
     <row r="73">
@@ -5959,10 +5959,10 @@
         <v>1.36</v>
       </c>
       <c r="I73" t="n">
-        <v>0.907</v>
+        <v>0.6781</v>
       </c>
       <c r="J73" t="n">
-        <v>23.582</v>
+        <v>17.6306</v>
       </c>
     </row>
     <row r="74">
@@ -5999,10 +5999,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3014</v>
+        <v>0.3586</v>
       </c>
       <c r="J74" t="n">
-        <v>7.8364</v>
+        <v>9.323600000000001</v>
       </c>
     </row>
     <row r="75">
@@ -6039,10 +6039,10 @@
         <v>1.11</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2461</v>
+        <v>0.3198</v>
       </c>
       <c r="J75" t="n">
-        <v>6.3986</v>
+        <v>8.3148</v>
       </c>
     </row>
     <row r="76">
@@ -6079,10 +6079,10 @@
         <v>1.01</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0791</v>
+        <v>-0.0036</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.0566</v>
+        <v>-0.0936</v>
       </c>
     </row>
     <row r="77">
@@ -6119,10 +6119,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3126</v>
+        <v>0.3305</v>
       </c>
       <c r="J77" t="n">
-        <v>8.127599999999999</v>
+        <v>8.593</v>
       </c>
     </row>
     <row r="78">
@@ -6159,10 +6159,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2097</v>
+        <v>0.2024</v>
       </c>
       <c r="J78" t="n">
-        <v>5.4522</v>
+        <v>5.2624</v>
       </c>
     </row>
     <row r="79">
@@ -6199,10 +6199,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1527</v>
+        <v>-0.121</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.9702</v>
+        <v>-3.146</v>
       </c>
     </row>
     <row r="80">
@@ -6239,10 +6239,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5309</v>
+        <v>-0.3479</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.8034</v>
+        <v>-9.045400000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6279,10 +6279,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6602</v>
+        <v>-0.4412</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.1652</v>
+        <v>-11.4712</v>
       </c>
     </row>
     <row r="82">
@@ -6319,10 +6319,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1271</v>
+        <v>0.1219</v>
       </c>
       <c r="J82" t="n">
-        <v>3.5588</v>
+        <v>3.4132</v>
       </c>
     </row>
     <row r="83">
@@ -6359,10 +6359,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1055</v>
+        <v>0.0973</v>
       </c>
       <c r="J83" t="n">
-        <v>2.954</v>
+        <v>2.7244</v>
       </c>
     </row>
     <row r="84">
@@ -6399,10 +6399,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J84" t="n">
-        <v>1.568</v>
+        <v>1.1844</v>
       </c>
     </row>
     <row r="85">
@@ -6439,10 +6439,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1</v>
+        <v>-0.0608</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.8</v>
+        <v>-1.7024</v>
       </c>
     </row>
     <row r="86">
@@ -6479,10 +6479,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3472</v>
+        <v>-0.2155</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.7216</v>
+        <v>-6.034</v>
       </c>
     </row>
     <row r="87">
@@ -6519,10 +6519,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1046</v>
+        <v>0.7891</v>
       </c>
       <c r="J87" t="n">
-        <v>30.9288</v>
+        <v>22.0948</v>
       </c>
     </row>
     <row r="88">
@@ -6559,10 +6559,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5157</v>
       </c>
       <c r="J88" t="n">
-        <v>18.2476</v>
+        <v>14.4396</v>
       </c>
     </row>
     <row r="89">
@@ -6599,10 +6599,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4234</v>
+        <v>0.3999</v>
       </c>
       <c r="J89" t="n">
-        <v>11.8552</v>
+        <v>11.1972</v>
       </c>
     </row>
     <row r="90">
@@ -6639,10 +6639,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4234</v>
+        <v>0.3999</v>
       </c>
       <c r="J90" t="n">
-        <v>11.8552</v>
+        <v>11.1972</v>
       </c>
     </row>
     <row r="91">
@@ -6679,10 +6679,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7408</v>
+        <v>-0.6886</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.7424</v>
+        <v>-19.2808</v>
       </c>
     </row>
     <row r="92">
@@ -6719,10 +6719,10 @@
         <v>0.99</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0978</v>
+        <v>0.0597</v>
       </c>
       <c r="J92" t="n">
-        <v>1.7604</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="93">
@@ -6759,10 +6759,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1498</v>
+        <v>-0.1388</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.6964</v>
+        <v>-2.4984</v>
       </c>
     </row>
     <row r="94">
@@ -6799,10 +6799,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4098</v>
+        <v>-0.29</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.3764</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="95">
@@ -6839,10 +6839,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4462</v>
+        <v>-0.3081</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.031599999999999</v>
+        <v>-5.5458</v>
       </c>
     </row>
     <row r="96">
@@ -6879,10 +6879,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9238</v>
+        <v>-0.6433</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.6284</v>
+        <v>-11.5794</v>
       </c>
     </row>
     <row r="97">
@@ -6919,10 +6919,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.872</v>
+        <v>1.3902</v>
       </c>
       <c r="J97" t="n">
-        <v>33.696</v>
+        <v>25.0236</v>
       </c>
     </row>
     <row r="98">
@@ -6959,10 +6959,10 @@
         <v>1.77</v>
       </c>
       <c r="I98" t="n">
-        <v>1.5997</v>
+        <v>1.1319</v>
       </c>
       <c r="J98" t="n">
-        <v>28.7946</v>
+        <v>20.3742</v>
       </c>
     </row>
     <row r="99">
@@ -6999,10 +6999,10 @@
         <v>1.39</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8086</v>
+        <v>0.6881</v>
       </c>
       <c r="J99" t="n">
-        <v>14.5548</v>
+        <v>12.3858</v>
       </c>
     </row>
     <row r="100">
@@ -7039,10 +7039,10 @@
         <v>1.27</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>9.844200000000001</v>
+        <v>9.5526</v>
       </c>
     </row>
     <row r="101">
@@ -7079,10 +7079,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0037</v>
+        <v>0.0863</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.06660000000000001</v>
+        <v>1.5534</v>
       </c>
     </row>
     <row r="102">
@@ -7119,10 +7119,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4285</v>
+        <v>0.4257</v>
       </c>
       <c r="J102" t="n">
-        <v>10.7125</v>
+        <v>10.6425</v>
       </c>
     </row>
     <row r="103">
@@ -7159,10 +7159,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0592</v>
+        <v>-0.0558</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.48</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="104">
@@ -7199,10 +7199,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1702</v>
+        <v>-0.1145</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.255</v>
+        <v>-2.8625</v>
       </c>
     </row>
     <row r="105">
@@ -7239,10 +7239,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4048</v>
+        <v>-0.2583</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.12</v>
+        <v>-6.4575</v>
       </c>
     </row>
     <row r="106">
@@ -7279,10 +7279,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4754</v>
+        <v>-0.3068</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.885</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="107">
@@ -7319,10 +7319,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4986</v>
+        <v>1.048</v>
       </c>
       <c r="J107" t="n">
-        <v>37.465</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="108">
@@ -7359,10 +7359,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3858</v>
+        <v>0.3962</v>
       </c>
       <c r="J108" t="n">
-        <v>9.645</v>
+        <v>9.904999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -7399,10 +7399,10 @@
         <v>1.07</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1523</v>
+        <v>0.2178</v>
       </c>
       <c r="J109" t="n">
-        <v>3.8075</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="110">
@@ -7439,10 +7439,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0886</v>
+        <v>0.1553</v>
       </c>
       <c r="J110" t="n">
-        <v>2.215</v>
+        <v>3.8825</v>
       </c>
     </row>
     <row r="111">
@@ -7479,10 +7479,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0198</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>0.495</v>
+        <v>2.1875</v>
       </c>
     </row>
     <row r="112">
@@ -7519,10 +7519,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J112" t="n">
-        <v>8.676</v>
+        <v>9.5076</v>
       </c>
     </row>
     <row r="113">
@@ -7559,10 +7559,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1701</v>
+        <v>0.1814</v>
       </c>
       <c r="J113" t="n">
-        <v>6.1236</v>
+        <v>6.5304</v>
       </c>
     </row>
     <row r="114">
@@ -7599,10 +7599,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.3348</v>
+        <v>-0.0216</v>
       </c>
     </row>
     <row r="115">
@@ -7639,10 +7639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.159</v>
+        <v>-0.0892</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.724</v>
+        <v>-3.2112</v>
       </c>
     </row>
     <row r="116">
@@ -7679,10 +7679,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1779</v>
+        <v>-0.1011</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.4044</v>
+        <v>-3.6396</v>
       </c>
     </row>
     <row r="117">
@@ -7719,10 +7719,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8449</v>
+        <v>0.6231</v>
       </c>
       <c r="J117" t="n">
-        <v>30.4164</v>
+        <v>22.4316</v>
       </c>
     </row>
     <row r="118">
@@ -7759,10 +7759,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5233</v>
+        <v>0.435</v>
       </c>
       <c r="J118" t="n">
-        <v>18.8388</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="119">
@@ -7799,10 +7799,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4082</v>
+        <v>0.374</v>
       </c>
       <c r="J119" t="n">
-        <v>14.6952</v>
+        <v>13.464</v>
       </c>
     </row>
     <row r="120">
@@ -7839,10 +7839,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1656</v>
+        <v>0.2067</v>
       </c>
       <c r="J120" t="n">
-        <v>5.9616</v>
+        <v>7.4412</v>
       </c>
     </row>
     <row r="121">
@@ -7879,10 +7879,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5271</v>
+        <v>-0.464</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.9756</v>
+        <v>-16.704</v>
       </c>
     </row>
     <row r="122">
@@ -7919,10 +7919,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9414</v>
+        <v>0.9365</v>
       </c>
       <c r="J122" t="n">
-        <v>27.3006</v>
+        <v>27.1585</v>
       </c>
     </row>
     <row r="123">
@@ -7959,10 +7959,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9193</v>
+        <v>0.915</v>
       </c>
       <c r="J123" t="n">
-        <v>26.6597</v>
+        <v>26.535</v>
       </c>
     </row>
     <row r="124">
@@ -7999,10 +7999,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3073</v>
+        <v>0.3631</v>
       </c>
       <c r="J124" t="n">
-        <v>8.9117</v>
+        <v>10.5299</v>
       </c>
     </row>
     <row r="125">
@@ -8039,10 +8039,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.219</v>
+        <v>0.2797</v>
       </c>
       <c r="J125" t="n">
-        <v>6.351</v>
+        <v>8.1113</v>
       </c>
     </row>
     <row r="126">
@@ -8079,10 +8079,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2873</v>
+        <v>-0.2109</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.3317</v>
+        <v>-6.1161</v>
       </c>
     </row>
     <row r="127">
@@ -8119,10 +8119,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.125</v>
+        <v>0.1088</v>
       </c>
       <c r="J127" t="n">
-        <v>3.625</v>
+        <v>3.1552</v>
       </c>
     </row>
     <row r="128">
@@ -8159,10 +8159,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.125</v>
+        <v>0.1088</v>
       </c>
       <c r="J128" t="n">
-        <v>3.625</v>
+        <v>3.1552</v>
       </c>
     </row>
     <row r="129">
@@ -8199,10 +8199,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1789</v>
+        <v>-0.1155</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.1881</v>
+        <v>-3.3495</v>
       </c>
     </row>
     <row r="130">
@@ -8239,10 +8239,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1985</v>
+        <v>-0.1264</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.7565</v>
+        <v>-3.6656</v>
       </c>
     </row>
     <row r="131">
@@ -8279,10 +8279,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4225</v>
+        <v>-0.2696</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.2525</v>
+        <v>-7.8184</v>
       </c>
     </row>
     <row r="132">
@@ -8319,10 +8319,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9329</v>
+        <v>0.9314</v>
       </c>
       <c r="J132" t="n">
-        <v>21.4567</v>
+        <v>21.4222</v>
       </c>
     </row>
     <row r="133">
@@ -8359,10 +8359,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8883</v>
+        <v>0.8874</v>
       </c>
       <c r="J133" t="n">
-        <v>20.4309</v>
+        <v>20.4102</v>
       </c>
     </row>
     <row r="134">
@@ -8399,10 +8399,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4403</v>
+        <v>0.4892</v>
       </c>
       <c r="J134" t="n">
-        <v>10.1269</v>
+        <v>11.2516</v>
       </c>
     </row>
     <row r="135">
@@ -8439,10 +8439,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1543</v>
       </c>
       <c r="J135" t="n">
-        <v>1.9987</v>
+        <v>3.5489</v>
       </c>
     </row>
     <row r="136">
@@ -8479,10 +8479,10 @@
         <v>1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0533</v>
+        <v>0.1212</v>
       </c>
       <c r="J136" t="n">
-        <v>1.2259</v>
+        <v>2.7876</v>
       </c>
     </row>
     <row r="137">
@@ -8519,10 +8519,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2062</v>
+        <v>0.2135</v>
       </c>
       <c r="J137" t="n">
-        <v>4.7426</v>
+        <v>4.9105</v>
       </c>
     </row>
     <row r="138">
@@ -8559,10 +8559,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0849</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>1.9527</v>
+        <v>1.6652</v>
       </c>
     </row>
     <row r="139">
@@ -8599,10 +8599,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.5318</v>
+        <v>-1.0948</v>
       </c>
     </row>
     <row r="140">
@@ -8639,10 +8639,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2335</v>
+        <v>-0.1415</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.3705</v>
+        <v>-3.2545</v>
       </c>
     </row>
     <row r="141">
@@ -8679,10 +8679,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2671</v>
+        <v>-0.163</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.1433</v>
+        <v>-3.749</v>
       </c>
     </row>
     <row r="142">
@@ -8719,10 +8719,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2907</v>
+        <v>1.1845</v>
       </c>
       <c r="J142" t="n">
-        <v>33.5582</v>
+        <v>30.797</v>
       </c>
     </row>
     <row r="143">
@@ -8759,10 +8759,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8255</v>
+        <v>0.8218</v>
       </c>
       <c r="J143" t="n">
-        <v>21.463</v>
+        <v>21.3668</v>
       </c>
     </row>
     <row r="144">
@@ -8799,10 +8799,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2455</v>
+        <v>0.3067</v>
       </c>
       <c r="J144" t="n">
-        <v>6.383</v>
+        <v>7.9742</v>
       </c>
     </row>
     <row r="145">
@@ -8839,10 +8839,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1751</v>
+        <v>-0.099</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.5526</v>
+        <v>-2.574</v>
       </c>
     </row>
     <row r="146">
@@ -8879,10 +8879,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2171</v>
+        <v>-0.1402</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.6446</v>
+        <v>-3.6452</v>
       </c>
     </row>
     <row r="147">
@@ -8919,10 +8919,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.739</v>
+        <v>0.9192</v>
       </c>
       <c r="J147" t="n">
-        <v>19.214</v>
+        <v>23.8992</v>
       </c>
     </row>
     <row r="148">
@@ -8959,10 +8959,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1182</v>
+        <v>-0.0828</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.0732</v>
+        <v>-2.1528</v>
       </c>
     </row>
     <row r="149">
@@ -8999,10 +8999,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1447</v>
+        <v>-0.0941</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.7622</v>
+        <v>-2.4466</v>
       </c>
     </row>
     <row r="150">
@@ -9039,10 +9039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3526</v>
+        <v>-0.2216</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.1676</v>
+        <v>-5.7616</v>
       </c>
     </row>
     <row r="151">
@@ -9079,10 +9079,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.4682</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.1246</v>
+        <v>-12.1732</v>
       </c>
     </row>
     <row r="152">
@@ -9119,10 +9119,10 @@
         <v>1.23</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4746</v>
+        <v>0.5503</v>
       </c>
       <c r="J152" t="n">
-        <v>11.865</v>
+        <v>13.7575</v>
       </c>
     </row>
     <row r="153">
@@ -9159,10 +9159,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2956</v>
+        <v>0.312</v>
       </c>
       <c r="J153" t="n">
-        <v>7.39</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="154">
@@ -9199,10 +9199,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4483</v>
+        <v>-0.2909</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.2075</v>
+        <v>-7.2725</v>
       </c>
     </row>
     <row r="155">
@@ -9239,10 +9239,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5712</v>
+        <v>-0.3764</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.28</v>
+        <v>-9.41</v>
       </c>
     </row>
     <row r="156">
@@ -9279,10 +9279,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5972</v>
+        <v>-0.3951</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.93</v>
+        <v>-9.8775</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9319,10 @@
         <v>1.81</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7385</v>
+        <v>1.4866</v>
       </c>
       <c r="J157" t="n">
-        <v>43.4625</v>
+        <v>37.165</v>
       </c>
     </row>
     <row r="158">
@@ -9359,10 +9359,10 @@
         <v>1.37</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8742</v>
+        <v>0.9174</v>
       </c>
       <c r="J158" t="n">
-        <v>21.855</v>
+        <v>22.935</v>
       </c>
     </row>
     <row r="159">
@@ -9399,10 +9399,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6358</v>
+        <v>0.7234</v>
       </c>
       <c r="J159" t="n">
-        <v>15.895</v>
+        <v>18.085</v>
       </c>
     </row>
     <row r="160">
@@ -9439,10 +9439,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3916</v>
+        <v>0.4844</v>
       </c>
       <c r="J160" t="n">
-        <v>9.789999999999999</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="161">
@@ -9479,10 +9479,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0298</v>
+        <v>0.0525</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.745</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="162">
@@ -9519,10 +9519,10 @@
         <v>1.71</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5564</v>
+        <v>1.3665</v>
       </c>
       <c r="J162" t="n">
-        <v>35.7972</v>
+        <v>31.4295</v>
       </c>
     </row>
     <row r="163">
@@ -9559,10 +9559,10 @@
         <v>1.52</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1937</v>
+        <v>1.1373</v>
       </c>
       <c r="J163" t="n">
-        <v>27.4551</v>
+        <v>26.1579</v>
       </c>
     </row>
     <row r="164">
@@ -9599,10 +9599,10 @@
         <v>1.33</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7558</v>
+        <v>0.8324</v>
       </c>
       <c r="J164" t="n">
-        <v>17.3834</v>
+        <v>19.1452</v>
       </c>
     </row>
     <row r="165">
@@ -9639,10 +9639,10 @@
         <v>1.13</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2611</v>
+        <v>0.3524</v>
       </c>
       <c r="J165" t="n">
-        <v>6.0053</v>
+        <v>8.1052</v>
       </c>
     </row>
     <row r="166">
@@ -9679,10 +9679,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0687</v>
+        <v>0.0136</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.5801</v>
+        <v>0.3128</v>
       </c>
     </row>
     <row r="167">
@@ -9719,10 +9719,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4407</v>
+        <v>0.5081</v>
       </c>
       <c r="J167" t="n">
-        <v>10.1361</v>
+        <v>11.6863</v>
       </c>
     </row>
     <row r="168">
@@ -9759,10 +9759,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3733</v>
+        <v>-0.2656</v>
       </c>
       <c r="J168" t="n">
-        <v>-8.585900000000001</v>
+        <v>-6.1088</v>
       </c>
     </row>
     <row r="169">
@@ -9799,10 +9799,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4605</v>
+        <v>-0.3117</v>
       </c>
       <c r="J169" t="n">
-        <v>-10.5915</v>
+        <v>-7.1691</v>
       </c>
     </row>
     <row r="170">
@@ -9839,10 +9839,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5493</v>
+        <v>-0.3679</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.6339</v>
+        <v>-8.4617</v>
       </c>
     </row>
     <row r="171">
@@ -9879,10 +9879,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7476</v>
+        <v>-0.5078</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.1948</v>
+        <v>-11.6794</v>
       </c>
     </row>
     <row r="172">
@@ -9919,10 +9919,10 @@
         <v>1.27</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7738</v>
       </c>
       <c r="J172" t="n">
-        <v>33.8058</v>
+        <v>32.4996</v>
       </c>
     </row>
     <row r="173">
@@ -9959,10 +9959,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7577</v>
+        <v>0.7245</v>
       </c>
       <c r="J173" t="n">
-        <v>31.8234</v>
+        <v>30.429</v>
       </c>
     </row>
     <row r="174">
@@ -9999,10 +9999,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1201</v>
       </c>
       <c r="J174" t="n">
-        <v>3.9984</v>
+        <v>5.0442</v>
       </c>
     </row>
     <row r="175">
@@ -10039,10 +10039,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4798</v>
+        <v>-0.4214</v>
       </c>
       <c r="J175" t="n">
-        <v>-20.1516</v>
+        <v>-17.6988</v>
       </c>
     </row>
     <row r="176">
@@ -10079,10 +10079,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5868</v>
+        <v>-0.5313</v>
       </c>
       <c r="J176" t="n">
-        <v>-24.6456</v>
+        <v>-22.3146</v>
       </c>
     </row>
     <row r="177">
@@ -10119,10 +10119,10 @@
         <v>1.09</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2082</v>
+        <v>0.2244</v>
       </c>
       <c r="J177" t="n">
-        <v>8.744400000000001</v>
+        <v>9.424799999999999</v>
       </c>
     </row>
     <row r="178">
@@ -10159,10 +10159,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1718</v>
+        <v>0.1823</v>
       </c>
       <c r="J178" t="n">
-        <v>7.2156</v>
+        <v>7.6566</v>
       </c>
     </row>
     <row r="179">
@@ -10199,10 +10199,10 @@
         <v>0.99</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0442</v>
+        <v>-0.021</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.8564</v>
+        <v>-0.882</v>
       </c>
     </row>
     <row r="180">
@@ -10239,10 +10239,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0442</v>
+        <v>-0.021</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.8564</v>
+        <v>-0.882</v>
       </c>
     </row>
     <row r="181">
@@ -10279,10 +10279,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2466</v>
+        <v>-0.1459</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3572</v>
+        <v>-6.1278</v>
       </c>
     </row>
     <row r="182">
@@ -10319,10 +10319,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5728</v>
+        <v>1.38</v>
       </c>
       <c r="J182" t="n">
-        <v>39.32</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="183">
@@ -10359,10 +10359,10 @@
         <v>1.58</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2912</v>
+        <v>1.2022</v>
       </c>
       <c r="J183" t="n">
-        <v>32.28</v>
+        <v>30.055</v>
       </c>
     </row>
     <row r="184">
@@ -10399,10 +10399,10 @@
         <v>1.3</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6555</v>
+        <v>0.7583</v>
       </c>
       <c r="J184" t="n">
-        <v>16.3875</v>
+        <v>18.9575</v>
       </c>
     </row>
     <row r="185">
@@ -10439,10 +10439,10 @@
         <v>1.29</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6323</v>
+        <v>0.7357</v>
       </c>
       <c r="J185" t="n">
-        <v>15.8075</v>
+        <v>18.3925</v>
       </c>
     </row>
     <row r="186">
@@ -10479,10 +10479,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0104</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>-0.26</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="187">
@@ -10519,10 +10519,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0578</v>
+        <v>-0.0713</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.445</v>
+        <v>-1.7825</v>
       </c>
     </row>
     <row r="188">
@@ -10559,10 +10559,10 @@
         <v>0.8</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2844</v>
+        <v>-0.2137</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.11</v>
+        <v>-5.3425</v>
       </c>
     </row>
     <row r="189">
@@ -10599,10 +10599,10 @@
         <v>0.8</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2844</v>
+        <v>-0.2137</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.11</v>
+        <v>-5.3425</v>
       </c>
     </row>
     <row r="190">
@@ -10639,10 +10639,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4</v>
+        <v>-0.2698</v>
       </c>
       <c r="J190" t="n">
-        <v>-10</v>
+        <v>-6.745</v>
       </c>
     </row>
     <row r="191">
@@ -10679,10 +10679,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5618</v>
+        <v>-0.3737</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.045</v>
+        <v>-9.342499999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10719,10 +10719,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8844</v>
+        <v>1.0739</v>
       </c>
       <c r="J192" t="n">
-        <v>26.532</v>
+        <v>32.217</v>
       </c>
     </row>
     <row r="193">
@@ -10759,10 +10759,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3697</v>
+        <v>0.4267</v>
       </c>
       <c r="J193" t="n">
-        <v>11.091</v>
+        <v>12.801</v>
       </c>
     </row>
     <row r="194">
@@ -10799,10 +10799,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2786</v>
+        <v>0.3154</v>
       </c>
       <c r="J194" t="n">
-        <v>8.358000000000001</v>
+        <v>9.462</v>
       </c>
     </row>
     <row r="195">
@@ -10839,10 +10839,10 @@
         <v>0.73</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.488</v>
+        <v>-0.3121</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.64</v>
+        <v>-9.363</v>
       </c>
     </row>
     <row r="196">
@@ -10879,10 +10879,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7567</v>
+        <v>-0.514</v>
       </c>
       <c r="J196" t="n">
-        <v>-22.701</v>
+        <v>-15.42</v>
       </c>
     </row>
     <row r="197">
@@ -10919,10 +10919,10 @@
         <v>1.54</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3576</v>
+        <v>1.2254</v>
       </c>
       <c r="J197" t="n">
-        <v>40.728</v>
+        <v>36.762</v>
       </c>
     </row>
     <row r="198">
@@ -10959,10 +10959,10 @@
         <v>1.12</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3911</v>
+        <v>0.3786</v>
       </c>
       <c r="J198" t="n">
-        <v>11.733</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="199">
@@ -10999,10 +10999,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0295</v>
+        <v>0.0751</v>
       </c>
       <c r="J199" t="n">
-        <v>0.885</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="200">
@@ -11039,10 +11039,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4666</v>
+        <v>-0.4032</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.998</v>
+        <v>-12.096</v>
       </c>
     </row>
     <row r="201">
@@ -11079,10 +11079,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4942</v>
+        <v>-0.4316</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.826</v>
+        <v>-12.948</v>
       </c>
     </row>
     <row r="202">
@@ -11119,10 +11119,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0416</v>
       </c>
       <c r="J202" t="n">
-        <v>1.7451</v>
+        <v>0.8736</v>
       </c>
     </row>
     <row r="203">
@@ -11159,10 +11159,10 @@
         <v>0.79</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2818</v>
+        <v>-0.2192</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.9178</v>
+        <v>-4.6032</v>
       </c>
     </row>
     <row r="204">
@@ -11199,10 +11199,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4478</v>
+        <v>-0.3032</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.4038</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="205">
@@ -11239,10 +11239,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4634</v>
+        <v>-0.3125</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.731400000000001</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="206">
@@ -11279,10 +11279,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6333</v>
+        <v>-0.425</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.2993</v>
+        <v>-8.925000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -11319,10 +11319,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4583</v>
+        <v>1.3075</v>
       </c>
       <c r="J207" t="n">
-        <v>30.6243</v>
+        <v>27.4575</v>
       </c>
     </row>
     <row r="208">
@@ -11359,10 +11359,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1252</v>
+        <v>1.1044</v>
       </c>
       <c r="J208" t="n">
-        <v>23.6292</v>
+        <v>23.1924</v>
       </c>
     </row>
     <row r="209">
@@ -11399,10 +11399,10 @@
         <v>1.45</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0177</v>
+        <v>1.0427</v>
       </c>
       <c r="J209" t="n">
-        <v>21.3717</v>
+        <v>21.8967</v>
       </c>
     </row>
     <row r="210">
@@ -11439,10 +11439,10 @@
         <v>1.44</v>
       </c>
       <c r="I210" t="n">
-        <v>0.9952</v>
+        <v>1.0291</v>
       </c>
       <c r="J210" t="n">
-        <v>20.8992</v>
+        <v>21.6111</v>
       </c>
     </row>
     <row r="211">
@@ -11479,10 +11479,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4409</v>
+        <v>-0.3589</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.258900000000001</v>
+        <v>-7.5369</v>
       </c>
     </row>
     <row r="212">
@@ -11519,10 +11519,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1872</v>
+        <v>1.1119</v>
       </c>
       <c r="J212" t="n">
-        <v>35.616</v>
+        <v>33.357</v>
       </c>
     </row>
     <row r="213">
@@ -11559,10 +11559,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0191</v>
+        <v>0.9936</v>
       </c>
       <c r="J213" t="n">
-        <v>30.573</v>
+        <v>29.808</v>
       </c>
     </row>
     <row r="214">
@@ -11599,10 +11599,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1161</v>
       </c>
       <c r="J214" t="n">
-        <v>2.433</v>
+        <v>3.483</v>
       </c>
     </row>
     <row r="215">
@@ -11639,10 +11639,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5412</v>
+        <v>-0.4821</v>
       </c>
       <c r="J215" t="n">
-        <v>-16.236</v>
+        <v>-14.463</v>
       </c>
     </row>
     <row r="216">
@@ -11679,10 +11679,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-1.035</v>
+        <v>-1.0149</v>
       </c>
       <c r="J216" t="n">
-        <v>-31.05</v>
+        <v>-30.447</v>
       </c>
     </row>
     <row r="217">
@@ -11719,10 +11719,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4613</v>
+        <v>0.5453</v>
       </c>
       <c r="J217" t="n">
-        <v>13.839</v>
+        <v>16.359</v>
       </c>
     </row>
     <row r="218">
@@ -11759,10 +11759,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1858</v>
+        <v>0.214</v>
       </c>
       <c r="J218" t="n">
-        <v>5.574</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="219">
@@ -11799,10 +11799,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1082</v>
       </c>
       <c r="J219" t="n">
-        <v>2.262</v>
+        <v>3.246</v>
       </c>
     </row>
     <row r="220">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1146</v>
+        <v>-0.0557</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.438</v>
+        <v>-1.671</v>
       </c>
     </row>
     <row r="221">
@@ -11879,10 +11879,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2103</v>
+        <v>-0.1179</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.309</v>
+        <v>-3.537</v>
       </c>
     </row>
     <row r="222">
@@ -11919,10 +11919,10 @@
         <v>1.6</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3291</v>
+        <v>1.2258</v>
       </c>
       <c r="J222" t="n">
-        <v>29.2402</v>
+        <v>26.9676</v>
       </c>
     </row>
     <row r="223">
@@ -11959,10 +11959,10 @@
         <v>1.59</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3098</v>
+        <v>1.2139</v>
       </c>
       <c r="J223" t="n">
-        <v>28.8156</v>
+        <v>26.7058</v>
       </c>
     </row>
     <row r="224">
@@ -11999,10 +11999,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7476</v>
+        <v>0.8465</v>
       </c>
       <c r="J224" t="n">
-        <v>16.4472</v>
+        <v>18.623</v>
       </c>
     </row>
     <row r="225">
@@ -12039,10 +12039,10 @@
         <v>1.29</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6314</v>
+        <v>0.7353</v>
       </c>
       <c r="J225" t="n">
-        <v>13.8908</v>
+        <v>16.1766</v>
       </c>
     </row>
     <row r="226">
@@ -12079,10 +12079,10 @@
         <v>1.13</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2458</v>
+        <v>0.3418</v>
       </c>
       <c r="J226" t="n">
-        <v>5.4076</v>
+        <v>7.5196</v>
       </c>
     </row>
     <row r="227">
@@ -12119,10 +12119,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3801</v>
+        <v>0.4221</v>
       </c>
       <c r="J227" t="n">
-        <v>8.3622</v>
+        <v>9.286199999999999</v>
       </c>
     </row>
     <row r="228">
@@ -12159,10 +12159,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3197</v>
+        <v>-0.2323</v>
       </c>
       <c r="J228" t="n">
-        <v>-7.0334</v>
+        <v>-5.1106</v>
       </c>
     </row>
     <row r="229">
@@ -12199,10 +12199,10 @@
         <v>0.76</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3636</v>
+        <v>-0.2505</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.9992</v>
+        <v>-5.511</v>
       </c>
     </row>
     <row r="230">
@@ -12239,10 +12239,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3811</v>
+        <v>-0.2599</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.3842</v>
+        <v>-5.7178</v>
       </c>
     </row>
     <row r="231">
@@ -12279,10 +12279,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.791</v>
+        <v>-0.5402</v>
       </c>
       <c r="J231" t="n">
-        <v>-17.402</v>
+        <v>-11.8844</v>
       </c>
     </row>
     <row r="232">
@@ -12319,10 +12319,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3611</v>
+        <v>1.236</v>
       </c>
       <c r="J232" t="n">
-        <v>31.3053</v>
+        <v>28.428</v>
       </c>
     </row>
     <row r="233">
@@ -12359,10 +12359,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7411</v>
+        <v>0.7759</v>
       </c>
       <c r="J233" t="n">
-        <v>17.0453</v>
+        <v>17.8457</v>
       </c>
     </row>
     <row r="234">
@@ -12399,10 +12399,10 @@
         <v>1.24</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5695</v>
+        <v>0.6417</v>
       </c>
       <c r="J234" t="n">
-        <v>13.0985</v>
+        <v>14.7591</v>
       </c>
     </row>
     <row r="235">
@@ -12439,10 +12439,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3641</v>
+        <v>0.4459</v>
       </c>
       <c r="J235" t="n">
-        <v>8.3743</v>
+        <v>10.2557</v>
       </c>
     </row>
     <row r="236">
@@ -12479,10 +12479,10 @@
         <v>1.1</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2027</v>
+        <v>0.2842</v>
       </c>
       <c r="J236" t="n">
-        <v>4.6621</v>
+        <v>6.5366</v>
       </c>
     </row>
     <row r="237">
@@ -12519,10 +12519,10 @@
         <v>0.98</v>
       </c>
       <c r="I237" t="n">
-        <v>0.0466</v>
+        <v>-0.0012</v>
       </c>
       <c r="J237" t="n">
-        <v>1.0718</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="238">
@@ -12559,10 +12559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2629</v>
+        <v>-0.2031</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.0467</v>
+        <v>-4.6713</v>
       </c>
     </row>
     <row r="239">
@@ -12599,10 +12599,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2985</v>
+        <v>-0.2227</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.8655</v>
+        <v>-5.1221</v>
       </c>
     </row>
     <row r="240">
@@ -12639,10 +12639,10 @@
         <v>0.72</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4289</v>
+        <v>-0.2879</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.864699999999999</v>
+        <v>-6.6217</v>
       </c>
     </row>
     <row r="241">
@@ -12679,10 +12679,10 @@
         <v>0.57</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6403</v>
+        <v>-0.4289</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.7269</v>
+        <v>-9.864699999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12719,10 +12719,10 @@
         <v>1.33</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8822</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>26.466</v>
+        <v>26.235</v>
       </c>
     </row>
     <row r="243">
@@ -12759,10 +12759,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7428</v>
+        <v>0.7345</v>
       </c>
       <c r="J243" t="n">
-        <v>22.284</v>
+        <v>22.035</v>
       </c>
     </row>
     <row r="244">
@@ -12799,10 +12799,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.346</v>
+        <v>0.3927</v>
       </c>
       <c r="J244" t="n">
-        <v>10.38</v>
+        <v>11.781</v>
       </c>
     </row>
     <row r="245">
@@ -12839,10 +12839,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2267</v>
+        <v>0.2829</v>
       </c>
       <c r="J245" t="n">
-        <v>6.801</v>
+        <v>8.487</v>
       </c>
     </row>
     <row r="246">
@@ -12879,10 +12879,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1673</v>
+        <v>-0.0939</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.019</v>
+        <v>-2.817</v>
       </c>
     </row>
     <row r="247">
@@ -12919,10 +12919,10 @@
         <v>0.99</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0231</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>0.6929999999999999</v>
+        <v>-0.246</v>
       </c>
     </row>
     <row r="248">
@@ -12959,10 +12959,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0023</v>
+        <v>-0.0243</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.729</v>
       </c>
     </row>
     <row r="249">
@@ -12999,10 +12999,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0253</v>
+        <v>-0.0388</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.759</v>
+        <v>-1.164</v>
       </c>
     </row>
     <row r="250">
@@ -13039,10 +13039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3359</v>
+        <v>-0.2154</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.077</v>
+        <v>-6.462</v>
       </c>
     </row>
     <row r="251">
@@ -13079,10 +13079,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5099</v>
+        <v>-0.3321</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.297</v>
+        <v>-9.962999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -13119,10 +13119,10 @@
         <v>1.99</v>
       </c>
       <c r="I252" t="n">
-        <v>1.9372</v>
+        <v>1.641</v>
       </c>
       <c r="J252" t="n">
-        <v>34.8696</v>
+        <v>29.538</v>
       </c>
     </row>
     <row r="253">
@@ -13159,10 +13159,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2716</v>
+        <v>1.2154</v>
       </c>
       <c r="J253" t="n">
-        <v>22.8888</v>
+        <v>21.8772</v>
       </c>
     </row>
     <row r="254">
@@ -13199,10 +13199,10 @@
         <v>1.58</v>
       </c>
       <c r="I254" t="n">
-        <v>1.2083</v>
+        <v>1.1813</v>
       </c>
       <c r="J254" t="n">
-        <v>21.7494</v>
+        <v>21.2634</v>
       </c>
     </row>
     <row r="255">
@@ -13239,10 +13239,10 @@
         <v>1.46</v>
       </c>
       <c r="I255" t="n">
-        <v>0.9336</v>
+        <v>1.0412</v>
       </c>
       <c r="J255" t="n">
-        <v>16.8048</v>
+        <v>18.7416</v>
       </c>
     </row>
     <row r="256">
@@ -13279,10 +13279,10 @@
         <v>1.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.179</v>
+        <v>0.2815</v>
       </c>
       <c r="J256" t="n">
-        <v>3.222</v>
+        <v>5.067</v>
       </c>
     </row>
     <row r="257">
@@ -13319,10 +13319,10 @@
         <v>0.77</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.243</v>
+        <v>-0.2105</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.374</v>
+        <v>-3.789</v>
       </c>
     </row>
     <row r="258">
@@ -13359,10 +13359,10 @@
         <v>0.73</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.3051</v>
+        <v>-0.2528</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.4918</v>
+        <v>-4.5504</v>
       </c>
     </row>
     <row r="259">
@@ -13399,10 +13399,10 @@
         <v>0.64</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.45</v>
+        <v>-0.341</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.1</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="260">
@@ -13439,10 +13439,10 @@
         <v>0.51</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.6716</v>
+        <v>-0.459</v>
       </c>
       <c r="J260" t="n">
-        <v>-12.0888</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="261">
@@ -13479,10 +13479,10 @@
         <v>0.44</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7673</v>
+        <v>-0.5251</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.8114</v>
+        <v>-9.4518</v>
       </c>
     </row>
     <row r="262">
@@ -13519,10 +13519,10 @@
         <v>1.43</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0648</v>
+        <v>1.0443</v>
       </c>
       <c r="J262" t="n">
-        <v>27.6848</v>
+        <v>27.1518</v>
       </c>
     </row>
     <row r="263">
@@ -13559,10 +13559,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9135</v>
+        <v>0.9208</v>
       </c>
       <c r="J263" t="n">
-        <v>23.751</v>
+        <v>23.9408</v>
       </c>
     </row>
     <row r="264">
@@ -13599,10 +13599,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8911</v>
+        <v>0.899</v>
       </c>
       <c r="J264" t="n">
-        <v>23.1686</v>
+        <v>23.374</v>
       </c>
     </row>
     <row r="265">
@@ -13639,10 +13639,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6212</v>
+        <v>0.6489</v>
       </c>
       <c r="J265" t="n">
-        <v>16.1512</v>
+        <v>16.8714</v>
       </c>
     </row>
     <row r="266">
@@ -13679,10 +13679,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8287</v>
+        <v>-0.7832</v>
       </c>
       <c r="J266" t="n">
-        <v>-21.5462</v>
+        <v>-20.3632</v>
       </c>
     </row>
     <row r="267">
@@ -13719,10 +13719,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.593</v>
+        <v>0.7144</v>
       </c>
       <c r="J267" t="n">
-        <v>15.418</v>
+        <v>18.5744</v>
       </c>
     </row>
     <row r="268">
@@ -13759,10 +13759,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1466</v>
+        <v>0.145</v>
       </c>
       <c r="J268" t="n">
-        <v>3.8116</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="269">
@@ -13799,10 +13799,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1235</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.211</v>
+        <v>-1.9084</v>
       </c>
     </row>
     <row r="270">
@@ -13839,10 +13839,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1443</v>
+        <v>-0.0856</v>
       </c>
       <c r="J270" t="n">
-        <v>-3.7518</v>
+        <v>-2.2256</v>
       </c>
     </row>
     <row r="271">
@@ -13879,10 +13879,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6663</v>
+        <v>-0.4448</v>
       </c>
       <c r="J271" t="n">
-        <v>-17.3238</v>
+        <v>-11.5648</v>
       </c>
     </row>
     <row r="272">
@@ -13919,10 +13919,10 @@
         <v>1.99</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9426</v>
+        <v>1.6451</v>
       </c>
       <c r="J272" t="n">
-        <v>38.852</v>
+        <v>32.902</v>
       </c>
     </row>
     <row r="273">
@@ -13959,10 +13959,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4564</v>
+        <v>1.3203</v>
       </c>
       <c r="J273" t="n">
-        <v>29.128</v>
+        <v>26.406</v>
       </c>
     </row>
     <row r="274">
@@ -13999,10 +13999,10 @@
         <v>1.6</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2618</v>
+        <v>1.206</v>
       </c>
       <c r="J274" t="n">
-        <v>25.236</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="275">
@@ -14039,10 +14039,10 @@
         <v>1.41</v>
       </c>
       <c r="I275" t="n">
-        <v>0.8366</v>
+        <v>0.9659</v>
       </c>
       <c r="J275" t="n">
-        <v>16.732</v>
+        <v>19.318</v>
       </c>
     </row>
     <row r="276">
@@ -14079,10 +14079,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3754</v>
+        <v>-0.2884</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.508</v>
+        <v>-5.768</v>
       </c>
     </row>
     <row r="277">
@@ -14119,10 +14119,10 @@
         <v>0.82</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.159</v>
+        <v>-0.1515</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.18</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="278">
@@ -14159,10 +14159,10 @@
         <v>0.75</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2684</v>
+        <v>-0.2289</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.368</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="279">
@@ -14199,10 +14199,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3933</v>
+        <v>-0.3107</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.866</v>
+        <v>-6.214</v>
       </c>
     </row>
     <row r="280">
@@ -14239,10 +14239,10 @@
         <v>0.4</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.8167</v>
+        <v>-0.5614</v>
       </c>
       <c r="J280" t="n">
-        <v>-16.334</v>
+        <v>-11.228</v>
       </c>
     </row>
     <row r="281">
@@ -14279,10 +14279,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8167</v>
+        <v>-0.5614</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.334</v>
+        <v>-11.228</v>
       </c>
     </row>
     <row r="282">
@@ -14319,10 +14319,10 @@
         <v>0.78</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.2163</v>
+        <v>-0.193</v>
       </c>
       <c r="J282" t="n">
-        <v>-4.326</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="283">
@@ -14359,10 +14359,10 @@
         <v>0.66</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.4028</v>
+        <v>-0.3181</v>
       </c>
       <c r="J283" t="n">
-        <v>-8.055999999999999</v>
+        <v>-6.362</v>
       </c>
     </row>
     <row r="284">
@@ -14399,10 +14399,10 @@
         <v>0.65</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.4189</v>
+        <v>-0.3278</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.378</v>
+        <v>-6.556</v>
       </c>
     </row>
     <row r="285">
@@ -14439,10 +14439,10 @@
         <v>0.53</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6335</v>
+        <v>-0.4365</v>
       </c>
       <c r="J285" t="n">
-        <v>-12.67</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="286">
@@ -14479,10 +14479,10 @@
         <v>0.37</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8527</v>
+        <v>-0.5884</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.054</v>
+        <v>-11.768</v>
       </c>
     </row>
     <row r="287">
@@ -14519,10 +14519,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4033</v>
+        <v>1.2769</v>
       </c>
       <c r="J287" t="n">
-        <v>28.066</v>
+        <v>25.538</v>
       </c>
     </row>
     <row r="288">
@@ -14559,10 +14559,10 @@
         <v>1.47</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0375</v>
+        <v>1.0636</v>
       </c>
       <c r="J288" t="n">
-        <v>20.75</v>
+        <v>21.272</v>
       </c>
     </row>
     <row r="289">
@@ -14599,10 +14599,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0143</v>
+        <v>1.0513</v>
       </c>
       <c r="J289" t="n">
-        <v>20.286</v>
+        <v>21.026</v>
       </c>
     </row>
     <row r="290">
@@ -14639,10 +14639,10 @@
         <v>1.32</v>
       </c>
       <c r="I290" t="n">
-        <v>0.679</v>
+        <v>0.7934</v>
       </c>
       <c r="J290" t="n">
-        <v>13.58</v>
+        <v>15.868</v>
       </c>
     </row>
     <row r="291">
@@ -14679,10 +14679,10 @@
         <v>1.29</v>
       </c>
       <c r="I291" t="n">
-        <v>0.6116</v>
+        <v>0.7257</v>
       </c>
       <c r="J291" t="n">
-        <v>12.232</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="292">
@@ -14719,10 +14719,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5555</v>
+        <v>0.6651</v>
       </c>
       <c r="J292" t="n">
-        <v>16.665</v>
+        <v>19.953</v>
       </c>
     </row>
     <row r="293">
@@ -14759,10 +14759,10 @@
         <v>1.19</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3656</v>
+        <v>0.4172</v>
       </c>
       <c r="J293" t="n">
-        <v>10.968</v>
+        <v>12.516</v>
       </c>
     </row>
     <row r="294">
@@ -14799,10 +14799,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0464</v>
+        <v>-0.0213</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.392</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="295">
@@ -14839,10 +14839,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.231</v>
+        <v>-0.1354</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.93</v>
+        <v>-4.062</v>
       </c>
     </row>
     <row r="296">
@@ -14879,10 +14879,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5982</v>
+        <v>-0.3935</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.946</v>
+        <v>-11.805</v>
       </c>
     </row>
     <row r="297">
@@ -14919,10 +14919,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4028</v>
+        <v>1.2601</v>
       </c>
       <c r="J297" t="n">
-        <v>42.084</v>
+        <v>37.803</v>
       </c>
     </row>
     <row r="298">
@@ -14959,10 +14959,10 @@
         <v>1.25</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6474</v>
+        <v>0.6715</v>
       </c>
       <c r="J298" t="n">
-        <v>19.422</v>
+        <v>20.145</v>
       </c>
     </row>
     <row r="299">
@@ -14999,10 +14999,10 @@
         <v>1.19</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4687</v>
+        <v>0.5314</v>
       </c>
       <c r="J299" t="n">
-        <v>14.061</v>
+        <v>15.942</v>
       </c>
     </row>
     <row r="300">
@@ -15039,10 +15039,10 @@
         <v>1.11</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2506</v>
+        <v>0.3235</v>
       </c>
       <c r="J300" t="n">
-        <v>7.518</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="301">
@@ -15079,10 +15079,10 @@
         <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.134</v>
+        <v>-0.0561</v>
       </c>
       <c r="J301" t="n">
-        <v>-4.02</v>
+        <v>-1.683</v>
       </c>
     </row>
     <row r="302">
@@ -15119,10 +15119,10 @@
         <v>1.52</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2128</v>
+        <v>1.1445</v>
       </c>
       <c r="J302" t="n">
-        <v>30.32</v>
+        <v>28.6125</v>
       </c>
     </row>
     <row r="303">
@@ -15159,10 +15159,10 @@
         <v>1.34</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8238</v>
+        <v>0.8593</v>
       </c>
       <c r="J303" t="n">
-        <v>20.595</v>
+        <v>21.4825</v>
       </c>
     </row>
     <row r="304">
@@ -15199,10 +15199,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7128</v>
+        <v>0.7728</v>
       </c>
       <c r="J304" t="n">
-        <v>17.82</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="305">
@@ -15239,10 +15239,10 @@
         <v>1.21</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4802</v>
+        <v>0.5656</v>
       </c>
       <c r="J305" t="n">
-        <v>12.005</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="306">
@@ -15279,10 +15279,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3018</v>
+        <v>0.3882</v>
       </c>
       <c r="J306" t="n">
-        <v>7.545</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="307">
@@ -15319,10 +15319,10 @@
         <v>1.35</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6349</v>
+        <v>0.7749</v>
       </c>
       <c r="J307" t="n">
-        <v>15.8725</v>
+        <v>19.3725</v>
       </c>
     </row>
     <row r="308">
@@ -15359,10 +15359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3245</v>
+        <v>-0.212</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.112500000000001</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="309">
@@ -15399,10 +15399,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3721</v>
+        <v>-0.2416</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.3025</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="310">
@@ -15439,10 +15439,10 @@
         <v>0.73</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4464</v>
+        <v>-0.2901</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.16</v>
+        <v>-7.2525</v>
       </c>
     </row>
     <row r="311">
@@ -15479,10 +15479,10 @@
         <v>0.63</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5829</v>
+        <v>-0.385</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.5725</v>
+        <v>-9.625</v>
       </c>
     </row>
     <row r="312">
@@ -15519,10 +15519,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4725</v>
+        <v>0.5476</v>
       </c>
       <c r="J312" t="n">
-        <v>12.285</v>
+        <v>14.2376</v>
       </c>
     </row>
     <row r="313">
@@ -15559,10 +15559,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1392</v>
+        <v>0.1121</v>
       </c>
       <c r="J313" t="n">
-        <v>3.6192</v>
+        <v>2.9146</v>
       </c>
     </row>
     <row r="314">
@@ -15599,10 +15599,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3124</v>
+        <v>-0.2093</v>
       </c>
       <c r="J314" t="n">
-        <v>-8.122400000000001</v>
+        <v>-5.4418</v>
       </c>
     </row>
     <row r="315">
@@ -15639,10 +15639,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5772</v>
+        <v>-0.3817</v>
       </c>
       <c r="J315" t="n">
-        <v>-15.0072</v>
+        <v>-9.924200000000001</v>
       </c>
     </row>
     <row r="316">
@@ -15679,10 +15679,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7411</v>
+        <v>-0.502</v>
       </c>
       <c r="J316" t="n">
-        <v>-19.2686</v>
+        <v>-13.052</v>
       </c>
     </row>
     <row r="317">
@@ -15719,10 +15719,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5219</v>
+        <v>1.3395</v>
       </c>
       <c r="J317" t="n">
-        <v>39.5694</v>
+        <v>34.827</v>
       </c>
     </row>
     <row r="318">
@@ -15759,10 +15759,10 @@
         <v>1.49</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1746</v>
+        <v>1.1161</v>
       </c>
       <c r="J318" t="n">
-        <v>30.5396</v>
+        <v>29.0186</v>
       </c>
     </row>
     <row r="319">
@@ -15799,10 +15799,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.8056</v>
+        <v>0.8248</v>
       </c>
       <c r="J319" t="n">
-        <v>20.9456</v>
+        <v>21.4448</v>
       </c>
     </row>
     <row r="320">
@@ -15839,10 +15839,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0618</v>
+        <v>0.1387</v>
       </c>
       <c r="J320" t="n">
-        <v>1.6068</v>
+        <v>3.6062</v>
       </c>
     </row>
     <row r="321">
@@ -15879,10 +15879,10 @@
         <v>0.75</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8569</v>
+        <v>-0.8142</v>
       </c>
       <c r="J321" t="n">
-        <v>-22.2794</v>
+        <v>-21.1692</v>
       </c>
     </row>
     <row r="322">
@@ -15919,10 +15919,10 @@
         <v>0.9</v>
       </c>
       <c r="I322" t="n">
-        <v>0.0095</v>
+        <v>-0.0233</v>
       </c>
       <c r="J322" t="n">
-        <v>0.1805</v>
+        <v>-0.4427</v>
       </c>
     </row>
     <row r="323">
@@ -15959,10 +15959,10 @@
         <v>0.64</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.4008</v>
+        <v>-0.3243</v>
       </c>
       <c r="J323" t="n">
-        <v>-7.6152</v>
+        <v>-6.1617</v>
       </c>
     </row>
     <row r="324">
@@ -15999,10 +15999,10 @@
         <v>0.5</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.6509</v>
+        <v>-0.4543</v>
       </c>
       <c r="J324" t="n">
-        <v>-12.3671</v>
+        <v>-8.6317</v>
       </c>
     </row>
     <row r="325">
@@ -16039,10 +16039,10 @@
         <v>0.5</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.6509</v>
+        <v>-0.4543</v>
       </c>
       <c r="J325" t="n">
-        <v>-12.3671</v>
+        <v>-8.6317</v>
       </c>
     </row>
     <row r="326">
@@ -16079,10 +16079,10 @@
         <v>0.19</v>
       </c>
       <c r="I326" t="n">
-        <v>-1.0657</v>
+        <v>-0.7562</v>
       </c>
       <c r="J326" t="n">
-        <v>-20.2483</v>
+        <v>-14.3678</v>
       </c>
     </row>
     <row r="327">
@@ -16119,10 +16119,10 @@
         <v>2.38</v>
       </c>
       <c r="I327" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J327" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="328">
@@ -16159,10 +16159,10 @@
         <v>2.03</v>
       </c>
       <c r="I328" t="n">
-        <v>1.9643</v>
+        <v>1.6716</v>
       </c>
       <c r="J328" t="n">
-        <v>37.3217</v>
+        <v>31.7604</v>
       </c>
     </row>
     <row r="329">
@@ -16199,10 +16199,10 @@
         <v>1.56</v>
       </c>
       <c r="I329" t="n">
-        <v>1.1104</v>
+        <v>1.154</v>
       </c>
       <c r="J329" t="n">
-        <v>21.0976</v>
+        <v>21.926</v>
       </c>
     </row>
     <row r="330">
@@ -16239,10 +16239,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1904</v>
+        <v>0.296</v>
       </c>
       <c r="J330" t="n">
-        <v>3.6176</v>
+        <v>5.624</v>
       </c>
     </row>
     <row r="331">
@@ -16279,10 +16279,10 @@
         <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2242</v>
+        <v>-0.1364</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.2598</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="332">
@@ -16319,10 +16319,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9254</v>
+        <v>0.9271</v>
       </c>
       <c r="J332" t="n">
-        <v>27.762</v>
+        <v>27.813</v>
       </c>
     </row>
     <row r="333">
@@ -16359,10 +16359,10 @@
         <v>1.33</v>
       </c>
       <c r="I333" t="n">
-        <v>0.858</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J333" t="n">
-        <v>25.74</v>
+        <v>25.812</v>
       </c>
     </row>
     <row r="334">
@@ -16399,10 +16399,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6126</v>
+        <v>0.6294</v>
       </c>
       <c r="J334" t="n">
-        <v>18.378</v>
+        <v>18.882</v>
       </c>
     </row>
     <row r="335">
@@ -16439,10 +16439,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.262</v>
+        <v>0.329</v>
       </c>
       <c r="J335" t="n">
-        <v>7.86</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="336">
@@ -16479,10 +16479,10 @@
         <v>1</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1255</v>
+        <v>-0.0501</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.765</v>
+        <v>-1.503</v>
       </c>
     </row>
     <row r="337">
@@ -16519,10 +16519,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0044</v>
+        <v>-0.0307</v>
       </c>
       <c r="J337" t="n">
-        <v>-0.132</v>
+        <v>-0.921</v>
       </c>
     </row>
     <row r="338">
@@ -16559,10 +16559,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.968</v>
+        <v>-2.115</v>
       </c>
     </row>
     <row r="339">
@@ -16599,10 +16599,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1766</v>
+        <v>-0.1397</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.298</v>
+        <v>-4.191</v>
       </c>
     </row>
     <row r="340">
@@ -16639,10 +16639,10 @@
         <v>0.79</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.348</v>
+        <v>-0.2293</v>
       </c>
       <c r="J340" t="n">
-        <v>-10.44</v>
+        <v>-6.879</v>
       </c>
     </row>
     <row r="341">
@@ -16679,10 +16679,10 @@
         <v>0.62</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5913</v>
+        <v>-0.3916</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.739</v>
+        <v>-11.748</v>
       </c>
     </row>
     <row r="342">
@@ -16719,10 +16719,10 @@
         <v>1.81</v>
       </c>
       <c r="I342" t="n">
-        <v>1.8382</v>
+        <v>1.5563</v>
       </c>
       <c r="J342" t="n">
-        <v>51.4696</v>
+        <v>43.5764</v>
       </c>
     </row>
     <row r="343">
@@ -16759,10 +16759,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3901</v>
+        <v>0.3986</v>
       </c>
       <c r="J343" t="n">
-        <v>10.9228</v>
+        <v>11.1608</v>
       </c>
     </row>
     <row r="344">
@@ -16799,10 +16799,10 @@
         <v>1</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0916</v>
+        <v>-0.0291</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.5648</v>
+        <v>-0.8148</v>
       </c>
     </row>
     <row r="345">
@@ -16839,10 +16839,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4229</v>
+        <v>-0.3545</v>
       </c>
       <c r="J345" t="n">
-        <v>-11.8412</v>
+        <v>-9.926</v>
       </c>
     </row>
     <row r="346">
@@ -16879,10 +16879,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.7808</v>
+        <v>-0.733</v>
       </c>
       <c r="J346" t="n">
-        <v>-21.8624</v>
+        <v>-20.524</v>
       </c>
     </row>
     <row r="347">
@@ -16919,10 +16919,10 @@
         <v>1.18</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3572</v>
+        <v>0.4042</v>
       </c>
       <c r="J347" t="n">
-        <v>10.0016</v>
+        <v>11.3176</v>
       </c>
     </row>
     <row r="348">
@@ -16959,10 +16959,10 @@
         <v>1.14</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2964</v>
+        <v>0.328</v>
       </c>
       <c r="J348" t="n">
-        <v>8.299200000000001</v>
+        <v>9.183999999999999</v>
       </c>
     </row>
     <row r="349">
@@ -16999,10 +16999,10 @@
         <v>1.07</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1776</v>
+        <v>0.1854</v>
       </c>
       <c r="J349" t="n">
-        <v>4.9728</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="350">
@@ -17039,10 +17039,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3223</v>
+        <v>-0.1974</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.0244</v>
+        <v>-5.5272</v>
       </c>
     </row>
     <row r="351">
@@ -17079,10 +17079,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4791</v>
+        <v>-0.3067</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.4148</v>
+        <v>-8.5876</v>
       </c>
     </row>
     <row r="352">
@@ -17119,10 +17119,10 @@
         <v>1.34</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6479</v>
+        <v>0.7993</v>
       </c>
       <c r="J352" t="n">
-        <v>13.6059</v>
+        <v>16.7853</v>
       </c>
     </row>
     <row r="353">
@@ -17159,10 +17159,10 @@
         <v>0.77</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.3598</v>
+        <v>-0.2436</v>
       </c>
       <c r="J353" t="n">
-        <v>-7.5558</v>
+        <v>-5.1156</v>
       </c>
     </row>
     <row r="354">
@@ -17199,10 +17199,10 @@
         <v>0.77</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.3598</v>
+        <v>-0.2436</v>
       </c>
       <c r="J354" t="n">
-        <v>-7.5558</v>
+        <v>-5.1156</v>
       </c>
     </row>
     <row r="355">
@@ -17239,10 +17239,10 @@
         <v>0.66</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.526</v>
+        <v>-0.3481</v>
       </c>
       <c r="J355" t="n">
-        <v>-11.046</v>
+        <v>-7.3101</v>
       </c>
     </row>
     <row r="356">
@@ -17279,10 +17279,10 @@
         <v>0.45</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.7948</v>
+        <v>-0.543</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.6908</v>
+        <v>-11.403</v>
       </c>
     </row>
     <row r="357">
@@ -17319,10 +17319,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.5617</v>
+        <v>1.3747</v>
       </c>
       <c r="J357" t="n">
-        <v>32.7957</v>
+        <v>28.8687</v>
       </c>
     </row>
     <row r="358">
@@ -17359,10 +17359,10 @@
         <v>1.42</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9347</v>
+        <v>0.9978</v>
       </c>
       <c r="J358" t="n">
-        <v>19.6287</v>
+        <v>20.9538</v>
       </c>
     </row>
     <row r="359">
@@ -17399,10 +17399,10 @@
         <v>1.34</v>
       </c>
       <c r="I359" t="n">
-        <v>0.735</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>15.435</v>
+        <v>17.6862</v>
       </c>
     </row>
     <row r="360">
@@ -17439,10 +17439,10 @@
         <v>1.3</v>
       </c>
       <c r="I360" t="n">
-        <v>0.6439</v>
+        <v>0.7532</v>
       </c>
       <c r="J360" t="n">
-        <v>13.5219</v>
+        <v>15.8172</v>
       </c>
     </row>
     <row r="361">
@@ -17479,10 +17479,10 @@
         <v>1.28</v>
       </c>
       <c r="I361" t="n">
-        <v>0.5982</v>
+        <v>0.7076</v>
       </c>
       <c r="J361" t="n">
-        <v>12.5622</v>
+        <v>14.8596</v>
       </c>
     </row>
     <row r="362">
@@ -17519,10 +17519,10 @@
         <v>2.1</v>
       </c>
       <c r="I362" t="n">
-        <v>2.0241</v>
+        <v>1.7424</v>
       </c>
       <c r="J362" t="n">
-        <v>36.4338</v>
+        <v>31.3632</v>
       </c>
     </row>
     <row r="363">
@@ -17559,10 +17559,10 @@
         <v>1.98</v>
       </c>
       <c r="I363" t="n">
-        <v>1.8981</v>
+        <v>1.6134</v>
       </c>
       <c r="J363" t="n">
-        <v>34.1658</v>
+        <v>29.0412</v>
       </c>
     </row>
     <row r="364">
@@ -17599,10 +17599,10 @@
         <v>1.49</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9595</v>
+        <v>1.0692</v>
       </c>
       <c r="J364" t="n">
-        <v>17.271</v>
+        <v>19.2456</v>
       </c>
     </row>
     <row r="365">
@@ -17639,10 +17639,10 @@
         <v>1.44</v>
       </c>
       <c r="I365" t="n">
-        <v>0.8595</v>
+        <v>1.0007</v>
       </c>
       <c r="J365" t="n">
-        <v>15.471</v>
+        <v>18.0126</v>
       </c>
     </row>
     <row r="366">
@@ -17679,10 +17679,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.3751</v>
+        <v>0.4963</v>
       </c>
       <c r="J366" t="n">
-        <v>6.7518</v>
+        <v>8.933400000000001</v>
       </c>
     </row>
     <row r="367">
@@ -17719,10 +17719,10 @@
         <v>0.74</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.2272</v>
+        <v>-0.2031</v>
       </c>
       <c r="J367" t="n">
-        <v>-4.0896</v>
+        <v>-3.6558</v>
       </c>
     </row>
     <row r="368">
@@ -17759,10 +17759,10 @@
         <v>0.63</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.3951</v>
+        <v>-0.3241</v>
       </c>
       <c r="J368" t="n">
-        <v>-7.1118</v>
+        <v>-5.8338</v>
       </c>
     </row>
     <row r="369">
@@ -17799,10 +17799,10 @@
         <v>0.5</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.6268</v>
+        <v>-0.4482</v>
       </c>
       <c r="J369" t="n">
-        <v>-11.2824</v>
+        <v>-8.067600000000001</v>
       </c>
     </row>
     <row r="370">
@@ -17839,10 +17839,10 @@
         <v>0.39</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.7991</v>
+        <v>-0.5522</v>
       </c>
       <c r="J370" t="n">
-        <v>-14.3838</v>
+        <v>-9.9396</v>
       </c>
     </row>
     <row r="371">
@@ -17879,10 +17879,10 @@
         <v>0.31</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.9084</v>
+        <v>-0.6312</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.3512</v>
+        <v>-11.3616</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2306/event_2306_evp_summary.xlsx
+++ b/database/event/2306/event_2306_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3605</v>
+        <v>8.609400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5829</v>
+        <v>3.6896</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1363</v>
+        <v>3.295</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3605</v>
+        <v>8.609400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5039</v>
+        <v>2.4017</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8566</v>
+        <v>6.2077</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5039</v>
+        <v>2.5316</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7141</v>
+        <v>2.6638</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8566</v>
+        <v>6.2077</v>
       </c>
       <c r="K2" t="n">
         <v>131</v>
@@ -529,7 +529,7 @@
         <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5707</v>
+        <v>8.871500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8694</v>
+        <v>5.8932</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5154</v>
+        <v>2.5256</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0117</v>
+        <v>2.0585</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8694</v>
+        <v>5.8932</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5692</v>
+        <v>2.2547</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3002</v>
+        <v>3.6385</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5692</v>
+        <v>2.2547</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7849</v>
+        <v>2.3724</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3002</v>
+        <v>3.6385</v>
       </c>
       <c r="K3" t="n">
         <v>131</v>
@@ -575,7 +575,7 @@
         <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0851</v>
+        <v>6.010899999999999</v>
       </c>
       <c r="N3" t="n">
         <v>307</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7366</v>
+        <v>5.8536</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4585</v>
+        <v>2.5086</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9518</v>
+        <v>2.0405</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7366</v>
+        <v>5.8536</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3012</v>
+        <v>2.3763</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4354</v>
+        <v>3.4773</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3012</v>
+        <v>2.4761</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4944</v>
+        <v>2.6054</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4354</v>
+        <v>3.4773</v>
       </c>
       <c r="K4" t="n">
         <v>131</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9298</v>
+        <v>6.0827</v>
       </c>
       <c r="N4" t="n">
         <v>307</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8238</v>
+        <v>4.6735</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0673</v>
+        <v>2.0029</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5397</v>
+        <v>1.5033</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8238</v>
+        <v>4.6735</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9747</v>
+        <v>2.679</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8491</v>
+        <v>1.9945</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1722</v>
+        <v>3.1385</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3027</v>
+        <v>3.2194</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8491</v>
+        <v>1.9945</v>
       </c>
       <c r="K5" t="n">
         <v>134</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1518</v>
+        <v>5.2139</v>
       </c>
       <c r="N5" t="n">
         <v>270</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3801</v>
+        <v>4.3635</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8771</v>
+        <v>1.87</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3394</v>
+        <v>1.3622</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3801</v>
+        <v>4.3635</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9163</v>
+        <v>2.853</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4638</v>
+        <v>1.5105</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7889</v>
+        <v>4.519</v>
       </c>
       <c r="I6" t="n">
-        <v>2.49</v>
+        <v>2.4402</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4638</v>
+        <v>1.5105</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9538</v>
+        <v>3.9507</v>
       </c>
       <c r="N6" t="n">
         <v>269</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.163</v>
+        <v>4.1608</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7841</v>
+        <v>1.7831</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2414</v>
+        <v>1.2699</v>
       </c>
       <c r="E7" t="n">
-        <v>4.163</v>
+        <v>4.1608</v>
       </c>
       <c r="F7" t="n">
-        <v>3.462</v>
+        <v>3.382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.701</v>
+        <v>0.7788</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7117</v>
+        <v>6.2642</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4898</v>
+        <v>3.3826</v>
       </c>
       <c r="J7" t="n">
-        <v>0.701</v>
+        <v>0.7788</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>154</v>
       </c>
       <c r="M7" t="n">
-        <v>4.190799999999999</v>
+        <v>4.1614</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8042</v>
+        <v>3.819</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6303</v>
+        <v>1.6367</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0794</v>
+        <v>1.1143</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8042</v>
+        <v>3.819</v>
       </c>
       <c r="F8" t="n">
-        <v>2.972</v>
+        <v>2.9176</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.9014</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9852</v>
+        <v>4.7319</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5921</v>
+        <v>2.5552</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.9014</v>
       </c>
       <c r="K8" t="n">
         <v>115</v>
@@ -805,7 +805,7 @@
         <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4243</v>
+        <v>3.4566</v>
       </c>
       <c r="N8" t="n">
         <v>269</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.62</v>
+        <v>3.6161</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5514</v>
+        <v>1.5497</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9962</v>
+        <v>1.0219</v>
       </c>
       <c r="E9" t="n">
-        <v>3.62</v>
+        <v>3.6161</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0129</v>
+        <v>2.3707</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6071</v>
+        <v>1.2454</v>
       </c>
       <c r="H9" t="n">
-        <v>3.256</v>
+        <v>2.4639</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3899</v>
+        <v>2.5925</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6071</v>
+        <v>1.2454</v>
       </c>
       <c r="K9" t="n">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>3.997</v>
+        <v>3.8379</v>
       </c>
       <c r="N9" t="n">
-        <v>148</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5252</v>
+        <v>3.4433</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5107</v>
+        <v>1.4756</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9534</v>
+        <v>0.9433</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5252</v>
+        <v>3.4433</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4677</v>
+        <v>4.0548</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0575</v>
+        <v>-0.6115</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4677</v>
+        <v>8.484</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6749</v>
+        <v>4.5813</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0575</v>
+        <v>-0.6115</v>
       </c>
       <c r="K10" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="L10" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7324</v>
+        <v>3.9698</v>
       </c>
       <c r="N10" t="n">
-        <v>307</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4669</v>
+        <v>3.4329</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4858</v>
+        <v>1.4712</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9271</v>
+        <v>0.9385</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4669</v>
+        <v>3.4329</v>
       </c>
       <c r="F11" t="n">
-        <v>4.084</v>
+        <v>2.485</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6171</v>
+        <v>0.9479</v>
       </c>
       <c r="H11" t="n">
-        <v>8.9032</v>
+        <v>3.3047</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6292</v>
+        <v>1.7845</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6171</v>
+        <v>0.9479</v>
       </c>
       <c r="K11" t="n">
         <v>115</v>
@@ -943,7 +943,7 @@
         <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0121</v>
+        <v>2.7324</v>
       </c>
       <c r="N11" t="n">
         <v>269</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3829</v>
+        <v>3.3958</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4498</v>
+        <v>1.4553</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8892</v>
+        <v>0.9216</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3829</v>
+        <v>3.3958</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7576</v>
+        <v>2.7408</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3747</v>
+        <v>0.655</v>
       </c>
       <c r="H12" t="n">
-        <v>7.7533</v>
+        <v>3.2737</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0313</v>
+        <v>3.3581</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3747</v>
+        <v>0.655</v>
       </c>
       <c r="K12" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6566</v>
+        <v>4.0131</v>
       </c>
       <c r="N12" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3455</v>
+        <v>3.3104</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4337</v>
+        <v>1.4187</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8723</v>
+        <v>0.8828</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3455</v>
+        <v>3.3104</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5512</v>
+        <v>3.7152</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7943</v>
+        <v>-0.4048</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5024</v>
+        <v>7.3636</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8211</v>
+        <v>3.9763</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7943</v>
+        <v>-0.4048</v>
       </c>
       <c r="K13" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L13" t="n">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6154</v>
+        <v>3.5715</v>
       </c>
       <c r="N13" t="n">
-        <v>269</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0572</v>
+        <v>3.2043</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3102</v>
+        <v>1.3732</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7422</v>
+        <v>0.8345</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0572</v>
+        <v>3.2043</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0572</v>
+        <v>0.7765</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.4278</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3533</v>
+        <v>0.7765</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3533</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.4278</v>
       </c>
       <c r="K14" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3533</v>
+        <v>3.2448</v>
       </c>
       <c r="N14" t="n">
-        <v>124</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9218</v>
+        <v>2.8381</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2522</v>
+        <v>1.2163</v>
       </c>
       <c r="D15" t="n">
-        <v>0.681</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9218</v>
+        <v>2.8381</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7747000000000001</v>
+        <v>2.8381</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1471</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7747000000000001</v>
+        <v>3.4868</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8397</v>
+        <v>3.4868</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1471</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="L15" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9868</v>
+        <v>3.4868</v>
       </c>
       <c r="N15" t="n">
-        <v>307</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9209</v>
+        <v>2.8248</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2518</v>
+        <v>1.2106</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6806</v>
+        <v>0.6617</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9209</v>
+        <v>2.8248</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6452</v>
+        <v>2.561</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2757</v>
+        <v>0.2638</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8338</v>
+        <v>3.5554</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9934</v>
+        <v>1.9199</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2757</v>
+        <v>0.2638</v>
       </c>
       <c r="K16" t="n">
         <v>109</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2691</v>
+        <v>2.1837</v>
       </c>
       <c r="N16" t="n">
         <v>160</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8917</v>
+        <v>2.8145</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2393</v>
+        <v>1.2062</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6674</v>
+        <v>0.657</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8917</v>
+        <v>2.8145</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6145</v>
+        <v>2.5173</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2772</v>
+        <v>0.2972</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7257</v>
+        <v>3.4113</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9372</v>
+        <v>1.8421</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2772</v>
+        <v>0.2972</v>
       </c>
       <c r="K17" t="n">
         <v>109</v>
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2144</v>
+        <v>2.1393</v>
       </c>
       <c r="N17" t="n">
         <v>160</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6681</v>
+        <v>2.4974</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1434</v>
+        <v>1.0703</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5665</v>
+        <v>0.5127</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6681</v>
+        <v>2.4974</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0156</v>
+        <v>2.1804</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3475</v>
+        <v>0.317</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2619</v>
+        <v>2.2999</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3961</v>
+        <v>1.2419</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3475</v>
+        <v>0.317</v>
       </c>
       <c r="K18" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0486</v>
+        <v>1.5589</v>
       </c>
       <c r="N18" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5771</v>
+        <v>2.3405</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1044</v>
+        <v>1.003</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5254</v>
+        <v>0.4412</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5771</v>
+        <v>2.3405</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8429</v>
+        <v>2.7139</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2658</v>
+        <v>-0.3734</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8827</v>
+        <v>3.215</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8827</v>
+        <v>3.2978</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2658</v>
+        <v>-0.3734</v>
       </c>
       <c r="K19" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6169</v>
+        <v>2.9244</v>
       </c>
       <c r="N19" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4983</v>
+        <v>2.2901</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0707</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4898</v>
+        <v>0.4183</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4983</v>
+        <v>2.2901</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2265</v>
+        <v>2.571</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2718</v>
+        <v>-0.2809</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3585</v>
+        <v>2.9021</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2263</v>
+        <v>2.9021</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2718</v>
+        <v>-0.2809</v>
       </c>
       <c r="K20" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4981</v>
+        <v>2.6212</v>
       </c>
       <c r="N20" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.125</v>
+        <v>1.9212</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9107</v>
+        <v>0.8233</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3213</v>
+        <v>0.2504</v>
       </c>
       <c r="E21" t="n">
-        <v>2.125</v>
+        <v>1.9212</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5329</v>
+        <v>2.3545</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4079</v>
+        <v>-0.4333</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5329</v>
+        <v>2.4282</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6371</v>
+        <v>2.4908</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4079</v>
+        <v>-0.4333</v>
       </c>
       <c r="K21" t="n">
         <v>87</v>
@@ -1403,7 +1403,7 @@
         <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>2.2292</v>
+        <v>2.0575</v>
       </c>
       <c r="N21" t="n">
         <v>148</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9015</v>
+        <v>1.8115</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8149</v>
+        <v>0.7763</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2204</v>
+        <v>0.2004</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9015</v>
+        <v>1.8115</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9015</v>
+        <v>1.7161</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9015</v>
+        <v>1.7161</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9015</v>
+        <v>1.7603</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="K22" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9015</v>
+        <v>1.8557</v>
       </c>
       <c r="N22" t="n">
-        <v>101</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.803</v>
+        <v>1.7559</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.176</v>
+        <v>0.1751</v>
       </c>
       <c r="E23" t="n">
-        <v>1.803</v>
+        <v>1.7559</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7644</v>
+        <v>1.7559</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7644</v>
+        <v>1.7559</v>
       </c>
       <c r="I23" t="n">
-        <v>1.837</v>
+        <v>1.7559</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="L23" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8756</v>
+        <v>1.7559</v>
       </c>
       <c r="N23" t="n">
-        <v>270</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7849</v>
+        <v>1.7486</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7649</v>
+        <v>0.7494</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1678</v>
+        <v>0.1718</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7849</v>
+        <v>1.7486</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9776</v>
+        <v>1.9546</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1927</v>
+        <v>-0.206</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9776</v>
+        <v>1.9546</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9776</v>
+        <v>1.9546</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1927</v>
+        <v>-0.206</v>
       </c>
       <c r="K24" t="n">
         <v>85</v>
@@ -1541,7 +1541,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7849</v>
+        <v>1.7486</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7312</v>
+        <v>1.7041</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7419</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1435</v>
+        <v>0.1515</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7312</v>
+        <v>1.7041</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5229</v>
+        <v>1.5009</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2083</v>
+        <v>0.2032</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5229</v>
+        <v>1.5009</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5855</v>
+        <v>1.5396</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2083</v>
+        <v>0.2032</v>
       </c>
       <c r="K25" t="n">
         <v>87</v>
@@ -1587,7 +1587,7 @@
         <v>61</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7938</v>
+        <v>1.7428</v>
       </c>
       <c r="N25" t="n">
         <v>148</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7285</v>
+        <v>1.5816</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7408</v>
+        <v>0.6778</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1423</v>
+        <v>0.0958</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7285</v>
+        <v>1.5816</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7296</v>
+        <v>1.6246</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0011</v>
+        <v>-0.043</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7296</v>
+        <v>1.6246</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7296</v>
+        <v>1.6246</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0011</v>
+        <v>-0.043</v>
       </c>
       <c r="K26" t="n">
         <v>85</v>
@@ -1633,7 +1633,7 @@
         <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7285</v>
+        <v>1.5816</v>
       </c>
       <c r="N26" t="n">
         <v>131</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7048</v>
+        <v>0.651</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1045</v>
+        <v>0.0673</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6447</v>
+        <v>1.5191</v>
       </c>
       <c r="N27" t="n">
         <v>101</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5254</v>
+        <v>1.4636</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6272</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0506</v>
+        <v>0.0421</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5254</v>
+        <v>1.4636</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2281</v>
+        <v>1.1411</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2973</v>
+        <v>0.3225</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2281</v>
+        <v>1.1411</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2786</v>
+        <v>1.1705</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2973</v>
+        <v>0.3225</v>
       </c>
       <c r="K28" t="n">
         <v>134</v>
@@ -1725,7 +1725,7 @@
         <v>136</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5759</v>
+        <v>1.493</v>
       </c>
       <c r="N28" t="n">
         <v>270</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2842</v>
+        <v>1.2655</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5504</v>
+        <v>0.5423</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0583</v>
+        <v>-0.0481</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2842</v>
+        <v>1.2655</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3993</v>
+        <v>1.3948</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1151</v>
+        <v>-0.1293</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3993</v>
+        <v>1.3948</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4569</v>
+        <v>1.4307</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1151</v>
+        <v>-0.1293</v>
       </c>
       <c r="K29" t="n">
         <v>87</v>
@@ -1771,7 +1771,7 @@
         <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3418</v>
+        <v>1.3014</v>
       </c>
       <c r="N29" t="n">
         <v>148</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2811</v>
+        <v>1.2362</v>
       </c>
       <c r="C30" t="n">
-        <v>0.549</v>
+        <v>0.5298</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0597</v>
+        <v>-0.0615</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2811</v>
+        <v>1.2362</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2811</v>
+        <v>0.5224</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.7138</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2811</v>
+        <v>0.5224</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2811</v>
+        <v>0.5359</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7138</v>
       </c>
       <c r="K30" t="n">
+        <v>134</v>
+      </c>
+      <c r="L30" t="n">
         <v>136</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
-        <v>1.2811</v>
+        <v>1.2497</v>
       </c>
       <c r="N30" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2579</v>
+        <v>1.2093</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5391</v>
+        <v>0.5183</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0701</v>
+        <v>-0.0737</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2579</v>
+        <v>1.2093</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2748</v>
+        <v>1.2416</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0169</v>
+        <v>-0.0323</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2748</v>
+        <v>1.2416</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2748</v>
+        <v>1.2416</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0169</v>
+        <v>-0.0323</v>
       </c>
       <c r="K31" t="n">
         <v>85</v>
@@ -1863,7 +1863,7 @@
         <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2579</v>
+        <v>1.2093</v>
       </c>
       <c r="N31" t="n">
         <v>131</v>
@@ -1872,231 +1872,231 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1455</v>
+        <v>1.1613</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4909</v>
+        <v>0.4977</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1209</v>
+        <v>-0.0956</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1455</v>
+        <v>1.1613</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5117</v>
+        <v>1.1613</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6338</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5117</v>
+        <v>1.1613</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5327</v>
+        <v>1.1613</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6338</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.1613</v>
+      </c>
+      <c r="N32" t="n">
         <v>136</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.1665</v>
-      </c>
-      <c r="N32" t="n">
-        <v>270</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0542</v>
+        <v>1.0384</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4518</v>
+        <v>0.445</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1621</v>
+        <v>-0.1515</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0542</v>
+        <v>1.0384</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0542</v>
+        <v>0.7123</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.3261</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0542</v>
+        <v>0.7123</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0542</v>
+        <v>0.7307</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.3261</v>
       </c>
       <c r="K33" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0542</v>
+        <v>1.0568</v>
       </c>
       <c r="N33" t="n">
-        <v>124</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.035</v>
+        <v>0.9563</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4436</v>
+        <v>0.4098</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1708</v>
+        <v>-0.1889</v>
       </c>
       <c r="E34" t="n">
-        <v>1.035</v>
+        <v>0.9563</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8938</v>
+        <v>0.9563</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8588</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8938</v>
+        <v>0.9563</v>
       </c>
       <c r="I34" t="n">
-        <v>1.8938</v>
+        <v>0.9563</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8588</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="L34" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.035</v>
+        <v>0.9563</v>
       </c>
       <c r="N34" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0227</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4383</v>
+        <v>0.4097</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1763</v>
+        <v>-0.189</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0227</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7301</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2926</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7301</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7601</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2926</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L35" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0527</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>270</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9337</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4001</v>
+        <v>0.3977</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2165</v>
+        <v>-0.2018</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9337</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9337</v>
+        <v>1.8005</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.8726</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9337</v>
+        <v>1.8005</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9337</v>
+        <v>1.8005</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.8726</v>
       </c>
       <c r="K36" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9337</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3055</v>
+        <v>0.2829</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3162</v>
+        <v>-0.3237</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7129</v>
+        <v>0.6601</v>
       </c>
       <c r="N37" t="n">
         <v>136</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2534</v>
+        <v>0.2318</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.371</v>
+        <v>-0.3779</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5914</v>
+        <v>0.541</v>
       </c>
       <c r="N38" t="n">
         <v>136</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0788</v>
+        <v>0.0369</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.555</v>
+        <v>-0.5851</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1838</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>142</v>
@@ -2240,139 +2240,139 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0228</v>
+        <v>0.0043</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.614</v>
+        <v>-0.6197</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0531</v>
+        <v>0.01</v>
       </c>
       <c r="N40" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0066</v>
+        <v>-0.018</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.631</v>
+        <v>-0.6433</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0155</v>
+        <v>-0.0419</v>
       </c>
       <c r="N41" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0007</v>
+        <v>-0.02</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6372</v>
+        <v>-0.6455</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0017</v>
+        <v>-0.0467</v>
       </c>
       <c r="N42" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0978</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7123</v>
+        <v>-0.7281</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1646</v>
+        <v>-0.2282</v>
       </c>
       <c r="N43" t="n">
         <v>96</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1552</v>
+        <v>-0.1465</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.8015</v>
+        <v>-0.7798</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3622</v>
+        <v>-0.3419</v>
       </c>
       <c r="N44" t="n">
         <v>124</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2022</v>
+        <v>-0.2303</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8511</v>
+        <v>-0.8689</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4719</v>
+        <v>-0.5375</v>
       </c>
       <c r="N45" t="n">
         <v>142</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2473</v>
+        <v>-0.2605</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.8985</v>
+        <v>-0.9009</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6078</v>
       </c>
       <c r="N46" t="n">
         <v>136</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2894</v>
+        <v>-0.3102</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9429</v>
+        <v>-0.9537</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6753</v>
+        <v>-0.7239</v>
       </c>
       <c r="N47" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2972</v>
+        <v>-0.3117</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.951</v>
+        <v>-0.9553</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6934</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3629</v>
+        <v>-0.366</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.0203</v>
+        <v>-1.013</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8468</v>
+        <v>-0.8541</v>
       </c>
       <c r="N49" t="n">
         <v>101</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.372</v>
+        <v>-0.3806</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.0299</v>
+        <v>-1.0285</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8681</v>
+        <v>-0.8882</v>
       </c>
       <c r="N50" t="n">
         <v>96</v>
@@ -2746,139 +2746,139 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4215</v>
+        <v>-0.4425</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.082</v>
+        <v>-1.0942</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.9835</v>
+        <v>-1.0325</v>
       </c>
       <c r="N51" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4245</v>
+        <v>-0.4517</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0852</v>
+        <v>-1.104</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.9905</v>
+        <v>-1.0539</v>
       </c>
       <c r="N52" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4406</v>
+        <v>-0.453</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.1021</v>
+        <v>-1.1054</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.028</v>
+        <v>-1.0571</v>
       </c>
       <c r="N53" t="n">
-        <v>101</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6408</v>
+        <v>-0.6531</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.313</v>
+        <v>-1.3179</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.4952</v>
+        <v>-1.5239</v>
       </c>
       <c r="N54" t="n">
         <v>142</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.3818</v>
+        <v>-2.1591</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.0207</v>
+        <v>-0.9253</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.7133</v>
+        <v>-1.6071</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.3818</v>
+        <v>-2.1591</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.5244</v>
+        <v>-1.2876</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.5244</v>
+        <v>-1.2876</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7926</v>
+        <v>-0.6953</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="K55" t="n">
         <v>109</v>
@@ -2967,7 +2967,7 @@
         <v>51</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.65</v>
+        <v>-1.5668</v>
       </c>
       <c r="N55" t="n">
         <v>160</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.0284</v>
+        <v>-1.0044</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.7214</v>
+        <v>-1.6911</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-2.3997</v>
+        <v>-2.3438</v>
       </c>
       <c r="N56" t="n">
         <v>101</v>
@@ -3119,10 +3119,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5618</v>
+        <v>0.5647</v>
       </c>
       <c r="J2" t="n">
-        <v>20.2248</v>
+        <v>20.3292</v>
       </c>
     </row>
     <row r="3">
@@ -3159,10 +3159,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3751</v>
+        <v>0.3878</v>
       </c>
       <c r="J3" t="n">
-        <v>13.5036</v>
+        <v>13.9608</v>
       </c>
     </row>
     <row r="4">
@@ -3199,10 +3199,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1604</v>
+        <v>0.1764</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7744</v>
+        <v>6.3504</v>
       </c>
     </row>
     <row r="5">
@@ -3239,10 +3239,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1251</v>
+        <v>-0.1341</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.5036</v>
+        <v>-4.8276</v>
       </c>
     </row>
     <row r="6">
@@ -3279,10 +3279,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1366</v>
+        <v>-0.146</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.9176</v>
+        <v>-5.256</v>
       </c>
     </row>
     <row r="7">
@@ -3319,10 +3319,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2662</v>
+        <v>0.2728</v>
       </c>
       <c r="J7" t="n">
-        <v>9.5832</v>
+        <v>9.8208</v>
       </c>
     </row>
     <row r="8">
@@ -3359,10 +3359,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03</v>
+        <v>0.0348</v>
       </c>
       <c r="J8" t="n">
-        <v>1.08</v>
+        <v>1.2528</v>
       </c>
     </row>
     <row r="9">
@@ -3399,10 +3399,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2428</v>
+        <v>-2.5848</v>
       </c>
     </row>
     <row r="10">
@@ -3439,10 +3439,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0871</v>
+        <v>-0.0982</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.1356</v>
+        <v>-3.5352</v>
       </c>
     </row>
     <row r="11">
@@ -3479,10 +3479,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1441</v>
+        <v>-0.1574</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.1876</v>
+        <v>-5.6664</v>
       </c>
     </row>
     <row r="12">
@@ -3519,10 +3519,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1846</v>
+        <v>-0.206</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0612</v>
+        <v>-4.532</v>
       </c>
     </row>
     <row r="13">
@@ -3559,10 +3559,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1846</v>
+        <v>-0.206</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.0612</v>
+        <v>-4.532</v>
       </c>
     </row>
     <row r="14">
@@ -3599,10 +3599,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2256</v>
+        <v>-0.2464</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.9632</v>
+        <v>-5.4208</v>
       </c>
     </row>
     <row r="15">
@@ -3639,10 +3639,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3094</v>
+        <v>-0.3286</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.8068</v>
+        <v>-7.2292</v>
       </c>
     </row>
     <row r="16">
@@ -3679,10 +3679,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4682</v>
+        <v>-0.4797</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.3004</v>
+        <v>-10.5534</v>
       </c>
     </row>
     <row r="17">
@@ -3719,10 +3719,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0908</v>
+        <v>1.0727</v>
       </c>
       <c r="J17" t="n">
-        <v>23.9976</v>
+        <v>23.5994</v>
       </c>
     </row>
     <row r="18">
@@ -3759,10 +3759,10 @@
         <v>1.47</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0784</v>
+        <v>1.0545</v>
       </c>
       <c r="J18" t="n">
-        <v>23.7248</v>
+        <v>23.199</v>
       </c>
     </row>
     <row r="19">
@@ -3799,10 +3799,10 @@
         <v>1.44</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0397</v>
+        <v>0.9996</v>
       </c>
       <c r="J19" t="n">
-        <v>22.8734</v>
+        <v>21.9912</v>
       </c>
     </row>
     <row r="20">
@@ -3839,10 +3839,10 @@
         <v>1.15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4096</v>
+        <v>0.4146</v>
       </c>
       <c r="J20" t="n">
-        <v>9.011200000000001</v>
+        <v>9.1212</v>
       </c>
     </row>
     <row r="21">
@@ -3879,10 +3879,10 @@
         <v>1.08</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2155</v>
+        <v>0.2363</v>
       </c>
       <c r="J21" t="n">
-        <v>4.741</v>
+        <v>5.1986</v>
       </c>
     </row>
     <row r="22">
@@ -3919,10 +3919,10 @@
         <v>0.84</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1619</v>
+        <v>-0.1838</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3999</v>
+        <v>-3.8598</v>
       </c>
     </row>
     <row r="23">
@@ -3959,10 +3959,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1727</v>
+        <v>-0.1945</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6267</v>
+        <v>-4.0845</v>
       </c>
     </row>
     <row r="24">
@@ -3999,10 +3999,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2346</v>
+        <v>-0.2554</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.9266</v>
+        <v>-5.3634</v>
       </c>
     </row>
     <row r="25">
@@ -4039,10 +4039,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2995</v>
+        <v>-0.319</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.2895</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="26">
@@ -4079,10 +4079,10 @@
         <v>0.46</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5232</v>
+        <v>-0.5314</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.9872</v>
+        <v>-11.1594</v>
       </c>
     </row>
     <row r="27">
@@ -4119,10 +4119,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2468</v>
+        <v>1.3032</v>
       </c>
       <c r="J27" t="n">
-        <v>26.1828</v>
+        <v>27.3672</v>
       </c>
     </row>
     <row r="28">
@@ -4159,10 +4159,10 @@
         <v>1.59</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2111</v>
+        <v>1.2516</v>
       </c>
       <c r="J28" t="n">
-        <v>25.4331</v>
+        <v>26.2836</v>
       </c>
     </row>
     <row r="29">
@@ -4199,10 +4199,10 @@
         <v>1.48</v>
       </c>
       <c r="I29" t="n">
-        <v>1.079</v>
+        <v>1.0589</v>
       </c>
       <c r="J29" t="n">
-        <v>22.659</v>
+        <v>22.2369</v>
       </c>
     </row>
     <row r="30">
@@ -4239,10 +4239,10 @@
         <v>1.32</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7996</v>
+        <v>0.766</v>
       </c>
       <c r="J30" t="n">
-        <v>16.7916</v>
+        <v>16.086</v>
       </c>
     </row>
     <row r="31">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0003</v>
+        <v>0.0342</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0063</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -4319,10 +4319,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.418</v>
+        <v>0.452</v>
       </c>
       <c r="J32" t="n">
-        <v>10.45</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="33">
@@ -4359,10 +4359,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2933</v>
+        <v>0.2868</v>
       </c>
       <c r="J33" t="n">
-        <v>7.3325</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="34">
@@ -4399,10 +4399,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1205</v>
+        <v>-0.1364</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.0125</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="35">
@@ -4439,10 +4439,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2901</v>
+        <v>-0.3062</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.2525</v>
+        <v>-7.655</v>
       </c>
     </row>
     <row r="36">
@@ -4479,10 +4479,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6132</v>
+        <v>-0.6129</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.33</v>
+        <v>-15.3225</v>
       </c>
     </row>
     <row r="37">
@@ -4519,10 +4519,10 @@
         <v>1.73</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1299</v>
+        <v>1.24</v>
       </c>
       <c r="J37" t="n">
-        <v>28.2475</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -4559,10 +4559,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7094</v>
+        <v>0.7892</v>
       </c>
       <c r="J38" t="n">
-        <v>17.735</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="39">
@@ -4599,10 +4599,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5142</v>
+        <v>0.5727</v>
       </c>
       <c r="J39" t="n">
-        <v>12.855</v>
+        <v>14.3175</v>
       </c>
     </row>
     <row r="40">
@@ -4639,10 +4639,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3986</v>
+        <v>0.4402</v>
       </c>
       <c r="J40" t="n">
-        <v>9.965</v>
+        <v>11.005</v>
       </c>
     </row>
     <row r="41">
@@ -4679,10 +4679,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3655</v>
+        <v>-0.3404</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.137499999999999</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="42">
@@ -4719,10 +4719,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5619</v>
+        <v>0.6232</v>
       </c>
       <c r="J42" t="n">
-        <v>14.6094</v>
+        <v>16.2032</v>
       </c>
     </row>
     <row r="43">
@@ -4759,10 +4759,10 @@
         <v>0.99</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0176</v>
+        <v>-0.023</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4576</v>
+        <v>-0.598</v>
       </c>
     </row>
     <row r="44">
@@ -4799,10 +4799,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1408</v>
+        <v>-0.1548</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.6608</v>
+        <v>-4.0248</v>
       </c>
     </row>
     <row r="45">
@@ -4839,10 +4839,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2442</v>
+        <v>-0.2586</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.3492</v>
+        <v>-6.7236</v>
       </c>
     </row>
     <row r="46">
@@ -4879,10 +4879,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2542</v>
+        <v>-0.2684</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.6092</v>
+        <v>-6.9784</v>
       </c>
     </row>
     <row r="47">
@@ -4919,10 +4919,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9866</v>
+        <v>1.0763</v>
       </c>
       <c r="J47" t="n">
-        <v>25.6516</v>
+        <v>27.9838</v>
       </c>
     </row>
     <row r="48">
@@ -4959,10 +4959,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4573</v>
+        <v>0.501</v>
       </c>
       <c r="J48" t="n">
-        <v>11.8898</v>
+        <v>13.026</v>
       </c>
     </row>
     <row r="49">
@@ -4999,10 +4999,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3385</v>
+        <v>-0.3282</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.801</v>
+        <v>-8.533200000000001</v>
       </c>
     </row>
     <row r="50">
@@ -5039,10 +5039,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5077</v>
+        <v>-0.4824</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.2002</v>
+        <v>-12.5424</v>
       </c>
     </row>
     <row r="51">
@@ -5079,10 +5079,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5615</v>
+        <v>-0.5306</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.599</v>
+        <v>-13.7956</v>
       </c>
     </row>
     <row r="52">
@@ -5119,10 +5119,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2844</v>
+        <v>0.2864</v>
       </c>
       <c r="J52" t="n">
-        <v>7.3944</v>
+        <v>7.4464</v>
       </c>
     </row>
     <row r="53">
@@ -5159,10 +5159,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2539</v>
+        <v>0.2571</v>
       </c>
       <c r="J53" t="n">
-        <v>6.6014</v>
+        <v>6.6846</v>
       </c>
     </row>
     <row r="54">
@@ -5199,10 +5199,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1366</v>
+        <v>-0.1515</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.5516</v>
+        <v>-3.939</v>
       </c>
     </row>
     <row r="55">
@@ -5239,10 +5239,10 @@
         <v>0.75</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2786</v>
+        <v>-0.2934</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.2436</v>
+        <v>-7.6284</v>
       </c>
     </row>
     <row r="56">
@@ -5279,10 +5279,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3457</v>
+        <v>-0.3586</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.988200000000001</v>
+        <v>-9.323600000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5319,10 +5319,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3694</v>
+        <v>0.4066</v>
       </c>
       <c r="J57" t="n">
-        <v>9.6044</v>
+        <v>10.5716</v>
       </c>
     </row>
     <row r="58">
@@ -5359,10 +5359,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2856</v>
+        <v>0.302</v>
       </c>
       <c r="J58" t="n">
-        <v>7.4256</v>
+        <v>7.852</v>
       </c>
     </row>
     <row r="59">
@@ -5399,10 +5399,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2486</v>
+        <v>0.2655</v>
       </c>
       <c r="J59" t="n">
-        <v>6.4636</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="60">
@@ -5439,10 +5439,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1847</v>
+        <v>0.2017</v>
       </c>
       <c r="J60" t="n">
-        <v>4.8022</v>
+        <v>5.2442</v>
       </c>
     </row>
     <row r="61">
@@ -5479,10 +5479,10 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0144</v>
+        <v>-0.0111</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.3744</v>
+        <v>-0.2886</v>
       </c>
     </row>
     <row r="62">
@@ -5519,10 +5519,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8317</v>
+        <v>0.9228</v>
       </c>
       <c r="J62" t="n">
-        <v>19.1291</v>
+        <v>21.2244</v>
       </c>
     </row>
     <row r="63">
@@ -5559,10 +5559,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6933</v>
+        <v>0.7723</v>
       </c>
       <c r="J63" t="n">
-        <v>15.9459</v>
+        <v>17.7629</v>
       </c>
     </row>
     <row r="64">
@@ -5599,10 +5599,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6551</v>
+        <v>0.7304</v>
       </c>
       <c r="J64" t="n">
-        <v>15.0673</v>
+        <v>16.7992</v>
       </c>
     </row>
     <row r="65">
@@ -5639,10 +5639,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4106</v>
+        <v>0.4562</v>
       </c>
       <c r="J65" t="n">
-        <v>9.4438</v>
+        <v>10.4926</v>
       </c>
     </row>
     <row r="66">
@@ -5679,10 +5679,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4106</v>
+        <v>0.4562</v>
       </c>
       <c r="J66" t="n">
-        <v>9.4438</v>
+        <v>10.4926</v>
       </c>
     </row>
     <row r="67">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1687</v>
+        <v>0.163</v>
       </c>
       <c r="J67" t="n">
-        <v>3.8801</v>
+        <v>3.749</v>
       </c>
     </row>
     <row r="68">
@@ -5759,10 +5759,10 @@
         <v>1.02</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1153</v>
+        <v>0.1092</v>
       </c>
       <c r="J68" t="n">
-        <v>2.6519</v>
+        <v>2.5116</v>
       </c>
     </row>
     <row r="69">
@@ -5799,10 +5799,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1381</v>
+        <v>-0.1555</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.1763</v>
+        <v>-3.5765</v>
       </c>
     </row>
     <row r="70">
@@ -5839,10 +5839,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2279</v>
+        <v>-0.2459</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.2417</v>
+        <v>-5.6557</v>
       </c>
     </row>
     <row r="71">
@@ -5879,10 +5879,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5829</v>
+        <v>-0.5851</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.4067</v>
+        <v>-13.4573</v>
       </c>
     </row>
     <row r="72">
@@ -5919,10 +5919,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0696</v>
       </c>
       <c r="J72" t="n">
-        <v>25.2538</v>
+        <v>27.8096</v>
       </c>
     </row>
     <row r="73">
@@ -5959,10 +5959,10 @@
         <v>1.36</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6781</v>
+        <v>0.7532</v>
       </c>
       <c r="J73" t="n">
-        <v>17.6306</v>
+        <v>19.5832</v>
       </c>
     </row>
     <row r="74">
@@ -5999,10 +5999,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3586</v>
+        <v>0.3796</v>
       </c>
       <c r="J74" t="n">
-        <v>9.323600000000001</v>
+        <v>9.8696</v>
       </c>
     </row>
     <row r="75">
@@ -6039,10 +6039,10 @@
         <v>1.11</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3198</v>
+        <v>0.3295</v>
       </c>
       <c r="J75" t="n">
-        <v>8.3148</v>
+        <v>8.567</v>
       </c>
     </row>
     <row r="76">
@@ -6079,10 +6079,10 @@
         <v>1.01</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0036</v>
+        <v>0.0193</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.0936</v>
+        <v>0.5018</v>
       </c>
     </row>
     <row r="77">
@@ -6119,10 +6119,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3305</v>
+        <v>0.3255</v>
       </c>
       <c r="J77" t="n">
-        <v>8.593</v>
+        <v>8.462999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6159,10 +6159,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2024</v>
+        <v>0.1998</v>
       </c>
       <c r="J78" t="n">
-        <v>5.2624</v>
+        <v>5.1948</v>
       </c>
     </row>
     <row r="79">
@@ -6199,10 +6199,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.121</v>
+        <v>-0.1368</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.146</v>
+        <v>-3.5568</v>
       </c>
     </row>
     <row r="80">
@@ -6239,10 +6239,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3479</v>
+        <v>-0.362</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.045400000000001</v>
+        <v>-9.412000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6279,10 +6279,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4412</v>
+        <v>-0.4512</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.4712</v>
+        <v>-11.7312</v>
       </c>
     </row>
     <row r="82">
@@ -6319,10 +6319,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1219</v>
+        <v>0.1288</v>
       </c>
       <c r="J82" t="n">
-        <v>3.4132</v>
+        <v>3.6064</v>
       </c>
     </row>
     <row r="83">
@@ -6359,10 +6359,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0973</v>
+        <v>0.1039</v>
       </c>
       <c r="J83" t="n">
-        <v>2.7244</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="84">
@@ -6399,10 +6399,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J84" t="n">
-        <v>1.1844</v>
+        <v>1.3048</v>
       </c>
     </row>
     <row r="85">
@@ -6439,10 +6439,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0608</v>
+        <v>-0.0707</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.7024</v>
+        <v>-1.9796</v>
       </c>
     </row>
     <row r="86">
@@ -6479,10 +6479,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2155</v>
+        <v>-0.2298</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.034</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="87">
@@ -6519,10 +6519,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7891</v>
+        <v>0.8699</v>
       </c>
       <c r="J87" t="n">
-        <v>22.0948</v>
+        <v>24.3572</v>
       </c>
     </row>
     <row r="88">
@@ -6559,10 +6559,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5157</v>
+        <v>0.5703</v>
       </c>
       <c r="J88" t="n">
-        <v>14.4396</v>
+        <v>15.9684</v>
       </c>
     </row>
     <row r="89">
@@ -6599,10 +6599,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3999</v>
+        <v>0.4366</v>
       </c>
       <c r="J89" t="n">
-        <v>11.1972</v>
+        <v>12.2248</v>
       </c>
     </row>
     <row r="90">
@@ -6639,10 +6639,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3999</v>
+        <v>0.4366</v>
       </c>
       <c r="J90" t="n">
-        <v>11.1972</v>
+        <v>12.2248</v>
       </c>
     </row>
     <row r="91">
@@ -6679,10 +6679,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6886</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.2808</v>
+        <v>-17.9088</v>
       </c>
     </row>
     <row r="92">
@@ -6719,10 +6719,10 @@
         <v>0.99</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0597</v>
+        <v>0.0277</v>
       </c>
       <c r="J92" t="n">
-        <v>1.0746</v>
+        <v>0.4986</v>
       </c>
     </row>
     <row r="93">
@@ -6759,10 +6759,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1388</v>
+        <v>-0.1611</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.4984</v>
+        <v>-2.8998</v>
       </c>
     </row>
     <row r="94">
@@ -6799,10 +6799,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.29</v>
+        <v>-0.3099</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.22</v>
+        <v>-5.5782</v>
       </c>
     </row>
     <row r="95">
@@ -6839,10 +6839,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3081</v>
+        <v>-0.3275</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.5458</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="96">
@@ -6879,10 +6879,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6433</v>
+        <v>-0.6428</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.5794</v>
+        <v>-11.5704</v>
       </c>
     </row>
     <row r="97">
@@ -6919,10 +6919,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3902</v>
+        <v>1.5218</v>
       </c>
       <c r="J97" t="n">
-        <v>25.0236</v>
+        <v>27.3924</v>
       </c>
     </row>
     <row r="98">
@@ -6959,10 +6959,10 @@
         <v>1.77</v>
       </c>
       <c r="I98" t="n">
-        <v>1.1319</v>
+        <v>1.2499</v>
       </c>
       <c r="J98" t="n">
-        <v>20.3742</v>
+        <v>22.4982</v>
       </c>
     </row>
     <row r="99">
@@ -6999,10 +6999,10 @@
         <v>1.39</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6881</v>
+        <v>0.771</v>
       </c>
       <c r="J99" t="n">
-        <v>12.3858</v>
+        <v>13.878</v>
       </c>
     </row>
     <row r="100">
@@ -7039,10 +7039,10 @@
         <v>1.27</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5972</v>
       </c>
       <c r="J100" t="n">
-        <v>9.5526</v>
+        <v>10.7496</v>
       </c>
     </row>
     <row r="101">
@@ -7079,10 +7079,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0863</v>
+        <v>0.1232</v>
       </c>
       <c r="J101" t="n">
-        <v>1.5534</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="102">
@@ -7119,10 +7119,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4257</v>
+        <v>0.465</v>
       </c>
       <c r="J102" t="n">
-        <v>10.6425</v>
+        <v>11.625</v>
       </c>
     </row>
     <row r="103">
@@ -7159,10 +7159,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0558</v>
+        <v>-0.0669</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.395</v>
+        <v>-1.6725</v>
       </c>
     </row>
     <row r="104">
@@ -7199,10 +7199,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1145</v>
+        <v>-0.1289</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.8625</v>
+        <v>-3.2225</v>
       </c>
     </row>
     <row r="105">
@@ -7239,10 +7239,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2583</v>
+        <v>-0.2736</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4575</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="106">
@@ -7279,10 +7279,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3068</v>
+        <v>-0.321</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.67</v>
+        <v>-8.025</v>
       </c>
     </row>
     <row r="107">
@@ -7319,10 +7319,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.048</v>
+        <v>1.1485</v>
       </c>
       <c r="J107" t="n">
-        <v>26.2</v>
+        <v>28.7125</v>
       </c>
     </row>
     <row r="108">
@@ -7359,10 +7359,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3962</v>
+        <v>0.4329</v>
       </c>
       <c r="J108" t="n">
-        <v>9.904999999999999</v>
+        <v>10.8225</v>
       </c>
     </row>
     <row r="109">
@@ -7399,10 +7399,10 @@
         <v>1.07</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2178</v>
+        <v>0.2307</v>
       </c>
       <c r="J109" t="n">
-        <v>5.445</v>
+        <v>5.7675</v>
       </c>
     </row>
     <row r="110">
@@ -7439,10 +7439,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1553</v>
+        <v>0.1715</v>
       </c>
       <c r="J110" t="n">
-        <v>3.8825</v>
+        <v>4.2875</v>
       </c>
     </row>
     <row r="111">
@@ -7479,10 +7479,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1062</v>
       </c>
       <c r="J111" t="n">
-        <v>2.1875</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="112">
@@ -7519,10 +7519,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J112" t="n">
-        <v>9.5076</v>
+        <v>9.723599999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7559,10 +7559,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1814</v>
+        <v>0.19</v>
       </c>
       <c r="J113" t="n">
-        <v>6.5304</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="114">
@@ -7599,10 +7599,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.0216</v>
+        <v>-0.0144</v>
       </c>
     </row>
     <row r="115">
@@ -7639,10 +7639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0892</v>
+        <v>-0.0998</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.2112</v>
+        <v>-3.5928</v>
       </c>
     </row>
     <row r="116">
@@ -7679,10 +7679,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1011</v>
+        <v>-0.1123</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.6396</v>
+        <v>-4.0428</v>
       </c>
     </row>
     <row r="117">
@@ -7719,10 +7719,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6231</v>
+        <v>0.6871</v>
       </c>
       <c r="J117" t="n">
-        <v>22.4316</v>
+        <v>24.7356</v>
       </c>
     </row>
     <row r="118">
@@ -7759,10 +7759,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.435</v>
+        <v>0.4777</v>
       </c>
       <c r="J118" t="n">
-        <v>15.66</v>
+        <v>17.1972</v>
       </c>
     </row>
     <row r="119">
@@ -7799,10 +7799,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.374</v>
+        <v>0.3973</v>
       </c>
       <c r="J119" t="n">
-        <v>13.464</v>
+        <v>14.3028</v>
       </c>
     </row>
     <row r="120">
@@ -7839,10 +7839,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2067</v>
+        <v>0.2152</v>
       </c>
       <c r="J120" t="n">
-        <v>7.4412</v>
+        <v>7.7472</v>
       </c>
     </row>
     <row r="121">
@@ -7879,10 +7879,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.464</v>
+        <v>-0.4405</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.704</v>
+        <v>-15.858</v>
       </c>
     </row>
     <row r="122">
@@ -7919,10 +7919,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9365</v>
+        <v>0.8781</v>
       </c>
       <c r="J122" t="n">
-        <v>27.1585</v>
+        <v>25.4649</v>
       </c>
     </row>
     <row r="123">
@@ -7959,10 +7959,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.915</v>
+        <v>0.8583</v>
       </c>
       <c r="J123" t="n">
-        <v>26.535</v>
+        <v>24.8907</v>
       </c>
     </row>
     <row r="124">
@@ -7999,10 +7999,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3631</v>
+        <v>0.3648</v>
       </c>
       <c r="J124" t="n">
-        <v>10.5299</v>
+        <v>10.5792</v>
       </c>
     </row>
     <row r="125">
@@ -8039,10 +8039,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2797</v>
+        <v>0.2877</v>
       </c>
       <c r="J125" t="n">
-        <v>8.1113</v>
+        <v>8.343299999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8079,10 +8079,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2109</v>
+        <v>-0.2011</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.1161</v>
+        <v>-5.8319</v>
       </c>
     </row>
     <row r="127">
@@ -8119,10 +8119,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1088</v>
+        <v>0.1122</v>
       </c>
       <c r="J127" t="n">
-        <v>3.1552</v>
+        <v>3.2538</v>
       </c>
     </row>
     <row r="128">
@@ -8159,10 +8159,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1088</v>
+        <v>0.1122</v>
       </c>
       <c r="J128" t="n">
-        <v>3.1552</v>
+        <v>3.2538</v>
       </c>
     </row>
     <row r="129">
@@ -8199,10 +8199,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1155</v>
+        <v>-0.1296</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.3495</v>
+        <v>-3.7584</v>
       </c>
     </row>
     <row r="130">
@@ -8239,10 +8239,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1264</v>
+        <v>-0.1409</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.6656</v>
+        <v>-4.0861</v>
       </c>
     </row>
     <row r="131">
@@ -8279,10 +8279,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2696</v>
+        <v>-0.2844</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.8184</v>
+        <v>-8.2476</v>
       </c>
     </row>
     <row r="132">
@@ -8319,10 +8319,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9314</v>
+        <v>0.8743</v>
       </c>
       <c r="J132" t="n">
-        <v>21.4222</v>
+        <v>20.1089</v>
       </c>
     </row>
     <row r="133">
@@ -8359,10 +8359,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8874</v>
+        <v>0.8348</v>
       </c>
       <c r="J133" t="n">
-        <v>20.4102</v>
+        <v>19.2004</v>
       </c>
     </row>
     <row r="134">
@@ -8399,10 +8399,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4892</v>
+        <v>0.4806</v>
       </c>
       <c r="J134" t="n">
-        <v>11.2516</v>
+        <v>11.0538</v>
       </c>
     </row>
     <row r="135">
@@ -8439,10 +8439,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1543</v>
+        <v>0.1709</v>
       </c>
       <c r="J135" t="n">
-        <v>3.5489</v>
+        <v>3.9307</v>
       </c>
     </row>
     <row r="136">
@@ -8479,10 +8479,10 @@
         <v>1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1212</v>
+        <v>0.1392</v>
       </c>
       <c r="J136" t="n">
-        <v>2.7876</v>
+        <v>3.2016</v>
       </c>
     </row>
     <row r="137">
@@ -8519,10 +8519,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2135</v>
+        <v>0.2186</v>
       </c>
       <c r="J137" t="n">
-        <v>4.9105</v>
+        <v>5.0278</v>
       </c>
     </row>
     <row r="138">
@@ -8559,10 +8559,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="J138" t="n">
-        <v>1.6652</v>
+        <v>1.7917</v>
       </c>
     </row>
     <row r="139">
@@ -8599,10 +8599,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0476</v>
+        <v>-0.0564</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.0948</v>
+        <v>-1.2972</v>
       </c>
     </row>
     <row r="140">
@@ -8639,10 +8639,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.2545</v>
+        <v>-3.5719</v>
       </c>
     </row>
     <row r="141">
@@ -8679,10 +8679,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.163</v>
+        <v>-0.1772</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.749</v>
+        <v>-4.0756</v>
       </c>
     </row>
     <row r="142">
@@ -8719,10 +8719,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1845</v>
+        <v>1.1494</v>
       </c>
       <c r="J142" t="n">
-        <v>30.797</v>
+        <v>29.8844</v>
       </c>
     </row>
     <row r="143">
@@ -8759,10 +8759,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8218</v>
+        <v>0.7768</v>
       </c>
       <c r="J143" t="n">
-        <v>21.3668</v>
+        <v>20.1968</v>
       </c>
     </row>
     <row r="144">
@@ -8799,10 +8799,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3067</v>
+        <v>0.3131</v>
       </c>
       <c r="J144" t="n">
-        <v>7.9742</v>
+        <v>8.140599999999999</v>
       </c>
     </row>
     <row r="145">
@@ -8839,10 +8839,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.099</v>
+        <v>-0.0902</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.574</v>
+        <v>-2.3452</v>
       </c>
     </row>
     <row r="146">
@@ -8879,10 +8879,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1402</v>
+        <v>-0.1317</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.6452</v>
+        <v>-3.4242</v>
       </c>
     </row>
     <row r="147">
@@ -8919,10 +8919,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9192</v>
+        <v>0.8642</v>
       </c>
       <c r="J147" t="n">
-        <v>23.8992</v>
+        <v>22.4692</v>
       </c>
     </row>
     <row r="148">
@@ -8959,10 +8959,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0828</v>
+        <v>-0.095</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.1528</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="149">
@@ -8999,10 +8999,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0941</v>
+        <v>-0.107</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.4466</v>
+        <v>-2.782</v>
       </c>
     </row>
     <row r="150">
@@ -9039,10 +9039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2216</v>
+        <v>-0.2367</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.7616</v>
+        <v>-6.1542</v>
       </c>
     </row>
     <row r="151">
@@ -9079,10 +9079,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4682</v>
+        <v>-0.4754</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.1732</v>
+        <v>-12.3604</v>
       </c>
     </row>
     <row r="152">
@@ -9119,10 +9119,10 @@
         <v>1.23</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5503</v>
+        <v>0.5262</v>
       </c>
       <c r="J152" t="n">
-        <v>13.7575</v>
+        <v>13.155</v>
       </c>
     </row>
     <row r="153">
@@ -9159,10 +9159,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.312</v>
+        <v>0.3051</v>
       </c>
       <c r="J153" t="n">
-        <v>7.8</v>
+        <v>7.6275</v>
       </c>
     </row>
     <row r="154">
@@ -9199,10 +9199,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2909</v>
+        <v>-0.3068</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.2725</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="155">
@@ -9239,10 +9239,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3764</v>
+        <v>-0.3893</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.41</v>
+        <v>-9.7325</v>
       </c>
     </row>
     <row r="156">
@@ -9279,10 +9279,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3951</v>
+        <v>-0.4072</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.8775</v>
+        <v>-10.18</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9319,10 @@
         <v>1.81</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4866</v>
+        <v>1.4767</v>
       </c>
       <c r="J157" t="n">
-        <v>37.165</v>
+        <v>36.9175</v>
       </c>
     </row>
     <row r="158">
@@ -9359,10 +9359,10 @@
         <v>1.37</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9174</v>
+        <v>0.8681</v>
       </c>
       <c r="J158" t="n">
-        <v>22.935</v>
+        <v>21.7025</v>
       </c>
     </row>
     <row r="159">
@@ -9399,10 +9399,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7234</v>
+        <v>0.696</v>
       </c>
       <c r="J159" t="n">
-        <v>18.085</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="160">
@@ -9439,10 +9439,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4844</v>
+        <v>0.4827</v>
       </c>
       <c r="J160" t="n">
-        <v>12.11</v>
+        <v>12.0675</v>
       </c>
     </row>
     <row r="161">
@@ -9479,10 +9479,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0525</v>
+        <v>0.0818</v>
       </c>
       <c r="J161" t="n">
-        <v>1.3125</v>
+        <v>2.045</v>
       </c>
     </row>
     <row r="162">
@@ -9519,10 +9519,10 @@
         <v>1.71</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3665</v>
+        <v>1.3503</v>
       </c>
       <c r="J162" t="n">
-        <v>31.4295</v>
+        <v>31.0569</v>
       </c>
     </row>
     <row r="163">
@@ -9559,10 +9559,10 @@
         <v>1.52</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1373</v>
+        <v>1.1055</v>
       </c>
       <c r="J163" t="n">
-        <v>26.1579</v>
+        <v>25.4265</v>
       </c>
     </row>
     <row r="164">
@@ -9599,10 +9599,10 @@
         <v>1.33</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8324</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>19.1452</v>
+        <v>18.2344</v>
       </c>
     </row>
     <row r="165">
@@ -9639,10 +9639,10 @@
         <v>1.13</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3524</v>
+        <v>0.3634</v>
       </c>
       <c r="J165" t="n">
-        <v>8.1052</v>
+        <v>8.3582</v>
       </c>
     </row>
     <row r="166">
@@ -9679,10 +9679,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0136</v>
+        <v>0.044</v>
       </c>
       <c r="J166" t="n">
-        <v>0.3128</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="167">
@@ -9719,10 +9719,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5081</v>
+        <v>0.4742</v>
       </c>
       <c r="J167" t="n">
-        <v>11.6863</v>
+        <v>10.9066</v>
       </c>
     </row>
     <row r="168">
@@ -9759,10 +9759,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2656</v>
+        <v>-0.2853</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.1088</v>
+        <v>-6.5619</v>
       </c>
     </row>
     <row r="169">
@@ -9799,10 +9799,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3117</v>
+        <v>-0.3303</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.1691</v>
+        <v>-7.5969</v>
       </c>
     </row>
     <row r="170">
@@ -9839,10 +9839,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3679</v>
+        <v>-0.3843</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.4617</v>
+        <v>-8.838900000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9879,10 +9879,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5078</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.6794</v>
+        <v>-11.8818</v>
       </c>
     </row>
     <row r="172">
@@ -9919,10 +9919,10 @@
         <v>1.27</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7738</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>32.4996</v>
+        <v>30.5046</v>
       </c>
     </row>
     <row r="173">
@@ -9959,10 +9959,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7245</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>30.429</v>
+        <v>28.686</v>
       </c>
     </row>
     <row r="174">
@@ -9999,10 +9999,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1201</v>
+        <v>0.1288</v>
       </c>
       <c r="J174" t="n">
-        <v>5.0442</v>
+        <v>5.4096</v>
       </c>
     </row>
     <row r="175">
@@ -10039,10 +10039,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4214</v>
+        <v>-0.4049</v>
       </c>
       <c r="J175" t="n">
-        <v>-17.6988</v>
+        <v>-17.0058</v>
       </c>
     </row>
     <row r="176">
@@ -10079,10 +10079,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5313</v>
+        <v>-0.5043</v>
       </c>
       <c r="J176" t="n">
-        <v>-22.3146</v>
+        <v>-21.1806</v>
       </c>
     </row>
     <row r="177">
@@ -10119,10 +10119,10 @@
         <v>1.09</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2244</v>
+        <v>0.2317</v>
       </c>
       <c r="J177" t="n">
-        <v>9.424799999999999</v>
+        <v>9.731400000000001</v>
       </c>
     </row>
     <row r="178">
@@ -10159,10 +10159,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1823</v>
+        <v>0.1907</v>
       </c>
       <c r="J178" t="n">
-        <v>7.6566</v>
+        <v>8.009399999999999</v>
       </c>
     </row>
     <row r="179">
@@ -10199,10 +10199,10 @@
         <v>0.99</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.021</v>
+        <v>-0.0256</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.882</v>
+        <v>-1.0752</v>
       </c>
     </row>
     <row r="180">
@@ -10239,10 +10239,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.021</v>
+        <v>-0.0256</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.882</v>
+        <v>-1.0752</v>
       </c>
     </row>
     <row r="181">
@@ -10279,10 +10279,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1459</v>
+        <v>-0.1587</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.1278</v>
+        <v>-6.6654</v>
       </c>
     </row>
     <row r="182">
@@ -10319,10 +10319,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.38</v>
+        <v>1.3664</v>
       </c>
       <c r="J182" t="n">
-        <v>34.5</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="183">
@@ -10359,10 +10359,10 @@
         <v>1.58</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2022</v>
+        <v>1.1769</v>
       </c>
       <c r="J183" t="n">
-        <v>30.055</v>
+        <v>29.4225</v>
       </c>
     </row>
     <row r="184">
@@ -10399,10 +10399,10 @@
         <v>1.3</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7583</v>
+        <v>0.7289</v>
       </c>
       <c r="J184" t="n">
-        <v>18.9575</v>
+        <v>18.2225</v>
       </c>
     </row>
     <row r="185">
@@ -10439,10 +10439,10 @@
         <v>1.29</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7357</v>
+        <v>0.7089</v>
       </c>
       <c r="J185" t="n">
-        <v>18.3925</v>
+        <v>17.7225</v>
       </c>
     </row>
     <row r="186">
@@ -10479,10 +10479,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1071</v>
       </c>
       <c r="J186" t="n">
-        <v>1.885</v>
+        <v>2.6775</v>
       </c>
     </row>
     <row r="187">
@@ -10519,10 +10519,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0713</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.7825</v>
+        <v>-2.235</v>
       </c>
     </row>
     <row r="188">
@@ -10559,10 +10559,10 @@
         <v>0.8</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2137</v>
+        <v>-0.2329</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.3425</v>
+        <v>-5.8225</v>
       </c>
     </row>
     <row r="189">
@@ -10599,10 +10599,10 @@
         <v>0.8</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2137</v>
+        <v>-0.2329</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.3425</v>
+        <v>-5.8225</v>
       </c>
     </row>
     <row r="190">
@@ -10639,10 +10639,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2698</v>
+        <v>-0.2885</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.745</v>
+        <v>-7.2125</v>
       </c>
     </row>
     <row r="191">
@@ -10679,10 +10679,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3737</v>
+        <v>-0.3888</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.342499999999999</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10719,10 +10719,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0739</v>
+        <v>1.0385</v>
       </c>
       <c r="J192" t="n">
-        <v>32.217</v>
+        <v>31.155</v>
       </c>
     </row>
     <row r="193">
@@ -10759,10 +10759,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4267</v>
+        <v>0.425</v>
       </c>
       <c r="J193" t="n">
-        <v>12.801</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="194">
@@ -10799,10 +10799,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3154</v>
+        <v>0.3205</v>
       </c>
       <c r="J194" t="n">
-        <v>9.462</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="195">
@@ -10839,10 +10839,10 @@
         <v>0.73</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3121</v>
+        <v>-0.3233</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.363</v>
+        <v>-9.699</v>
       </c>
     </row>
     <row r="196">
@@ -10879,10 +10879,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.514</v>
+        <v>-0.5173</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.42</v>
+        <v>-15.519</v>
       </c>
     </row>
     <row r="197">
@@ -10919,10 +10919,10 @@
         <v>1.54</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2254</v>
+        <v>1.1881</v>
       </c>
       <c r="J197" t="n">
-        <v>36.762</v>
+        <v>35.643</v>
       </c>
     </row>
     <row r="198">
@@ -10959,10 +10959,10 @@
         <v>1.12</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3786</v>
+        <v>0.3753</v>
       </c>
       <c r="J198" t="n">
-        <v>11.358</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="199">
@@ -10999,10 +10999,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0751</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>2.253</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="200">
@@ -11039,10 +11039,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4032</v>
+        <v>-0.3862</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.096</v>
+        <v>-11.586</v>
       </c>
     </row>
     <row r="201">
@@ -11079,10 +11079,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4316</v>
+        <v>-0.412</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.948</v>
+        <v>-12.36</v>
       </c>
     </row>
     <row r="202">
@@ -11119,10 +11119,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0416</v>
+        <v>0.0144</v>
       </c>
       <c r="J202" t="n">
-        <v>0.8736</v>
+        <v>0.3024</v>
       </c>
     </row>
     <row r="203">
@@ -11159,10 +11159,10 @@
         <v>0.79</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2192</v>
+        <v>-0.2393</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.6032</v>
+        <v>-5.0253</v>
       </c>
     </row>
     <row r="204">
@@ -11199,10 +11199,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3032</v>
+        <v>-0.3219</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.3672</v>
+        <v>-6.7599</v>
       </c>
     </row>
     <row r="205">
@@ -11239,10 +11239,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3125</v>
+        <v>-0.3309</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.5625</v>
+        <v>-6.9489</v>
       </c>
     </row>
     <row r="206">
@@ -11279,10 +11279,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.425</v>
+        <v>-0.4384</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.925000000000001</v>
+        <v>-9.2064</v>
       </c>
     </row>
     <row r="207">
@@ -11319,10 +11319,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3075</v>
+        <v>1.2897</v>
       </c>
       <c r="J207" t="n">
-        <v>27.4575</v>
+        <v>27.0837</v>
       </c>
     </row>
     <row r="208">
@@ -11359,10 +11359,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1044</v>
+        <v>1.0715</v>
       </c>
       <c r="J208" t="n">
-        <v>23.1924</v>
+        <v>22.5015</v>
       </c>
     </row>
     <row r="209">
@@ -11399,10 +11399,10 @@
         <v>1.45</v>
       </c>
       <c r="I209" t="n">
-        <v>1.0427</v>
+        <v>0.9998</v>
       </c>
       <c r="J209" t="n">
-        <v>21.8967</v>
+        <v>20.9958</v>
       </c>
     </row>
     <row r="210">
@@ -11439,10 +11439,10 @@
         <v>1.44</v>
       </c>
       <c r="I210" t="n">
-        <v>1.0291</v>
+        <v>0.984</v>
       </c>
       <c r="J210" t="n">
-        <v>21.6111</v>
+        <v>20.664</v>
       </c>
     </row>
     <row r="211">
@@ -11479,10 +11479,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3589</v>
+        <v>-0.3288</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.5369</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="212">
@@ -11519,10 +11519,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1119</v>
+        <v>1.0653</v>
       </c>
       <c r="J212" t="n">
-        <v>33.357</v>
+        <v>31.959</v>
       </c>
     </row>
     <row r="213">
@@ -11559,10 +11559,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9936</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>29.808</v>
+        <v>27.837</v>
       </c>
     </row>
     <row r="214">
@@ -11599,10 +11599,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1161</v>
+        <v>0.1261</v>
       </c>
       <c r="J214" t="n">
-        <v>3.483</v>
+        <v>3.783</v>
       </c>
     </row>
     <row r="215">
@@ -11639,10 +11639,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4821</v>
+        <v>-0.4589</v>
       </c>
       <c r="J215" t="n">
-        <v>-14.463</v>
+        <v>-13.767</v>
       </c>
     </row>
     <row r="216">
@@ -11679,10 +11679,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-1.0149</v>
+        <v>-0.9281</v>
       </c>
       <c r="J216" t="n">
-        <v>-30.447</v>
+        <v>-27.843</v>
       </c>
     </row>
     <row r="217">
@@ -11719,10 +11719,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5453</v>
+        <v>0.5354</v>
       </c>
       <c r="J217" t="n">
-        <v>16.359</v>
+        <v>16.062</v>
       </c>
     </row>
     <row r="218">
@@ -11759,10 +11759,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.214</v>
+        <v>0.2242</v>
       </c>
       <c r="J218" t="n">
-        <v>6.42</v>
+        <v>6.726</v>
       </c>
     </row>
     <row r="219">
@@ -11799,10 +11799,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1082</v>
+        <v>0.1191</v>
       </c>
       <c r="J219" t="n">
-        <v>3.246</v>
+        <v>3.573</v>
       </c>
     </row>
     <row r="220">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0557</v>
+        <v>-0.0625</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.671</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="221">
@@ -11879,10 +11879,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1179</v>
+        <v>-0.1285</v>
       </c>
       <c r="J221" t="n">
-        <v>-3.537</v>
+        <v>-3.855</v>
       </c>
     </row>
     <row r="222">
@@ -11919,10 +11919,10 @@
         <v>1.6</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2258</v>
+        <v>1.2023</v>
       </c>
       <c r="J222" t="n">
-        <v>26.9676</v>
+        <v>26.4506</v>
       </c>
     </row>
     <row r="223">
@@ -11959,10 +11959,10 @@
         <v>1.59</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2139</v>
+        <v>1.1894</v>
       </c>
       <c r="J223" t="n">
-        <v>26.7058</v>
+        <v>26.1668</v>
       </c>
     </row>
     <row r="224">
@@ -11999,10 +11999,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8465</v>
+        <v>0.8067</v>
       </c>
       <c r="J224" t="n">
-        <v>18.623</v>
+        <v>17.7474</v>
       </c>
     </row>
     <row r="225">
@@ -12039,10 +12039,10 @@
         <v>1.29</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7353</v>
+        <v>0.7087</v>
       </c>
       <c r="J225" t="n">
-        <v>16.1766</v>
+        <v>15.5914</v>
       </c>
     </row>
     <row r="226">
@@ -12079,10 +12079,10 @@
         <v>1.13</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3418</v>
+        <v>0.356</v>
       </c>
       <c r="J226" t="n">
-        <v>7.5196</v>
+        <v>7.832</v>
       </c>
     </row>
     <row r="227">
@@ -12119,10 +12119,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4221</v>
+        <v>0.399</v>
       </c>
       <c r="J227" t="n">
-        <v>9.286199999999999</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="228">
@@ -12159,10 +12159,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2323</v>
+        <v>-0.2515</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.1106</v>
+        <v>-5.533</v>
       </c>
     </row>
     <row r="229">
@@ -12199,10 +12199,10 @@
         <v>0.76</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2505</v>
+        <v>-0.2697</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.511</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="230">
@@ -12239,10 +12239,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2599</v>
+        <v>-0.2789</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.7178</v>
+        <v>-6.1358</v>
       </c>
     </row>
     <row r="231">
@@ -12279,10 +12279,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5402</v>
+        <v>-0.5462</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.8844</v>
+        <v>-12.0164</v>
       </c>
     </row>
     <row r="232">
@@ -12319,10 +12319,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.236</v>
+        <v>1.2089</v>
       </c>
       <c r="J232" t="n">
-        <v>28.428</v>
+        <v>27.8047</v>
       </c>
     </row>
     <row r="233">
@@ -12359,10 +12359,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7759</v>
+        <v>0.7408</v>
       </c>
       <c r="J233" t="n">
-        <v>17.8457</v>
+        <v>17.0384</v>
       </c>
     </row>
     <row r="234">
@@ -12399,10 +12399,10 @@
         <v>1.24</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6417</v>
+        <v>0.6212</v>
       </c>
       <c r="J234" t="n">
-        <v>14.7591</v>
+        <v>14.2876</v>
       </c>
     </row>
     <row r="235">
@@ -12439,10 +12439,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4459</v>
+        <v>0.4453</v>
       </c>
       <c r="J235" t="n">
-        <v>10.2557</v>
+        <v>10.2419</v>
       </c>
     </row>
     <row r="236">
@@ -12479,10 +12479,10 @@
         <v>1.1</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2842</v>
+        <v>0.2975</v>
       </c>
       <c r="J236" t="n">
-        <v>6.5366</v>
+        <v>6.8425</v>
       </c>
     </row>
     <row r="237">
@@ -12519,10 +12519,10 @@
         <v>0.98</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0012</v>
+        <v>-0.0157</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.0276</v>
+        <v>-0.3611</v>
       </c>
     </row>
     <row r="238">
@@ -12559,10 +12559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2031</v>
+        <v>-0.2225</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.6713</v>
+        <v>-5.1175</v>
       </c>
     </row>
     <row r="239">
@@ -12599,10 +12599,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2227</v>
+        <v>-0.242</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.1221</v>
+        <v>-5.566</v>
       </c>
     </row>
     <row r="240">
@@ -12639,10 +12639,10 @@
         <v>0.72</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2879</v>
+        <v>-0.3063</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.6217</v>
+        <v>-7.0449</v>
       </c>
     </row>
     <row r="241">
@@ -12679,10 +12679,10 @@
         <v>0.57</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4289</v>
+        <v>-0.4415</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.864699999999999</v>
+        <v>-10.1545</v>
       </c>
     </row>
     <row r="242">
@@ -12719,10 +12719,10 @@
         <v>1.33</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8217</v>
       </c>
       <c r="J242" t="n">
-        <v>26.235</v>
+        <v>24.651</v>
       </c>
     </row>
     <row r="243">
@@ -12759,10 +12759,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7345</v>
+        <v>0.6989</v>
       </c>
       <c r="J243" t="n">
-        <v>22.035</v>
+        <v>20.967</v>
       </c>
     </row>
     <row r="244">
@@ -12799,10 +12799,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3927</v>
+        <v>0.3913</v>
       </c>
       <c r="J244" t="n">
-        <v>11.781</v>
+        <v>11.739</v>
       </c>
     </row>
     <row r="245">
@@ -12839,10 +12839,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2829</v>
+        <v>0.29</v>
       </c>
       <c r="J245" t="n">
-        <v>8.487</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12879,10 +12879,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.0939</v>
+        <v>-0.0866</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.817</v>
+        <v>-2.598</v>
       </c>
     </row>
     <row r="247">
@@ -12919,10 +12919,10 @@
         <v>0.99</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0158</v>
       </c>
       <c r="J247" t="n">
-        <v>-0.246</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="248">
@@ -12959,10 +12959,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0243</v>
+        <v>-0.0338</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.729</v>
+        <v>-1.014</v>
       </c>
     </row>
     <row r="249">
@@ -12999,10 +12999,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0388</v>
+        <v>-0.0496</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.164</v>
+        <v>-1.488</v>
       </c>
     </row>
     <row r="250">
@@ -13039,10 +13039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2154</v>
+        <v>-0.2319</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.462</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="251">
@@ -13079,10 +13079,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3321</v>
+        <v>-0.3462</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.962999999999999</v>
+        <v>-10.386</v>
       </c>
     </row>
     <row r="252">
@@ -13119,10 +13119,10 @@
         <v>1.99</v>
       </c>
       <c r="I252" t="n">
-        <v>1.641</v>
+        <v>1.647</v>
       </c>
       <c r="J252" t="n">
-        <v>29.538</v>
+        <v>29.646</v>
       </c>
     </row>
     <row r="253">
@@ -13159,10 +13159,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2154</v>
+        <v>1.1956</v>
       </c>
       <c r="J253" t="n">
-        <v>21.8772</v>
+        <v>21.5208</v>
       </c>
     </row>
     <row r="254">
@@ -13199,10 +13199,10 @@
         <v>1.58</v>
       </c>
       <c r="I254" t="n">
-        <v>1.1813</v>
+        <v>1.1588</v>
       </c>
       <c r="J254" t="n">
-        <v>21.2634</v>
+        <v>20.8584</v>
       </c>
     </row>
     <row r="255">
@@ -13239,10 +13239,10 @@
         <v>1.46</v>
       </c>
       <c r="I255" t="n">
-        <v>1.0412</v>
+        <v>1.0018</v>
       </c>
       <c r="J255" t="n">
-        <v>18.7416</v>
+        <v>18.0324</v>
       </c>
     </row>
     <row r="256">
@@ -13279,10 +13279,10 @@
         <v>1.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.2815</v>
+        <v>0.3079</v>
       </c>
       <c r="J256" t="n">
-        <v>5.067</v>
+        <v>5.5422</v>
       </c>
     </row>
     <row r="257">
@@ -13319,10 +13319,10 @@
         <v>0.77</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2105</v>
+        <v>-0.2367</v>
       </c>
       <c r="J257" t="n">
-        <v>-3.789</v>
+        <v>-4.2606</v>
       </c>
     </row>
     <row r="258">
@@ -13359,10 +13359,10 @@
         <v>0.73</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2528</v>
+        <v>-0.2774</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.5504</v>
+        <v>-4.9932</v>
       </c>
     </row>
     <row r="259">
@@ -13399,10 +13399,10 @@
         <v>0.64</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.341</v>
+        <v>-0.3619</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.138</v>
+        <v>-6.5142</v>
       </c>
     </row>
     <row r="260">
@@ -13439,10 +13439,10 @@
         <v>0.51</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.459</v>
+        <v>-0.474</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.262</v>
+        <v>-8.532</v>
       </c>
     </row>
     <row r="261">
@@ -13479,10 +13479,10 @@
         <v>0.44</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5251</v>
+        <v>-0.5356</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.4518</v>
+        <v>-9.6408</v>
       </c>
     </row>
     <row r="262">
@@ -13519,10 +13519,10 @@
         <v>1.43</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0443</v>
+        <v>0.9949</v>
       </c>
       <c r="J262" t="n">
-        <v>27.1518</v>
+        <v>25.8674</v>
       </c>
     </row>
     <row r="263">
@@ -13559,10 +13559,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9208</v>
+        <v>0.8665</v>
       </c>
       <c r="J263" t="n">
-        <v>23.9408</v>
+        <v>22.529</v>
       </c>
     </row>
     <row r="264">
@@ -13599,10 +13599,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.899</v>
+        <v>0.8469</v>
       </c>
       <c r="J264" t="n">
-        <v>23.374</v>
+        <v>22.0194</v>
       </c>
     </row>
     <row r="265">
@@ -13639,10 +13639,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6489</v>
+        <v>0.626</v>
       </c>
       <c r="J265" t="n">
-        <v>16.8714</v>
+        <v>16.276</v>
       </c>
     </row>
     <row r="266">
@@ -13679,10 +13679,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7832</v>
+        <v>-0.7199</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.3632</v>
+        <v>-18.7174</v>
       </c>
     </row>
     <row r="267">
@@ -13719,10 +13719,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7144</v>
+        <v>0.6835</v>
       </c>
       <c r="J267" t="n">
-        <v>18.5744</v>
+        <v>17.771</v>
       </c>
     </row>
     <row r="268">
@@ -13759,10 +13759,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="J268" t="n">
-        <v>3.77</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="269">
@@ -13799,10 +13799,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.9084</v>
+        <v>-2.1892</v>
       </c>
     </row>
     <row r="270">
@@ -13839,10 +13839,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0856</v>
+        <v>-0.097</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.2256</v>
+        <v>-2.522</v>
       </c>
     </row>
     <row r="271">
@@ -13879,10 +13879,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4448</v>
+        <v>-0.4525</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.5648</v>
+        <v>-11.765</v>
       </c>
     </row>
     <row r="272">
@@ -13919,10 +13919,10 @@
         <v>1.99</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6451</v>
+        <v>1.6506</v>
       </c>
       <c r="J272" t="n">
-        <v>32.902</v>
+        <v>33.012</v>
       </c>
     </row>
     <row r="273">
@@ -13959,10 +13959,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3203</v>
+        <v>1.3075</v>
       </c>
       <c r="J273" t="n">
-        <v>26.406</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="274">
@@ -13999,10 +13999,10 @@
         <v>1.6</v>
       </c>
       <c r="I274" t="n">
-        <v>1.206</v>
+        <v>1.185</v>
       </c>
       <c r="J274" t="n">
-        <v>24.12</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="275">
@@ -14039,10 +14039,10 @@
         <v>1.41</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9659</v>
+        <v>0.9202</v>
       </c>
       <c r="J275" t="n">
-        <v>19.318</v>
+        <v>18.404</v>
       </c>
     </row>
     <row r="276">
@@ -14079,10 +14079,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2884</v>
+        <v>-0.2556</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.768</v>
+        <v>-5.112</v>
       </c>
     </row>
     <row r="277">
@@ -14119,10 +14119,10 @@
         <v>0.82</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1515</v>
+        <v>-0.1801</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.03</v>
+        <v>-3.602</v>
       </c>
     </row>
     <row r="278">
@@ -14159,10 +14159,10 @@
         <v>0.75</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2289</v>
+        <v>-0.2549</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.578</v>
+        <v>-5.098</v>
       </c>
     </row>
     <row r="279">
@@ -14199,10 +14199,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3107</v>
+        <v>-0.3332</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.214</v>
+        <v>-6.664</v>
       </c>
     </row>
     <row r="280">
@@ -14239,10 +14239,10 @@
         <v>0.4</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5614</v>
+        <v>-0.5694</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.228</v>
+        <v>-11.388</v>
       </c>
     </row>
     <row r="281">
@@ -14279,10 +14279,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5614</v>
+        <v>-0.5694</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.228</v>
+        <v>-11.388</v>
       </c>
     </row>
     <row r="282">
@@ -14319,10 +14319,10 @@
         <v>0.78</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.193</v>
+        <v>-0.2209</v>
       </c>
       <c r="J282" t="n">
-        <v>-3.86</v>
+        <v>-4.418</v>
       </c>
     </row>
     <row r="283">
@@ -14359,10 +14359,10 @@
         <v>0.66</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.3181</v>
+        <v>-0.3408</v>
       </c>
       <c r="J283" t="n">
-        <v>-6.362</v>
+        <v>-6.816</v>
       </c>
     </row>
     <row r="284">
@@ -14399,10 +14399,10 @@
         <v>0.65</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3278</v>
+        <v>-0.35</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.556</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="285">
@@ -14439,10 +14439,10 @@
         <v>0.53</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4365</v>
+        <v>-0.4535</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.73</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="286">
@@ -14479,10 +14479,10 @@
         <v>0.37</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5884</v>
+        <v>-0.5945</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.768</v>
+        <v>-11.89</v>
       </c>
     </row>
     <row r="287">
@@ -14519,10 +14519,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2769</v>
+        <v>1.2584</v>
       </c>
       <c r="J287" t="n">
-        <v>25.538</v>
+        <v>25.168</v>
       </c>
     </row>
     <row r="288">
@@ -14559,10 +14559,10 @@
         <v>1.47</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0636</v>
+        <v>1.0257</v>
       </c>
       <c r="J288" t="n">
-        <v>21.272</v>
+        <v>20.514</v>
       </c>
     </row>
     <row r="289">
@@ -14599,10 +14599,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0513</v>
+        <v>1.0111</v>
       </c>
       <c r="J289" t="n">
-        <v>21.026</v>
+        <v>20.222</v>
       </c>
     </row>
     <row r="290">
@@ -14639,10 +14639,10 @@
         <v>1.32</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7934</v>
+        <v>0.7617</v>
       </c>
       <c r="J290" t="n">
-        <v>15.868</v>
+        <v>15.234</v>
       </c>
     </row>
     <row r="291">
@@ -14679,10 +14679,10 @@
         <v>1.29</v>
       </c>
       <c r="I291" t="n">
-        <v>0.7257</v>
+        <v>0.702</v>
       </c>
       <c r="J291" t="n">
-        <v>14.514</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="292">
@@ -14719,10 +14719,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6651</v>
+        <v>0.6415</v>
       </c>
       <c r="J292" t="n">
-        <v>19.953</v>
+        <v>19.245</v>
       </c>
     </row>
     <row r="293">
@@ -14759,10 +14759,10 @@
         <v>1.19</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4172</v>
+        <v>0.4143</v>
       </c>
       <c r="J293" t="n">
-        <v>12.516</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="294">
@@ -14799,10 +14799,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0213</v>
+        <v>-0.0258</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.639</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="295">
@@ -14839,10 +14839,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1354</v>
+        <v>-0.1478</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.062</v>
+        <v>-4.434</v>
       </c>
     </row>
     <row r="296">
@@ -14879,10 +14879,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3935</v>
+        <v>-0.4028</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.805</v>
+        <v>-12.084</v>
       </c>
     </row>
     <row r="297">
@@ -14919,10 +14919,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2601</v>
+        <v>1.2324</v>
       </c>
       <c r="J297" t="n">
-        <v>37.803</v>
+        <v>36.972</v>
       </c>
     </row>
     <row r="298">
@@ -14959,10 +14959,10 @@
         <v>1.25</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6715</v>
+        <v>0.6463</v>
       </c>
       <c r="J298" t="n">
-        <v>20.145</v>
+        <v>19.389</v>
       </c>
     </row>
     <row r="299">
@@ -14999,10 +14999,10 @@
         <v>1.19</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5314</v>
+        <v>0.5204</v>
       </c>
       <c r="J299" t="n">
-        <v>15.942</v>
+        <v>15.612</v>
       </c>
     </row>
     <row r="300">
@@ -15039,10 +15039,10 @@
         <v>1.11</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3235</v>
+        <v>0.3312</v>
       </c>
       <c r="J300" t="n">
-        <v>9.705</v>
+        <v>9.936</v>
       </c>
     </row>
     <row r="301">
@@ -15079,10 +15079,10 @@
         <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.0561</v>
+        <v>-0.0388</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.683</v>
+        <v>-1.164</v>
       </c>
     </row>
     <row r="302">
@@ -15119,10 +15119,10 @@
         <v>1.52</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1445</v>
+        <v>1.1118</v>
       </c>
       <c r="J302" t="n">
-        <v>28.6125</v>
+        <v>27.795</v>
       </c>
     </row>
     <row r="303">
@@ -15159,10 +15159,10 @@
         <v>1.34</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8593</v>
+        <v>0.8153</v>
       </c>
       <c r="J303" t="n">
-        <v>21.4825</v>
+        <v>20.3825</v>
       </c>
     </row>
     <row r="304">
@@ -15199,10 +15199,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7728</v>
+        <v>0.7388</v>
       </c>
       <c r="J304" t="n">
-        <v>19.32</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="305">
@@ -15239,10 +15239,10 @@
         <v>1.21</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5656</v>
+        <v>0.5541</v>
       </c>
       <c r="J305" t="n">
-        <v>14.14</v>
+        <v>13.8525</v>
       </c>
     </row>
     <row r="306">
@@ -15279,10 +15279,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3882</v>
+        <v>0.3941</v>
       </c>
       <c r="J306" t="n">
-        <v>9.705</v>
+        <v>9.852499999999999</v>
       </c>
     </row>
     <row r="307">
@@ -15319,10 +15319,10 @@
         <v>1.35</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7749</v>
+        <v>0.7284</v>
       </c>
       <c r="J307" t="n">
-        <v>19.3725</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="308">
@@ -15359,10 +15359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.212</v>
+        <v>-0.2293</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.3</v>
+        <v>-5.7325</v>
       </c>
     </row>
     <row r="309">
@@ -15399,10 +15399,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2416</v>
+        <v>-0.2586</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.04</v>
+        <v>-6.465</v>
       </c>
     </row>
     <row r="310">
@@ -15439,10 +15439,10 @@
         <v>0.73</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2901</v>
+        <v>-0.3062</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.2525</v>
+        <v>-7.655</v>
       </c>
     </row>
     <row r="311">
@@ -15479,10 +15479,10 @@
         <v>0.63</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.385</v>
+        <v>-0.3977</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.625</v>
+        <v>-9.942500000000001</v>
       </c>
     </row>
     <row r="312">
@@ -15519,10 +15519,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5476</v>
+        <v>0.5209</v>
       </c>
       <c r="J312" t="n">
-        <v>14.2376</v>
+        <v>13.5434</v>
       </c>
     </row>
     <row r="313">
@@ -15559,10 +15559,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1121</v>
+        <v>0.1068</v>
       </c>
       <c r="J313" t="n">
-        <v>2.9146</v>
+        <v>2.7768</v>
       </c>
     </row>
     <row r="314">
@@ -15599,10 +15599,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2093</v>
+        <v>-0.2272</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.4418</v>
+        <v>-5.9072</v>
       </c>
     </row>
     <row r="315">
@@ -15639,10 +15639,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3817</v>
+        <v>-0.3951</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.924200000000001</v>
+        <v>-10.2726</v>
       </c>
     </row>
     <row r="316">
@@ -15679,10 +15679,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.502</v>
+        <v>-0.5092</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.052</v>
+        <v>-13.2392</v>
       </c>
     </row>
     <row r="317">
@@ -15719,10 +15719,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3395</v>
+        <v>1.318</v>
       </c>
       <c r="J317" t="n">
-        <v>34.827</v>
+        <v>34.268</v>
       </c>
     </row>
     <row r="318">
@@ -15759,10 +15759,10 @@
         <v>1.49</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1161</v>
+        <v>1.0794</v>
       </c>
       <c r="J318" t="n">
-        <v>29.0186</v>
+        <v>28.0644</v>
       </c>
     </row>
     <row r="319">
@@ -15799,10 +15799,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.8248</v>
+        <v>0.7831</v>
       </c>
       <c r="J319" t="n">
-        <v>21.4448</v>
+        <v>20.3606</v>
       </c>
     </row>
     <row r="320">
@@ -15839,10 +15839,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1387</v>
+        <v>0.16</v>
       </c>
       <c r="J320" t="n">
-        <v>3.6062</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="321">
@@ -15879,10 +15879,10 @@
         <v>0.75</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8142</v>
+        <v>-0.7462</v>
       </c>
       <c r="J321" t="n">
-        <v>-21.1692</v>
+        <v>-19.4012</v>
       </c>
     </row>
     <row r="322">
@@ -15919,10 +15919,10 @@
         <v>0.9</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0233</v>
+        <v>-0.06</v>
       </c>
       <c r="J322" t="n">
-        <v>-0.4427</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="323">
@@ -15959,10 +15959,10 @@
         <v>0.64</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.3243</v>
+        <v>-0.349</v>
       </c>
       <c r="J323" t="n">
-        <v>-6.1617</v>
+        <v>-6.631</v>
       </c>
     </row>
     <row r="324">
@@ -15999,10 +15999,10 @@
         <v>0.5</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.4543</v>
+        <v>-0.4718</v>
       </c>
       <c r="J324" t="n">
-        <v>-8.6317</v>
+        <v>-8.9642</v>
       </c>
     </row>
     <row r="325">
@@ -16039,10 +16039,10 @@
         <v>0.5</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4543</v>
+        <v>-0.4718</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.6317</v>
+        <v>-8.9642</v>
       </c>
     </row>
     <row r="326">
@@ -16079,10 +16079,10 @@
         <v>0.19</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7562</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.3678</v>
+        <v>-14.2215</v>
       </c>
     </row>
     <row r="327">
@@ -16119,10 +16119,10 @@
         <v>2.38</v>
       </c>
       <c r="I327" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J327" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="328">
@@ -16159,10 +16159,10 @@
         <v>2.03</v>
       </c>
       <c r="I328" t="n">
-        <v>1.6716</v>
+        <v>1.6811</v>
       </c>
       <c r="J328" t="n">
-        <v>31.7604</v>
+        <v>31.9409</v>
       </c>
     </row>
     <row r="329">
@@ -16199,10 +16199,10 @@
         <v>1.56</v>
       </c>
       <c r="I329" t="n">
-        <v>1.154</v>
+        <v>1.1302</v>
       </c>
       <c r="J329" t="n">
-        <v>21.926</v>
+        <v>21.4738</v>
       </c>
     </row>
     <row r="330">
@@ -16239,10 +16239,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.296</v>
+        <v>0.3238</v>
       </c>
       <c r="J330" t="n">
-        <v>5.624</v>
+        <v>6.1522</v>
       </c>
     </row>
     <row r="331">
@@ -16279,10 +16279,10 @@
         <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1364</v>
+        <v>-0.0953</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.5916</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="332">
@@ -16319,10 +16319,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9271</v>
+        <v>0.8711</v>
       </c>
       <c r="J332" t="n">
-        <v>27.813</v>
+        <v>26.133</v>
       </c>
     </row>
     <row r="333">
@@ -16359,10 +16359,10 @@
         <v>1.33</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8119</v>
       </c>
       <c r="J333" t="n">
-        <v>25.812</v>
+        <v>24.357</v>
       </c>
     </row>
     <row r="334">
@@ -16399,10 +16399,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6294</v>
+        <v>0.6078</v>
       </c>
       <c r="J334" t="n">
-        <v>18.882</v>
+        <v>18.234</v>
       </c>
     </row>
     <row r="335">
@@ -16439,10 +16439,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.329</v>
+        <v>0.335</v>
       </c>
       <c r="J335" t="n">
-        <v>9.869999999999999</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="336">
@@ -16479,10 +16479,10 @@
         <v>1</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0501</v>
+        <v>-0.0346</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.503</v>
+        <v>-1.038</v>
       </c>
     </row>
     <row r="337">
@@ -16519,10 +16519,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0307</v>
+        <v>-0.0434</v>
       </c>
       <c r="J337" t="n">
-        <v>-0.921</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="338">
@@ -16559,10 +16559,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.115</v>
+        <v>-2.568</v>
       </c>
     </row>
     <row r="339">
@@ -16599,10 +16599,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1397</v>
+        <v>-0.1568</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.191</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="340">
@@ -16639,10 +16639,10 @@
         <v>0.79</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2293</v>
+        <v>-0.247</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.879</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="341">
@@ -16679,10 +16679,10 @@
         <v>0.62</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3916</v>
+        <v>-0.4045</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.748</v>
+        <v>-12.135</v>
       </c>
     </row>
     <row r="342">
@@ -16719,10 +16719,10 @@
         <v>1.81</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5563</v>
+        <v>1.5388</v>
       </c>
       <c r="J342" t="n">
-        <v>43.5764</v>
+        <v>43.0864</v>
       </c>
     </row>
     <row r="343">
@@ -16759,10 +16759,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3986</v>
+        <v>0.3952</v>
       </c>
       <c r="J343" t="n">
-        <v>11.1608</v>
+        <v>11.0656</v>
       </c>
     </row>
     <row r="344">
@@ -16799,10 +16799,10 @@
         <v>1</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0291</v>
+        <v>-0.02</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.8148</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="345">
@@ -16839,10 +16839,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3545</v>
+        <v>-0.3393</v>
       </c>
       <c r="J345" t="n">
-        <v>-9.926</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="346">
@@ -16879,10 +16879,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.733</v>
+        <v>-0.6801</v>
       </c>
       <c r="J346" t="n">
-        <v>-20.524</v>
+        <v>-19.0428</v>
       </c>
     </row>
     <row r="347">
@@ -16919,10 +16919,10 @@
         <v>1.18</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4042</v>
+        <v>0.4011</v>
       </c>
       <c r="J347" t="n">
-        <v>11.3176</v>
+        <v>11.2308</v>
       </c>
     </row>
     <row r="348">
@@ -16959,10 +16959,10 @@
         <v>1.14</v>
       </c>
       <c r="I348" t="n">
-        <v>0.328</v>
+        <v>0.3297</v>
       </c>
       <c r="J348" t="n">
-        <v>9.183999999999999</v>
+        <v>9.2316</v>
       </c>
     </row>
     <row r="349">
@@ -16999,10 +16999,10 @@
         <v>1.07</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1854</v>
+        <v>0.1929</v>
       </c>
       <c r="J349" t="n">
-        <v>5.1912</v>
+        <v>5.4012</v>
       </c>
     </row>
     <row r="350">
@@ -17039,10 +17039,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1974</v>
+        <v>-0.2112</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.5272</v>
+        <v>-5.9136</v>
       </c>
     </row>
     <row r="351">
@@ -17079,10 +17079,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3067</v>
+        <v>-0.3191</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.5876</v>
+        <v>-8.934799999999999</v>
       </c>
     </row>
     <row r="352">
@@ -17119,10 +17119,10 @@
         <v>1.34</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7993</v>
+        <v>0.7438</v>
       </c>
       <c r="J352" t="n">
-        <v>16.7853</v>
+        <v>15.6198</v>
       </c>
     </row>
     <row r="353">
@@ -17159,10 +17159,10 @@
         <v>0.77</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.2436</v>
+        <v>-0.2622</v>
       </c>
       <c r="J353" t="n">
-        <v>-5.1156</v>
+        <v>-5.5062</v>
       </c>
     </row>
     <row r="354">
@@ -17199,10 +17199,10 @@
         <v>0.77</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.2436</v>
+        <v>-0.2622</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.1156</v>
+        <v>-5.5062</v>
       </c>
     </row>
     <row r="355">
@@ -17239,10 +17239,10 @@
         <v>0.66</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3481</v>
+        <v>-0.3638</v>
       </c>
       <c r="J355" t="n">
-        <v>-7.3101</v>
+        <v>-7.6398</v>
       </c>
     </row>
     <row r="356">
@@ -17279,10 +17279,10 @@
         <v>0.45</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.543</v>
+        <v>-0.5484</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.403</v>
+        <v>-11.5164</v>
       </c>
     </row>
     <row r="357">
@@ -17319,10 +17319,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3747</v>
+        <v>1.3617</v>
       </c>
       <c r="J357" t="n">
-        <v>28.8687</v>
+        <v>28.5957</v>
       </c>
     </row>
     <row r="358">
@@ -17359,10 +17359,10 @@
         <v>1.42</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9978</v>
+        <v>0.9497</v>
       </c>
       <c r="J358" t="n">
-        <v>20.9538</v>
+        <v>19.9437</v>
       </c>
     </row>
     <row r="359">
@@ -17399,10 +17399,10 @@
         <v>1.34</v>
       </c>
       <c r="I359" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8037</v>
       </c>
       <c r="J359" t="n">
-        <v>17.6862</v>
+        <v>16.8777</v>
       </c>
     </row>
     <row r="360">
@@ -17439,10 +17439,10 @@
         <v>1.3</v>
       </c>
       <c r="I360" t="n">
-        <v>0.7532</v>
+        <v>0.7254</v>
       </c>
       <c r="J360" t="n">
-        <v>15.8172</v>
+        <v>15.2334</v>
       </c>
     </row>
     <row r="361">
@@ -17479,10 +17479,10 @@
         <v>1.28</v>
       </c>
       <c r="I361" t="n">
-        <v>0.7076</v>
+        <v>0.6851</v>
       </c>
       <c r="J361" t="n">
-        <v>14.8596</v>
+        <v>14.3871</v>
       </c>
     </row>
     <row r="362">
@@ -17519,10 +17519,10 @@
         <v>2.1</v>
       </c>
       <c r="I362" t="n">
-        <v>1.7424</v>
+        <v>1.7559</v>
       </c>
       <c r="J362" t="n">
-        <v>31.3632</v>
+        <v>31.6062</v>
       </c>
     </row>
     <row r="363">
@@ -17559,10 +17559,10 @@
         <v>1.98</v>
       </c>
       <c r="I363" t="n">
-        <v>1.6134</v>
+        <v>1.6208</v>
       </c>
       <c r="J363" t="n">
-        <v>29.0412</v>
+        <v>29.1744</v>
       </c>
     </row>
     <row r="364">
@@ -17599,10 +17599,10 @@
         <v>1.49</v>
       </c>
       <c r="I364" t="n">
-        <v>1.0692</v>
+        <v>1.037</v>
       </c>
       <c r="J364" t="n">
-        <v>19.2456</v>
+        <v>18.666</v>
       </c>
     </row>
     <row r="365">
@@ -17639,10 +17639,10 @@
         <v>1.44</v>
       </c>
       <c r="I365" t="n">
-        <v>1.0007</v>
+        <v>0.9593</v>
       </c>
       <c r="J365" t="n">
-        <v>18.0126</v>
+        <v>17.2674</v>
       </c>
     </row>
     <row r="366">
@@ -17679,10 +17679,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.4963</v>
+        <v>0.5058</v>
       </c>
       <c r="J366" t="n">
-        <v>8.933400000000001</v>
+        <v>9.1044</v>
       </c>
     </row>
     <row r="367">
@@ -17719,10 +17719,10 @@
         <v>0.74</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.2031</v>
+        <v>-0.2365</v>
       </c>
       <c r="J367" t="n">
-        <v>-3.6558</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="368">
@@ -17759,10 +17759,10 @@
         <v>0.63</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.3241</v>
+        <v>-0.3505</v>
       </c>
       <c r="J368" t="n">
-        <v>-5.8338</v>
+        <v>-6.309</v>
       </c>
     </row>
     <row r="369">
@@ -17799,10 +17799,10 @@
         <v>0.5</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.4482</v>
+        <v>-0.4671</v>
       </c>
       <c r="J369" t="n">
-        <v>-8.067600000000001</v>
+        <v>-8.4078</v>
       </c>
     </row>
     <row r="370">
@@ -17839,10 +17839,10 @@
         <v>0.39</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.5522</v>
+        <v>-0.5634</v>
       </c>
       <c r="J370" t="n">
-        <v>-9.9396</v>
+        <v>-10.1412</v>
       </c>
     </row>
     <row r="371">
@@ -17879,10 +17879,10 @@
         <v>0.31</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6312</v>
+        <v>-0.6357</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.3616</v>
+        <v>-11.4426</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2306/event_2306_evp_summary.xlsx
+++ b/database/event/2306/event_2306_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.609400000000001</v>
+        <v>8.575699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6896</v>
+        <v>3.6752</v>
       </c>
       <c r="D2" t="n">
-        <v>3.295</v>
+        <v>3.3009</v>
       </c>
       <c r="E2" t="n">
-        <v>8.609400000000001</v>
+        <v>8.575699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4017</v>
+        <v>2.3719</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2077</v>
+        <v>6.2037</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5316</v>
+        <v>2.4856</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6638</v>
+        <v>2.6202</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2077</v>
+        <v>6.2037</v>
       </c>
       <c r="K2" t="n">
         <v>131</v>
@@ -529,7 +529,7 @@
         <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>8.871500000000001</v>
+        <v>8.8239</v>
       </c>
       <c r="N2" t="n">
         <v>307</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8932</v>
+        <v>5.9057</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5256</v>
+        <v>2.5309</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0585</v>
+        <v>2.0845</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8932</v>
+        <v>5.9057</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2547</v>
+        <v>2.2433</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6385</v>
+        <v>3.6624</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2547</v>
+        <v>2.2433</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3724</v>
+        <v>2.3648</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6385</v>
+        <v>3.6624</v>
       </c>
       <c r="K3" t="n">
         <v>131</v>
@@ -575,7 +575,7 @@
         <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>6.010899999999999</v>
+        <v>6.0272</v>
       </c>
       <c r="N3" t="n">
         <v>307</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8536</v>
+        <v>5.8059</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5086</v>
+        <v>2.4882</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0405</v>
+        <v>2.0391</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8536</v>
+        <v>5.8059</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3763</v>
+        <v>2.329</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4773</v>
+        <v>3.4769</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4761</v>
+        <v>2.3873</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6054</v>
+        <v>2.5166</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4773</v>
+        <v>3.4769</v>
       </c>
       <c r="K4" t="n">
         <v>131</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0827</v>
+        <v>5.9935</v>
       </c>
       <c r="N4" t="n">
         <v>307</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6735</v>
+        <v>4.5368</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0029</v>
+        <v>1.9443</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5033</v>
+        <v>1.4609</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6735</v>
+        <v>4.5368</v>
       </c>
       <c r="F5" t="n">
-        <v>2.679</v>
+        <v>2.5946</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9945</v>
+        <v>1.9422</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1385</v>
+        <v>2.9959</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2194</v>
+        <v>3.076</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9945</v>
+        <v>1.9422</v>
       </c>
       <c r="K5" t="n">
         <v>134</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2139</v>
+        <v>5.0182</v>
       </c>
       <c r="N5" t="n">
         <v>270</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3635</v>
+        <v>4.2685</v>
       </c>
       <c r="C6" t="n">
-        <v>1.87</v>
+        <v>1.8293</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3622</v>
+        <v>1.3387</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3635</v>
+        <v>4.2685</v>
       </c>
       <c r="F6" t="n">
-        <v>2.853</v>
+        <v>2.8535</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5105</v>
+        <v>1.415</v>
       </c>
       <c r="H6" t="n">
-        <v>4.519</v>
+        <v>4.2706</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4402</v>
+        <v>2.3978</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5105</v>
+        <v>1.415</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9507</v>
+        <v>3.8128</v>
       </c>
       <c r="N6" t="n">
         <v>269</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1608</v>
+        <v>4.1449</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7831</v>
+        <v>1.7763</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2699</v>
+        <v>1.2824</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1608</v>
+        <v>4.1449</v>
       </c>
       <c r="F7" t="n">
-        <v>3.382</v>
+        <v>3.3322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7788</v>
+        <v>0.8127</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2642</v>
+        <v>6.068</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3826</v>
+        <v>3.407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7788</v>
+        <v>0.8127</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>154</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1614</v>
+        <v>4.2197</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.819</v>
+        <v>3.7512</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6367</v>
+        <v>1.6076</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1143</v>
+        <v>1.1031</v>
       </c>
       <c r="E8" t="n">
-        <v>3.819</v>
+        <v>3.7512</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9176</v>
+        <v>2.9133</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9014</v>
+        <v>0.8379</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7319</v>
+        <v>4.4954</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5552</v>
+        <v>2.524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9014</v>
+        <v>0.8379</v>
       </c>
       <c r="K8" t="n">
         <v>115</v>
@@ -805,7 +805,7 @@
         <v>154</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4566</v>
+        <v>3.3619</v>
       </c>
       <c r="N8" t="n">
         <v>269</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6161</v>
+        <v>3.5495</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5497</v>
+        <v>1.5212</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0219</v>
+        <v>1.0112</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6161</v>
+        <v>3.5495</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3707</v>
+        <v>2.2933</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2454</v>
+        <v>1.2562</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4639</v>
+        <v>2.3054</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5925</v>
+        <v>2.4303</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2454</v>
+        <v>1.2562</v>
       </c>
       <c r="K9" t="n">
         <v>131</v>
@@ -851,7 +851,7 @@
         <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8379</v>
+        <v>3.6865</v>
       </c>
       <c r="N9" t="n">
         <v>307</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4433</v>
+        <v>3.3986</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4756</v>
+        <v>1.4565</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9433</v>
+        <v>0.9424</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4433</v>
+        <v>3.3986</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0548</v>
+        <v>2.5286</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6115</v>
+        <v>0.87</v>
       </c>
       <c r="H10" t="n">
-        <v>8.484</v>
+        <v>3.0507</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5813</v>
+        <v>1.7129</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6115</v>
+        <v>0.87</v>
       </c>
       <c r="K10" t="n">
         <v>115</v>
@@ -897,7 +897,7 @@
         <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9698</v>
+        <v>2.5829</v>
       </c>
       <c r="N10" t="n">
         <v>269</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4329</v>
+        <v>3.3422</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4712</v>
+        <v>1.4323</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9385</v>
+        <v>0.9167</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4329</v>
+        <v>3.3422</v>
       </c>
       <c r="F11" t="n">
-        <v>2.485</v>
+        <v>3.9208</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9479</v>
+        <v>-0.5786</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3047</v>
+        <v>8.277900000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7845</v>
+        <v>4.6478</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9479</v>
+        <v>-0.5786</v>
       </c>
       <c r="K11" t="n">
         <v>115</v>
@@ -943,7 +943,7 @@
         <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7324</v>
+        <v>4.0692</v>
       </c>
       <c r="N11" t="n">
         <v>269</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3958</v>
+        <v>3.3008</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4553</v>
+        <v>1.4146</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9216</v>
+        <v>0.8979</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3958</v>
+        <v>3.3008</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7408</v>
+        <v>2.736</v>
       </c>
       <c r="G12" t="n">
-        <v>0.655</v>
+        <v>0.5648</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2737</v>
+        <v>3.32</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3581</v>
+        <v>3.4087</v>
       </c>
       <c r="J12" t="n">
-        <v>0.655</v>
+        <v>0.5648</v>
       </c>
       <c r="K12" t="n">
         <v>87</v>
@@ -989,7 +989,7 @@
         <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>4.0131</v>
+        <v>3.9735</v>
       </c>
       <c r="N12" t="n">
         <v>148</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3104</v>
+        <v>3.2355</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4187</v>
+        <v>1.3866</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8828</v>
+        <v>0.8681</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3104</v>
+        <v>3.2355</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7152</v>
+        <v>3.6047</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4048</v>
+        <v>-0.3692</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3636</v>
+        <v>7.0909</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9763</v>
+        <v>3.9813</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4048</v>
+        <v>-0.3692</v>
       </c>
       <c r="K13" t="n">
         <v>109</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5715</v>
+        <v>3.6121</v>
       </c>
       <c r="N13" t="n">
         <v>160</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2043</v>
+        <v>3.1615</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3732</v>
+        <v>1.3549</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8345</v>
+        <v>0.8344</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2043</v>
+        <v>3.1615</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7765</v>
+        <v>0.7509</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4278</v>
+        <v>2.4106</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7765</v>
+        <v>0.7509</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.7916</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4278</v>
+        <v>2.4106</v>
       </c>
       <c r="K14" t="n">
         <v>131</v>
@@ -1081,7 +1081,7 @@
         <v>176</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2448</v>
+        <v>3.2022</v>
       </c>
       <c r="N14" t="n">
         <v>307</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8381</v>
+        <v>2.8317</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2163</v>
+        <v>1.2135</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6842</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8381</v>
+        <v>2.8317</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8381</v>
+        <v>2.5624</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2693</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4868</v>
+        <v>3.1777</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4868</v>
+        <v>1.7842</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2693</v>
       </c>
       <c r="K15" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4868</v>
+        <v>2.0535</v>
       </c>
       <c r="N15" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8248</v>
+        <v>2.8298</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2106</v>
+        <v>1.2127</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6617</v>
+        <v>0.6833</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8248</v>
+        <v>2.8298</v>
       </c>
       <c r="F16" t="n">
-        <v>2.561</v>
+        <v>2.6076</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2638</v>
+        <v>0.2222</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5554</v>
+        <v>3.3473</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9199</v>
+        <v>1.8794</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2638</v>
+        <v>0.2222</v>
       </c>
       <c r="K16" t="n">
         <v>109</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1837</v>
+        <v>2.1016</v>
       </c>
       <c r="N16" t="n">
         <v>160</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8145</v>
+        <v>2.828</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2062</v>
+        <v>1.212</v>
       </c>
       <c r="D17" t="n">
-        <v>0.657</v>
+        <v>0.6825</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8145</v>
+        <v>2.828</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5173</v>
+        <v>2.828</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2972</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4113</v>
+        <v>3.5309</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8421</v>
+        <v>3.5309</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2972</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1393</v>
+        <v>3.5309</v>
       </c>
       <c r="N17" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4974</v>
+        <v>2.4995</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0703</v>
+        <v>1.0712</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5127</v>
+        <v>0.5329</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4974</v>
+        <v>2.4995</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1804</v>
+        <v>2.1926</v>
       </c>
       <c r="G18" t="n">
-        <v>0.317</v>
+        <v>0.3069</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2999</v>
+        <v>2.1926</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2419</v>
+        <v>1.2311</v>
       </c>
       <c r="J18" t="n">
-        <v>0.317</v>
+        <v>0.3069</v>
       </c>
       <c r="K18" t="n">
         <v>109</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5589</v>
+        <v>1.538</v>
       </c>
       <c r="N18" t="n">
         <v>160</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3405</v>
+        <v>2.3772</v>
       </c>
       <c r="C19" t="n">
-        <v>1.003</v>
+        <v>1.0188</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4412</v>
+        <v>0.4771</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3405</v>
+        <v>2.3772</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7139</v>
+        <v>2.7145</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3734</v>
+        <v>-0.3373</v>
       </c>
       <c r="H19" t="n">
-        <v>3.215</v>
+        <v>3.2707</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2978</v>
+        <v>3.3581</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3734</v>
+        <v>-0.3373</v>
       </c>
       <c r="K19" t="n">
         <v>87</v>
@@ -1311,7 +1311,7 @@
         <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9244</v>
+        <v>3.0208</v>
       </c>
       <c r="N19" t="n">
         <v>148</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2901</v>
+        <v>2.2667</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9714</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4183</v>
+        <v>0.4268</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2901</v>
+        <v>2.2667</v>
       </c>
       <c r="F20" t="n">
-        <v>2.571</v>
+        <v>2.5489</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2809</v>
+        <v>-0.2822</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9021</v>
+        <v>2.8911</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9021</v>
+        <v>2.8911</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2809</v>
+        <v>-0.2822</v>
       </c>
       <c r="K20" t="n">
         <v>85</v>
@@ -1357,7 +1357,7 @@
         <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6212</v>
+        <v>2.6089</v>
       </c>
       <c r="N20" t="n">
         <v>131</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9212</v>
+        <v>1.9497</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8233</v>
+        <v>0.8356</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2504</v>
+        <v>0.2824</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9212</v>
+        <v>1.9497</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3545</v>
+        <v>2.3481</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4333</v>
+        <v>-0.3984</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4282</v>
+        <v>2.431</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4908</v>
+        <v>2.496</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4333</v>
+        <v>-0.3984</v>
       </c>
       <c r="K21" t="n">
         <v>87</v>
@@ -1403,7 +1403,7 @@
         <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0575</v>
+        <v>2.0976</v>
       </c>
       <c r="N21" t="n">
         <v>148</v>
@@ -1412,231 +1412,231 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8115</v>
+        <v>1.7928</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7763</v>
+        <v>0.7683</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2004</v>
+        <v>0.2109</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8115</v>
+        <v>1.7928</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7161</v>
+        <v>2.0118</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0954</v>
+        <v>-0.219</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7161</v>
+        <v>2.0118</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7603</v>
+        <v>2.0118</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0954</v>
+        <v>-0.219</v>
       </c>
       <c r="K22" t="n">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="L22" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8557</v>
+        <v>1.7928</v>
       </c>
       <c r="N22" t="n">
-        <v>270</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7559</v>
+        <v>1.7305</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7416</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1751</v>
+        <v>0.1825</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7559</v>
+        <v>1.7305</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7559</v>
+        <v>1.5646</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7559</v>
+        <v>1.5646</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7559</v>
+        <v>1.6064</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7559</v>
+        <v>1.7723</v>
       </c>
       <c r="N23" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7486</v>
+        <v>1.651</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7494</v>
+        <v>0.7075</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1718</v>
+        <v>0.1463</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7486</v>
+        <v>1.651</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9546</v>
+        <v>1.651</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.206</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9546</v>
+        <v>1.651</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9546</v>
+        <v>1.651</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.206</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7486</v>
+        <v>1.651</v>
       </c>
       <c r="N24" t="n">
-        <v>131</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7041</v>
+        <v>1.6466</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7057</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1515</v>
+        <v>0.1443</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7041</v>
+        <v>1.6466</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5009</v>
+        <v>1.6646</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2032</v>
+        <v>-0.018</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5009</v>
+        <v>1.6646</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5396</v>
+        <v>1.6646</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2032</v>
+        <v>-0.018</v>
       </c>
       <c r="K25" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7428</v>
+        <v>1.6466</v>
       </c>
       <c r="N25" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5816</v>
+        <v>1.6232</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6778</v>
+        <v>0.6956</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0958</v>
+        <v>0.1337</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5816</v>
+        <v>1.6232</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6246</v>
+        <v>1.5918</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.043</v>
+        <v>0.0314</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6246</v>
+        <v>1.5918</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6246</v>
+        <v>1.6344</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.043</v>
+        <v>0.0314</v>
       </c>
       <c r="K26" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5816</v>
+        <v>1.6658</v>
       </c>
       <c r="N26" t="n">
-        <v>131</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="C27" t="n">
-        <v>0.651</v>
+        <v>0.655</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0673</v>
+        <v>0.0905</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5191</v>
+        <v>1.5284</v>
       </c>
       <c r="N27" t="n">
         <v>101</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4636</v>
+        <v>1.3309</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6272</v>
+        <v>0.5704</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0421</v>
+        <v>0.0005</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4636</v>
+        <v>1.3309</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1411</v>
+        <v>1.0744</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3225</v>
+        <v>0.2565</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1411</v>
+        <v>1.0744</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1705</v>
+        <v>1.1031</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3225</v>
+        <v>0.2565</v>
       </c>
       <c r="K28" t="n">
         <v>134</v>
@@ -1725,7 +1725,7 @@
         <v>136</v>
       </c>
       <c r="M28" t="n">
-        <v>1.493</v>
+        <v>1.3596</v>
       </c>
       <c r="N28" t="n">
         <v>270</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2655</v>
+        <v>1.3218</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5423</v>
+        <v>0.5665</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0481</v>
+        <v>-0.0036</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2655</v>
+        <v>1.3218</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3948</v>
+        <v>1.4337</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1293</v>
+        <v>-0.1119</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3948</v>
+        <v>1.4337</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4307</v>
+        <v>1.472</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1293</v>
+        <v>-0.1119</v>
       </c>
       <c r="K29" t="n">
         <v>87</v>
@@ -1771,7 +1771,7 @@
         <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3014</v>
+        <v>1.3601</v>
       </c>
       <c r="N29" t="n">
         <v>148</v>
@@ -1780,185 +1780,185 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2362</v>
+        <v>1.2054</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5298</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0615</v>
+        <v>-0.0567</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2362</v>
+        <v>1.2054</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5224</v>
+        <v>1.2537</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7138</v>
+        <v>-0.0483</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5224</v>
+        <v>1.2537</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5359</v>
+        <v>1.2537</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7138</v>
+        <v>-0.0483</v>
       </c>
       <c r="K30" t="n">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="L30" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2497</v>
+        <v>1.2054</v>
       </c>
       <c r="N30" t="n">
-        <v>270</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2093</v>
+        <v>1.092</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5183</v>
+        <v>0.468</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0737</v>
+        <v>-0.1083</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2093</v>
+        <v>1.092</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2416</v>
+        <v>1.092</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0323</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2416</v>
+        <v>1.092</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2416</v>
+        <v>1.092</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0323</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2093</v>
+        <v>1.092</v>
       </c>
       <c r="N31" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1613</v>
+        <v>1.0401</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4977</v>
+        <v>0.4457</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0956</v>
+        <v>-0.132</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1613</v>
+        <v>1.0401</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1613</v>
+        <v>0.4607</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.5794</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1613</v>
+        <v>0.4607</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1613</v>
+        <v>0.473</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.5794</v>
       </c>
       <c r="K32" t="n">
+        <v>134</v>
+      </c>
+      <c r="L32" t="n">
         <v>136</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
-        <v>1.1613</v>
+        <v>1.0524</v>
       </c>
       <c r="N32" t="n">
-        <v>136</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0384</v>
+        <v>1.011</v>
       </c>
       <c r="C33" t="n">
-        <v>0.445</v>
+        <v>0.4333</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1515</v>
+        <v>-0.1452</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0384</v>
+        <v>1.011</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7123</v>
+        <v>1.011</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3261</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7123</v>
+        <v>1.011</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7307</v>
+        <v>1.011</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3261</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L33" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0568</v>
+        <v>1.011</v>
       </c>
       <c r="N33" t="n">
-        <v>270</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4098</v>
+        <v>0.4262</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1889</v>
+        <v>-0.1528</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9563</v>
+        <v>0.9944</v>
       </c>
       <c r="N34" t="n">
         <v>124</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9204</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4097</v>
+        <v>0.3944</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.189</v>
+        <v>-0.1865</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9204</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9560999999999999</v>
+        <v>1.7934</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.873</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9560999999999999</v>
+        <v>1.7934</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9560999999999999</v>
+        <v>1.7934</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.873</v>
       </c>
       <c r="K35" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9204000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.8965</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3977</v>
+        <v>0.3842</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2018</v>
+        <v>-0.1974</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.8965</v>
       </c>
       <c r="F36" t="n">
-        <v>1.8005</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8726</v>
+        <v>0.1631</v>
       </c>
       <c r="H36" t="n">
-        <v>1.8005</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>1.8005</v>
+        <v>0.753</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8726</v>
+        <v>0.1631</v>
       </c>
       <c r="K36" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="L36" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9161</v>
       </c>
       <c r="N36" t="n">
-        <v>131</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2829</v>
+        <v>0.2885</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3237</v>
+        <v>-0.2991</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6601</v>
+        <v>0.6732</v>
       </c>
       <c r="N37" t="n">
         <v>136</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2318</v>
+        <v>0.1994</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3779</v>
+        <v>-0.3938</v>
       </c>
       <c r="E38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="F38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="I38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.541</v>
+        <v>0.4654</v>
       </c>
       <c r="N38" t="n">
         <v>136</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0369</v>
+        <v>0.0138</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5851</v>
+        <v>-0.5911</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="I39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="N39" t="n">
         <v>142</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0043</v>
+        <v>-0.0105</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.6197</v>
+        <v>-0.6169</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.01</v>
+        <v>-0.0245</v>
       </c>
       <c r="N40" t="n">
         <v>124</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.018</v>
+        <v>-0.0207</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6433</v>
+        <v>-0.6278</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0419</v>
+        <v>-0.0483</v>
       </c>
       <c r="N41" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.02</v>
+        <v>-0.0565</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6455</v>
+        <v>-0.6659</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0467</v>
+        <v>-0.1319</v>
       </c>
       <c r="N42" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0978</v>
+        <v>-0.0915</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7281</v>
+        <v>-0.703</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2282</v>
+        <v>-0.2134</v>
       </c>
       <c r="N43" t="n">
         <v>96</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1465</v>
+        <v>-0.1656</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7798</v>
+        <v>-0.7819</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3419</v>
+        <v>-0.3865</v>
       </c>
       <c r="N44" t="n">
         <v>124</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2303</v>
+        <v>-0.2172</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8689</v>
+        <v>-0.8367</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.5375</v>
+        <v>-0.5068</v>
       </c>
       <c r="N45" t="n">
         <v>142</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2605</v>
+        <v>-0.2344</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.9009</v>
+        <v>-0.855</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.6078</v>
+        <v>-0.547</v>
       </c>
       <c r="N46" t="n">
         <v>136</v>
@@ -2562,93 +2562,93 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3102</v>
+        <v>-0.2879</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9537</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.7239</v>
+        <v>-0.6718</v>
       </c>
       <c r="N47" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3117</v>
+        <v>-0.2986</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9553</v>
+        <v>-0.9232</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6967</v>
       </c>
       <c r="N48" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.366</v>
+        <v>-0.3607</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.013</v>
+        <v>-0.9892</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8541</v>
+        <v>-0.8417</v>
       </c>
       <c r="N49" t="n">
         <v>101</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.3806</v>
+        <v>-0.3805</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.0285</v>
+        <v>-1.0103</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8882</v>
+        <v>-0.8879</v>
       </c>
       <c r="N50" t="n">
         <v>96</v>
@@ -2746,139 +2746,139 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4425</v>
+        <v>-0.4247</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.0942</v>
+        <v>-1.0572</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.0325</v>
+        <v>-0.991</v>
       </c>
       <c r="N51" t="n">
-        <v>96</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4517</v>
+        <v>-0.438</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.104</v>
+        <v>-1.0714</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.0539</v>
+        <v>-1.0221</v>
       </c>
       <c r="N52" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.453</v>
+        <v>-0.4518</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.1054</v>
+        <v>-1.0861</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.0571</v>
+        <v>-1.0543</v>
       </c>
       <c r="N53" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6531</v>
+        <v>-0.656</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.3179</v>
+        <v>-1.3031</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.5239</v>
+        <v>-1.5308</v>
       </c>
       <c r="N54" t="n">
         <v>142</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-2.1591</v>
+        <v>-2.072</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.9253</v>
+        <v>-0.888</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.6071</v>
+        <v>-1.5497</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.1591</v>
+        <v>-2.072</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2876</v>
+        <v>-1.2027</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8693</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.2876</v>
+        <v>-1.2027</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6953</v>
+        <v>-0.6753</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8693</v>
       </c>
       <c r="K55" t="n">
         <v>109</v>
@@ -2967,7 +2967,7 @@
         <v>51</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.5668</v>
+        <v>-1.5446</v>
       </c>
       <c r="N55" t="n">
         <v>160</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.0044</v>
+        <v>-1.0006</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.6911</v>
+        <v>-1.6694</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-2.3438</v>
+        <v>-2.3349</v>
       </c>
       <c r="N56" t="n">
         <v>101</v>
@@ -3119,10 +3119,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5647</v>
+        <v>0.4943</v>
       </c>
       <c r="J2" t="n">
-        <v>20.3292</v>
+        <v>17.7948</v>
       </c>
     </row>
     <row r="3">
@@ -3159,10 +3159,10 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3878</v>
+        <v>0.3256</v>
       </c>
       <c r="J3" t="n">
-        <v>13.9608</v>
+        <v>11.7216</v>
       </c>
     </row>
     <row r="4">
@@ -3199,10 +3199,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1764</v>
+        <v>0.1379</v>
       </c>
       <c r="J4" t="n">
-        <v>6.3504</v>
+        <v>4.9644</v>
       </c>
     </row>
     <row r="5">
@@ -3239,10 +3239,10 @@
         <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1341</v>
+        <v>-0.1149</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.8276</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="6">
@@ -3279,10 +3279,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.146</v>
+        <v>-0.1263</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.256</v>
+        <v>-4.5468</v>
       </c>
     </row>
     <row r="7">
@@ -3319,10 +3319,10 @@
         <v>1.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2728</v>
+        <v>0.2589</v>
       </c>
       <c r="J7" t="n">
-        <v>9.8208</v>
+        <v>9.320399999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3359,10 +3359,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0348</v>
+        <v>0.0262</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2528</v>
+        <v>0.9432</v>
       </c>
     </row>
     <row r="9">
@@ -3399,10 +3399,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5848</v>
+        <v>-2.0808</v>
       </c>
     </row>
     <row r="10">
@@ -3439,10 +3439,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0982</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5352</v>
+        <v>-2.9376</v>
       </c>
     </row>
     <row r="11">
@@ -3479,10 +3479,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1574</v>
+        <v>-0.1374</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.6664</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="12">
@@ -3519,10 +3519,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.206</v>
+        <v>-0.1906</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.532</v>
+        <v>-4.1932</v>
       </c>
     </row>
     <row r="13">
@@ -3559,10 +3559,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.206</v>
+        <v>-0.1906</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.532</v>
+        <v>-4.1932</v>
       </c>
     </row>
     <row r="14">
@@ -3599,10 +3599,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2464</v>
+        <v>-0.2313</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.4208</v>
+        <v>-5.0886</v>
       </c>
     </row>
     <row r="15">
@@ -3639,10 +3639,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3286</v>
+        <v>-0.3141</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.2292</v>
+        <v>-6.9102</v>
       </c>
     </row>
     <row r="16">
@@ -3679,10 +3679,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4797</v>
+        <v>-0.4758</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.5534</v>
+        <v>-10.4676</v>
       </c>
     </row>
     <row r="17">
@@ -3719,10 +3719,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0727</v>
+        <v>1.075</v>
       </c>
       <c r="J17" t="n">
-        <v>23.5994</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="18">
@@ -3759,10 +3759,10 @@
         <v>1.47</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0545</v>
+        <v>1.055</v>
       </c>
       <c r="J18" t="n">
-        <v>23.199</v>
+        <v>23.21</v>
       </c>
     </row>
     <row r="19">
@@ -3799,10 +3799,10 @@
         <v>1.44</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9996</v>
+        <v>0.9951</v>
       </c>
       <c r="J19" t="n">
-        <v>21.9912</v>
+        <v>21.8922</v>
       </c>
     </row>
     <row r="20">
@@ -3839,10 +3839,10 @@
         <v>1.15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4146</v>
+        <v>0.3829</v>
       </c>
       <c r="J20" t="n">
-        <v>9.1212</v>
+        <v>8.4238</v>
       </c>
     </row>
     <row r="21">
@@ -3879,10 +3879,10 @@
         <v>1.08</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2363</v>
+        <v>0.2059</v>
       </c>
       <c r="J21" t="n">
-        <v>5.1986</v>
+        <v>4.5298</v>
       </c>
     </row>
     <row r="22">
@@ -3919,10 +3919,10 @@
         <v>0.84</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1838</v>
+        <v>-0.1683</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.8598</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="23">
@@ -3959,10 +3959,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1945</v>
+        <v>-0.179</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.0845</v>
+        <v>-3.759</v>
       </c>
     </row>
     <row r="24">
@@ -3999,10 +3999,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2554</v>
+        <v>-0.2405</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3634</v>
+        <v>-5.0505</v>
       </c>
     </row>
     <row r="25">
@@ -4039,10 +4039,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.319</v>
+        <v>-0.3046</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.699</v>
+        <v>-6.3966</v>
       </c>
     </row>
     <row r="26">
@@ -4079,10 +4079,10 @@
         <v>0.46</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5314</v>
+        <v>-0.5339</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.1594</v>
+        <v>-11.2119</v>
       </c>
     </row>
     <row r="27">
@@ -4119,10 +4119,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3032</v>
+        <v>1.3335</v>
       </c>
       <c r="J27" t="n">
-        <v>27.3672</v>
+        <v>28.0035</v>
       </c>
     </row>
     <row r="28">
@@ -4159,10 +4159,10 @@
         <v>1.59</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2516</v>
+        <v>1.276</v>
       </c>
       <c r="J28" t="n">
-        <v>26.2836</v>
+        <v>26.796</v>
       </c>
     </row>
     <row r="29">
@@ -4199,10 +4199,10 @@
         <v>1.48</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0589</v>
+        <v>1.0633</v>
       </c>
       <c r="J29" t="n">
-        <v>22.2369</v>
+        <v>22.3293</v>
       </c>
     </row>
     <row r="30">
@@ -4239,10 +4239,10 @@
         <v>1.32</v>
       </c>
       <c r="I30" t="n">
-        <v>0.766</v>
+        <v>0.7494</v>
       </c>
       <c r="J30" t="n">
-        <v>16.086</v>
+        <v>15.7374</v>
       </c>
     </row>
     <row r="31">
@@ -4279,10 +4279,10 @@
         <v>1.02</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0342</v>
+        <v>0.0155</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.3255</v>
       </c>
     </row>
     <row r="32">
@@ -4319,10 +4319,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.452</v>
+        <v>0.4046</v>
       </c>
       <c r="J32" t="n">
-        <v>11.3</v>
+        <v>10.115</v>
       </c>
     </row>
     <row r="33">
@@ -4359,10 +4359,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2868</v>
+        <v>0.2392</v>
       </c>
       <c r="J33" t="n">
-        <v>7.17</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="34">
@@ -4399,10 +4399,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1364</v>
+        <v>-0.1202</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.41</v>
+        <v>-3.005</v>
       </c>
     </row>
     <row r="35">
@@ -4439,10 +4439,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3062</v>
+        <v>-0.2886</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.655</v>
+        <v>-7.215</v>
       </c>
     </row>
     <row r="36">
@@ -4479,10 +4479,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6129</v>
+        <v>-0.6304</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.3225</v>
+        <v>-15.76</v>
       </c>
     </row>
     <row r="37">
@@ -4519,10 +4519,10 @@
         <v>1.73</v>
       </c>
       <c r="I37" t="n">
-        <v>1.24</v>
+        <v>1.239</v>
       </c>
       <c r="J37" t="n">
-        <v>31</v>
+        <v>30.975</v>
       </c>
     </row>
     <row r="38">
@@ -4559,10 +4559,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7892</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>19.73</v>
+        <v>19.3925</v>
       </c>
     </row>
     <row r="39">
@@ -4599,10 +4599,10 @@
         <v>1.24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5727</v>
+        <v>0.5675</v>
       </c>
       <c r="J39" t="n">
-        <v>14.3175</v>
+        <v>14.1875</v>
       </c>
     </row>
     <row r="40">
@@ -4639,10 +4639,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4402</v>
+        <v>0.4118</v>
       </c>
       <c r="J40" t="n">
-        <v>11.005</v>
+        <v>10.295</v>
       </c>
     </row>
     <row r="41">
@@ -4679,10 +4679,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3404</v>
+        <v>-0.3022</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.51</v>
+        <v>-7.555</v>
       </c>
     </row>
     <row r="42">
@@ -4719,10 +4719,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6232</v>
+        <v>0.5955</v>
       </c>
       <c r="J42" t="n">
-        <v>16.2032</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="43">
@@ -4759,10 +4759,10 @@
         <v>0.99</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.598</v>
+        <v>-0.442</v>
       </c>
     </row>
     <row r="44">
@@ -4799,10 +4799,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1548</v>
+        <v>-0.1353</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.0248</v>
+        <v>-3.5178</v>
       </c>
     </row>
     <row r="45">
@@ -4839,10 +4839,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2586</v>
+        <v>-0.2389</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.7236</v>
+        <v>-6.2114</v>
       </c>
     </row>
     <row r="46">
@@ -4879,10 +4879,10 @@
         <v>0.78</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2684</v>
+        <v>-0.249</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.9784</v>
+        <v>-6.474</v>
       </c>
     </row>
     <row r="47">
@@ -4919,10 +4919,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0763</v>
+        <v>1.0711</v>
       </c>
       <c r="J47" t="n">
-        <v>27.9838</v>
+        <v>27.8486</v>
       </c>
     </row>
     <row r="48">
@@ -4959,10 +4959,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.501</v>
+        <v>0.4819</v>
       </c>
       <c r="J48" t="n">
-        <v>13.026</v>
+        <v>12.5294</v>
       </c>
     </row>
     <row r="49">
@@ -4999,10 +4999,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3282</v>
+        <v>-0.2861</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.533200000000001</v>
+        <v>-7.4386</v>
       </c>
     </row>
     <row r="50">
@@ -5039,10 +5039,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4824</v>
+        <v>-0.4401</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.5424</v>
+        <v>-11.4426</v>
       </c>
     </row>
     <row r="51">
@@ -5079,10 +5079,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5306</v>
+        <v>-0.4896</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.7956</v>
+        <v>-12.7296</v>
       </c>
     </row>
     <row r="52">
@@ -5119,10 +5119,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2864</v>
+        <v>0.2741</v>
       </c>
       <c r="J52" t="n">
-        <v>7.4464</v>
+        <v>7.1266</v>
       </c>
     </row>
     <row r="53">
@@ -5159,10 +5159,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2571</v>
+        <v>0.2428</v>
       </c>
       <c r="J53" t="n">
-        <v>6.6846</v>
+        <v>6.3128</v>
       </c>
     </row>
     <row r="54">
@@ -5199,10 +5199,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1515</v>
+        <v>-0.1329</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.939</v>
+        <v>-3.4554</v>
       </c>
     </row>
     <row r="55">
@@ -5239,10 +5239,10 @@
         <v>0.75</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2934</v>
+        <v>-0.275</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.6284</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="56">
@@ -5279,10 +5279,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3586</v>
+        <v>-0.3441</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.323600000000001</v>
+        <v>-8.9466</v>
       </c>
     </row>
     <row r="57">
@@ -5319,10 +5319,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4066</v>
+        <v>0.3437</v>
       </c>
       <c r="J57" t="n">
-        <v>10.5716</v>
+        <v>8.936199999999999</v>
       </c>
     </row>
     <row r="58">
@@ -5359,10 +5359,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.302</v>
+        <v>0.2481</v>
       </c>
       <c r="J58" t="n">
-        <v>7.852</v>
+        <v>6.4506</v>
       </c>
     </row>
     <row r="59">
@@ -5399,10 +5399,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2655</v>
+        <v>0.2157</v>
       </c>
       <c r="J59" t="n">
-        <v>6.903</v>
+        <v>5.6082</v>
       </c>
     </row>
     <row r="60">
@@ -5439,10 +5439,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2017</v>
+        <v>0.1602</v>
       </c>
       <c r="J60" t="n">
-        <v>5.2442</v>
+        <v>4.1652</v>
       </c>
     </row>
     <row r="61">
@@ -5479,10 +5479,10 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0111</v>
+        <v>-0.0086</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.2886</v>
+        <v>-0.2236</v>
       </c>
     </row>
     <row r="62">
@@ -5519,10 +5519,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9228</v>
+        <v>0.9095</v>
       </c>
       <c r="J62" t="n">
-        <v>21.2244</v>
+        <v>20.9185</v>
       </c>
     </row>
     <row r="63">
@@ -5559,10 +5559,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7723</v>
+        <v>0.7599</v>
       </c>
       <c r="J63" t="n">
-        <v>17.7629</v>
+        <v>17.4777</v>
       </c>
     </row>
     <row r="64">
@@ -5599,10 +5599,10 @@
         <v>1.35</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7304</v>
+        <v>0.7191</v>
       </c>
       <c r="J64" t="n">
-        <v>16.7992</v>
+        <v>16.5393</v>
       </c>
     </row>
     <row r="65">
@@ -5639,10 +5639,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4562</v>
+        <v>0.432</v>
       </c>
       <c r="J65" t="n">
-        <v>10.4926</v>
+        <v>9.936</v>
       </c>
     </row>
     <row r="66">
@@ -5679,10 +5679,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4562</v>
+        <v>0.432</v>
       </c>
       <c r="J66" t="n">
-        <v>10.4926</v>
+        <v>9.936</v>
       </c>
     </row>
     <row r="67">
@@ -5719,10 +5719,10 @@
         <v>1.04</v>
       </c>
       <c r="I67" t="n">
-        <v>0.163</v>
+        <v>0.129</v>
       </c>
       <c r="J67" t="n">
-        <v>3.749</v>
+        <v>2.967</v>
       </c>
     </row>
     <row r="68">
@@ -5759,10 +5759,10 @@
         <v>1.02</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1092</v>
+        <v>0.0835</v>
       </c>
       <c r="J68" t="n">
-        <v>2.5116</v>
+        <v>1.9205</v>
       </c>
     </row>
     <row r="69">
@@ -5799,10 +5799,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1555</v>
+        <v>-0.1391</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.5765</v>
+        <v>-3.1993</v>
       </c>
     </row>
     <row r="70">
@@ -5839,10 +5839,10 @@
         <v>0.79</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2459</v>
+        <v>-0.2275</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.6557</v>
+        <v>-5.2325</v>
       </c>
     </row>
     <row r="71">
@@ -5879,10 +5879,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5851</v>
+        <v>-0.5974</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.4573</v>
+        <v>-13.7402</v>
       </c>
     </row>
     <row r="72">
@@ -5919,10 +5919,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0696</v>
+        <v>1.0596</v>
       </c>
       <c r="J72" t="n">
-        <v>27.8096</v>
+        <v>27.5496</v>
       </c>
     </row>
     <row r="73">
@@ -5959,10 +5959,10 @@
         <v>1.36</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7532</v>
+        <v>0.7391</v>
       </c>
       <c r="J73" t="n">
-        <v>19.5832</v>
+        <v>19.2166</v>
       </c>
     </row>
     <row r="74">
@@ -5999,10 +5999,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3796</v>
+        <v>0.3465</v>
       </c>
       <c r="J74" t="n">
-        <v>9.8696</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="75">
@@ -6039,10 +6039,10 @@
         <v>1.11</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3295</v>
+        <v>0.2971</v>
       </c>
       <c r="J75" t="n">
-        <v>8.567</v>
+        <v>7.7246</v>
       </c>
     </row>
     <row r="76">
@@ -6079,10 +6079,10 @@
         <v>1.01</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0193</v>
+        <v>0.0094</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5018</v>
+        <v>0.2444</v>
       </c>
     </row>
     <row r="77">
@@ -6119,10 +6119,10 @@
         <v>1.12</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3255</v>
+        <v>0.2755</v>
       </c>
       <c r="J77" t="n">
-        <v>8.462999999999999</v>
+        <v>7.163</v>
       </c>
     </row>
     <row r="78">
@@ -6159,10 +6159,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1998</v>
+        <v>0.1596</v>
       </c>
       <c r="J78" t="n">
-        <v>5.1948</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="79">
@@ -6199,10 +6199,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1368</v>
+        <v>-0.1204</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.5568</v>
+        <v>-3.1304</v>
       </c>
     </row>
     <row r="80">
@@ -6239,10 +6239,10 @@
         <v>0.67</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.362</v>
+        <v>-0.3476</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.412000000000001</v>
+        <v>-9.037599999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6279,10 +6279,10 @@
         <v>0.57</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4512</v>
+        <v>-0.4451</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.7312</v>
+        <v>-11.5726</v>
       </c>
     </row>
     <row r="82">
@@ -6319,10 +6319,10 @@
         <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1288</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>3.6064</v>
+        <v>2.7188</v>
       </c>
     </row>
     <row r="83">
@@ -6359,10 +6359,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1039</v>
+        <v>0.0765</v>
       </c>
       <c r="J83" t="n">
-        <v>2.9092</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="84">
@@ -6399,10 +6399,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J84" t="n">
-        <v>1.3048</v>
+        <v>0.8736</v>
       </c>
     </row>
     <row r="85">
@@ -6439,10 +6439,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0707</v>
+        <v>-0.0571</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.9796</v>
+        <v>-1.5988</v>
       </c>
     </row>
     <row r="86">
@@ -6479,10 +6479,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2298</v>
+        <v>-0.2094</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.4344</v>
+        <v>-5.8632</v>
       </c>
     </row>
     <row r="87">
@@ -6519,10 +6519,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8699</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>24.3572</v>
+        <v>23.9204</v>
       </c>
     </row>
     <row r="88">
@@ -6559,10 +6559,10 @@
         <v>1.23</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5703</v>
+        <v>0.5604</v>
       </c>
       <c r="J88" t="n">
-        <v>15.9684</v>
+        <v>15.6912</v>
       </c>
     </row>
     <row r="89">
@@ -6599,10 +6599,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4366</v>
+        <v>0.4024</v>
       </c>
       <c r="J89" t="n">
-        <v>12.2248</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="90">
@@ -6639,10 +6639,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4366</v>
+        <v>0.4024</v>
       </c>
       <c r="J90" t="n">
-        <v>12.2248</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="91">
@@ -6679,10 +6679,10 @@
         <v>0.79</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6054</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.9088</v>
+        <v>-16.9512</v>
       </c>
     </row>
     <row r="92">
@@ -6719,10 +6719,10 @@
         <v>0.99</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0277</v>
+        <v>0.0391</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4986</v>
+        <v>0.7038</v>
       </c>
     </row>
     <row r="93">
@@ -6759,10 +6759,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1611</v>
+        <v>-0.1454</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.8998</v>
+        <v>-2.6172</v>
       </c>
     </row>
     <row r="94">
@@ -6799,10 +6799,10 @@
         <v>0.71</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3099</v>
+        <v>-0.2955</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.5782</v>
+        <v>-5.319</v>
       </c>
     </row>
     <row r="95">
@@ -6839,10 +6839,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3275</v>
+        <v>-0.3134</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.895</v>
+        <v>-5.6412</v>
       </c>
     </row>
     <row r="96">
@@ -6879,10 +6879,10 @@
         <v>0.33</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6428</v>
+        <v>-0.6636</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.5704</v>
+        <v>-11.9448</v>
       </c>
     </row>
     <row r="97">
@@ -6919,10 +6919,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5218</v>
+        <v>1.5411</v>
       </c>
       <c r="J97" t="n">
-        <v>27.3924</v>
+        <v>27.7398</v>
       </c>
     </row>
     <row r="98">
@@ -6959,10 +6959,10 @@
         <v>1.77</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2499</v>
+        <v>1.25</v>
       </c>
       <c r="J98" t="n">
-        <v>22.4982</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="99">
@@ -6999,10 +6999,10 @@
         <v>1.39</v>
       </c>
       <c r="I99" t="n">
-        <v>0.771</v>
+        <v>0.7645</v>
       </c>
       <c r="J99" t="n">
-        <v>13.878</v>
+        <v>13.761</v>
       </c>
     </row>
     <row r="100">
@@ -7039,10 +7039,10 @@
         <v>1.27</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5972</v>
+        <v>0.5945</v>
       </c>
       <c r="J100" t="n">
-        <v>10.7496</v>
+        <v>10.701</v>
       </c>
     </row>
     <row r="101">
@@ -7079,10 +7079,10 @@
         <v>1.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1232</v>
+        <v>0.0935</v>
       </c>
       <c r="J101" t="n">
-        <v>2.2176</v>
+        <v>1.683</v>
       </c>
     </row>
     <row r="102">
@@ -7119,10 +7119,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.465</v>
+        <v>0.4182</v>
       </c>
       <c r="J102" t="n">
-        <v>11.625</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="103">
@@ -7159,10 +7159,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0669</v>
+        <v>-0.055</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.6725</v>
+        <v>-1.375</v>
       </c>
     </row>
     <row r="104">
@@ -7199,10 +7199,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1289</v>
+        <v>-0.1117</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.2225</v>
+        <v>-2.7925</v>
       </c>
     </row>
     <row r="105">
@@ -7239,10 +7239,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2736</v>
+        <v>-0.2545</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.84</v>
+        <v>-6.3625</v>
       </c>
     </row>
     <row r="106">
@@ -7279,10 +7279,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.321</v>
+        <v>-0.304</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.025</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="107">
@@ -7319,10 +7319,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1485</v>
+        <v>1.1434</v>
       </c>
       <c r="J107" t="n">
-        <v>28.7125</v>
+        <v>28.585</v>
       </c>
     </row>
     <row r="108">
@@ -7359,10 +7359,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4329</v>
+        <v>0.4001</v>
       </c>
       <c r="J108" t="n">
-        <v>10.8225</v>
+        <v>10.0025</v>
       </c>
     </row>
     <row r="109">
@@ -7399,10 +7399,10 @@
         <v>1.07</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2307</v>
+        <v>0.2008</v>
       </c>
       <c r="J109" t="n">
-        <v>5.7675</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="110">
@@ -7439,10 +7439,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1715</v>
+        <v>0.1452</v>
       </c>
       <c r="J110" t="n">
-        <v>4.2875</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="111">
@@ -7479,10 +7479,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1062</v>
+        <v>0.0857</v>
       </c>
       <c r="J111" t="n">
-        <v>2.655</v>
+        <v>2.1425</v>
       </c>
     </row>
     <row r="112">
@@ -7519,10 +7519,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J112" t="n">
-        <v>9.723599999999999</v>
+        <v>7.9956</v>
       </c>
     </row>
     <row r="113">
@@ -7559,10 +7559,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.19</v>
+        <v>0.1505</v>
       </c>
       <c r="J113" t="n">
-        <v>6.84</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="114">
@@ -7599,10 +7599,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.0144</v>
+        <v>-0.0072</v>
       </c>
     </row>
     <row r="115">
@@ -7639,10 +7639,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0998</v>
+        <v>-0.0828</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.5928</v>
+        <v>-2.9808</v>
       </c>
     </row>
     <row r="116">
@@ -7679,10 +7679,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1123</v>
+        <v>-0.0944</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.0428</v>
+        <v>-3.3984</v>
       </c>
     </row>
     <row r="117">
@@ -7719,10 +7719,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6871</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>24.7356</v>
+        <v>24.1884</v>
       </c>
     </row>
     <row r="118">
@@ -7759,10 +7759,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4777</v>
+        <v>0.4521</v>
       </c>
       <c r="J118" t="n">
-        <v>17.1972</v>
+        <v>16.2756</v>
       </c>
     </row>
     <row r="119">
@@ -7799,10 +7799,10 @@
         <v>1.13</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3973</v>
+        <v>0.3585</v>
       </c>
       <c r="J119" t="n">
-        <v>14.3028</v>
+        <v>12.906</v>
       </c>
     </row>
     <row r="120">
@@ -7839,10 +7839,10 @@
         <v>1.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2152</v>
+        <v>0.1844</v>
       </c>
       <c r="J120" t="n">
-        <v>7.7472</v>
+        <v>6.6384</v>
       </c>
     </row>
     <row r="121">
@@ -7879,10 +7879,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4405</v>
+        <v>-0.398</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.858</v>
+        <v>-14.328</v>
       </c>
     </row>
     <row r="122">
@@ -7919,10 +7919,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8781</v>
+        <v>0.8587</v>
       </c>
       <c r="J122" t="n">
-        <v>25.4649</v>
+        <v>24.9023</v>
       </c>
     </row>
     <row r="123">
@@ -7959,10 +7959,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8583</v>
+        <v>0.8373</v>
       </c>
       <c r="J123" t="n">
-        <v>24.8907</v>
+        <v>24.2817</v>
       </c>
     </row>
     <row r="124">
@@ -7999,10 +7999,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3648</v>
+        <v>0.3301</v>
       </c>
       <c r="J124" t="n">
-        <v>10.5792</v>
+        <v>9.572900000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8039,10 +8039,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2877</v>
+        <v>0.2551</v>
       </c>
       <c r="J125" t="n">
-        <v>8.343299999999999</v>
+        <v>7.3979</v>
       </c>
     </row>
     <row r="126">
@@ -8079,10 +8079,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2011</v>
+        <v>-0.1665</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.8319</v>
+        <v>-4.8285</v>
       </c>
     </row>
     <row r="127">
@@ -8119,10 +8119,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1122</v>
+        <v>0.083</v>
       </c>
       <c r="J127" t="n">
-        <v>3.2538</v>
+        <v>2.407</v>
       </c>
     </row>
     <row r="128">
@@ -8159,10 +8159,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1122</v>
+        <v>0.083</v>
       </c>
       <c r="J128" t="n">
-        <v>3.2538</v>
+        <v>2.407</v>
       </c>
     </row>
     <row r="129">
@@ -8199,10 +8199,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1296</v>
+        <v>-0.112</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.7584</v>
+        <v>-3.248</v>
       </c>
     </row>
     <row r="130">
@@ -8239,10 +8239,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1409</v>
+        <v>-0.1226</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.0861</v>
+        <v>-3.5554</v>
       </c>
     </row>
     <row r="131">
@@ -8279,10 +8279,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2844</v>
+        <v>-0.2656</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.2476</v>
+        <v>-7.7024</v>
       </c>
     </row>
     <row r="132">
@@ -8319,10 +8319,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8743</v>
+        <v>0.855</v>
       </c>
       <c r="J132" t="n">
-        <v>20.1089</v>
+        <v>19.665</v>
       </c>
     </row>
     <row r="133">
@@ -8359,10 +8359,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8348</v>
+        <v>0.8125</v>
       </c>
       <c r="J133" t="n">
-        <v>19.2004</v>
+        <v>18.6875</v>
       </c>
     </row>
     <row r="134">
@@ -8399,10 +8399,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4806</v>
+        <v>0.4455</v>
       </c>
       <c r="J134" t="n">
-        <v>11.0538</v>
+        <v>10.2465</v>
       </c>
     </row>
     <row r="135">
@@ -8439,10 +8439,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1709</v>
+        <v>0.1446</v>
       </c>
       <c r="J135" t="n">
-        <v>3.9307</v>
+        <v>3.3258</v>
       </c>
     </row>
     <row r="136">
@@ -8479,10 +8479,10 @@
         <v>1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1392</v>
+        <v>0.1154</v>
       </c>
       <c r="J136" t="n">
-        <v>3.2016</v>
+        <v>2.6542</v>
       </c>
     </row>
     <row r="137">
@@ -8519,10 +8519,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2186</v>
+        <v>0.1751</v>
       </c>
       <c r="J137" t="n">
-        <v>5.0278</v>
+        <v>4.0273</v>
       </c>
     </row>
     <row r="138">
@@ -8559,10 +8559,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0779</v>
+        <v>0.0553</v>
       </c>
       <c r="J138" t="n">
-        <v>1.7917</v>
+        <v>1.2719</v>
       </c>
     </row>
     <row r="139">
@@ -8599,10 +8599,10 @@
         <v>0.97</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0564</v>
+        <v>-0.0447</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.2972</v>
+        <v>-1.0281</v>
       </c>
     </row>
     <row r="140">
@@ -8639,10 +8639,10 @@
         <v>0.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.5719</v>
+        <v>-3.1211</v>
       </c>
     </row>
     <row r="141">
@@ -8679,10 +8679,10 @@
         <v>0.87</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1772</v>
+        <v>-0.157</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.0756</v>
+        <v>-3.611</v>
       </c>
     </row>
     <row r="142">
@@ -8719,10 +8719,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1494</v>
+        <v>1.1627</v>
       </c>
       <c r="J142" t="n">
-        <v>29.8844</v>
+        <v>30.2302</v>
       </c>
     </row>
     <row r="143">
@@ -8759,10 +8759,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7768</v>
+        <v>0.7504</v>
       </c>
       <c r="J143" t="n">
-        <v>20.1968</v>
+        <v>19.5104</v>
       </c>
     </row>
     <row r="144">
@@ -8799,10 +8799,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3131</v>
+        <v>0.2798</v>
       </c>
       <c r="J144" t="n">
-        <v>8.140599999999999</v>
+        <v>7.2748</v>
       </c>
     </row>
     <row r="145">
@@ -8839,10 +8839,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0902</v>
+        <v>-0.0692</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.3452</v>
+        <v>-1.7992</v>
       </c>
     </row>
     <row r="146">
@@ -8879,10 +8879,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1317</v>
+        <v>-0.1044</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.4242</v>
+        <v>-2.7144</v>
       </c>
     </row>
     <row r="147">
@@ -8919,10 +8919,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8642</v>
+        <v>0.8217</v>
       </c>
       <c r="J147" t="n">
-        <v>22.4692</v>
+        <v>21.3642</v>
       </c>
     </row>
     <row r="148">
@@ -8959,10 +8959,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.47</v>
+        <v>-2.0722</v>
       </c>
     </row>
     <row r="149">
@@ -8999,10 +8999,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.107</v>
+        <v>-0.0907</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.782</v>
+        <v>-2.3582</v>
       </c>
     </row>
     <row r="150">
@@ -9039,10 +9039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2367</v>
+        <v>-0.2166</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.1542</v>
+        <v>-5.6316</v>
       </c>
     </row>
     <row r="151">
@@ -9079,10 +9079,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4754</v>
+        <v>-0.473</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3604</v>
+        <v>-12.298</v>
       </c>
     </row>
     <row r="152">
@@ -9119,10 +9119,10 @@
         <v>1.23</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5262</v>
+        <v>0.4726</v>
       </c>
       <c r="J152" t="n">
-        <v>13.155</v>
+        <v>11.815</v>
       </c>
     </row>
     <row r="153">
@@ -9159,10 +9159,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3051</v>
+        <v>0.2561</v>
       </c>
       <c r="J153" t="n">
-        <v>7.6275</v>
+        <v>6.4025</v>
       </c>
     </row>
     <row r="154">
@@ -9199,10 +9199,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3068</v>
+        <v>-0.2892</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.67</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="155">
@@ -9239,10 +9239,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3893</v>
+        <v>-0.3771</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.7325</v>
+        <v>-9.4275</v>
       </c>
     </row>
     <row r="156">
@@ -9279,10 +9279,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4072</v>
+        <v>-0.3966</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.18</v>
+        <v>-9.914999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9319,10 @@
         <v>1.81</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4767</v>
+        <v>1.507</v>
       </c>
       <c r="J157" t="n">
-        <v>36.9175</v>
+        <v>37.675</v>
       </c>
     </row>
     <row r="158">
@@ -9359,10 +9359,10 @@
         <v>1.37</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8681</v>
+        <v>0.8542</v>
       </c>
       <c r="J158" t="n">
-        <v>21.7025</v>
+        <v>21.355</v>
       </c>
     </row>
     <row r="159">
@@ -9399,10 +9399,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.696</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>17.4</v>
+        <v>16.8225</v>
       </c>
     </row>
     <row r="160">
@@ -9439,10 +9439,10 @@
         <v>1.18</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4827</v>
+        <v>0.4522</v>
       </c>
       <c r="J160" t="n">
-        <v>12.0675</v>
+        <v>11.305</v>
       </c>
     </row>
     <row r="161">
@@ -9479,10 +9479,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0818</v>
+        <v>0.0605</v>
       </c>
       <c r="J161" t="n">
-        <v>2.045</v>
+        <v>1.5125</v>
       </c>
     </row>
     <row r="162">
@@ -9519,10 +9519,10 @@
         <v>1.71</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3503</v>
+        <v>1.3722</v>
       </c>
       <c r="J162" t="n">
-        <v>31.0569</v>
+        <v>31.5606</v>
       </c>
     </row>
     <row r="163">
@@ -9559,10 +9559,10 @@
         <v>1.52</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1055</v>
+        <v>1.1185</v>
       </c>
       <c r="J163" t="n">
-        <v>25.4265</v>
+        <v>25.7255</v>
       </c>
     </row>
     <row r="164">
@@ -9599,10 +9599,10 @@
         <v>1.33</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7748</v>
       </c>
       <c r="J164" t="n">
-        <v>18.2344</v>
+        <v>17.8204</v>
       </c>
     </row>
     <row r="165">
@@ -9639,10 +9639,10 @@
         <v>1.13</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3634</v>
+        <v>0.3314</v>
       </c>
       <c r="J165" t="n">
-        <v>8.3582</v>
+        <v>7.6222</v>
       </c>
     </row>
     <row r="166">
@@ -9679,10 +9679,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.044</v>
+        <v>0.0266</v>
       </c>
       <c r="J166" t="n">
-        <v>1.012</v>
+        <v>0.6118</v>
       </c>
     </row>
     <row r="167">
@@ -9719,10 +9719,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4742</v>
+        <v>0.4337</v>
       </c>
       <c r="J167" t="n">
-        <v>10.9066</v>
+        <v>9.975099999999999</v>
       </c>
     </row>
     <row r="168">
@@ -9759,10 +9759,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2853</v>
+        <v>-0.2698</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.5619</v>
+        <v>-6.2054</v>
       </c>
     </row>
     <row r="169">
@@ -9799,10 +9799,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3303</v>
+        <v>-0.3154</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.5969</v>
+        <v>-7.2542</v>
       </c>
     </row>
     <row r="170">
@@ -9839,10 +9839,10 @@
         <v>0.63</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3843</v>
+        <v>-0.3719</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.838900000000001</v>
+        <v>-8.553699999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9879,10 +9879,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5173</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.8818</v>
+        <v>-11.8979</v>
       </c>
     </row>
     <row r="172">
@@ -9919,10 +9919,10 @@
         <v>1.27</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.6943</v>
       </c>
       <c r="J172" t="n">
-        <v>30.5046</v>
+        <v>29.1606</v>
       </c>
     </row>
     <row r="173">
@@ -9959,10 +9959,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6484</v>
       </c>
       <c r="J173" t="n">
-        <v>28.686</v>
+        <v>27.2328</v>
       </c>
     </row>
     <row r="174">
@@ -9999,10 +9999,10 @@
         <v>1.03</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1288</v>
+        <v>0.1042</v>
       </c>
       <c r="J174" t="n">
-        <v>5.4096</v>
+        <v>4.3764</v>
       </c>
     </row>
     <row r="175">
@@ -10039,10 +10039,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4049</v>
+        <v>-0.3618</v>
       </c>
       <c r="J175" t="n">
-        <v>-17.0058</v>
+        <v>-15.1956</v>
       </c>
     </row>
     <row r="176">
@@ -10079,10 +10079,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5043</v>
+        <v>-0.4624</v>
       </c>
       <c r="J176" t="n">
-        <v>-21.1806</v>
+        <v>-19.4208</v>
       </c>
     </row>
     <row r="177">
@@ -10119,10 +10119,10 @@
         <v>1.09</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2317</v>
+        <v>0.1873</v>
       </c>
       <c r="J177" t="n">
-        <v>9.731400000000001</v>
+        <v>7.8666</v>
       </c>
     </row>
     <row r="178">
@@ -10159,10 +10159,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1907</v>
+        <v>0.151</v>
       </c>
       <c r="J178" t="n">
-        <v>8.009399999999999</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="179">
@@ -10199,10 +10199,10 @@
         <v>0.99</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0256</v>
+        <v>-0.0183</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.0752</v>
+        <v>-0.7685999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -10239,10 +10239,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0256</v>
+        <v>-0.0183</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.0752</v>
+        <v>-0.7685999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -10279,10 +10279,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1587</v>
+        <v>-0.1387</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.6654</v>
+        <v>-5.8254</v>
       </c>
     </row>
     <row r="182">
@@ -10319,10 +10319,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3664</v>
+        <v>1.3893</v>
       </c>
       <c r="J182" t="n">
-        <v>34.16</v>
+        <v>34.7325</v>
       </c>
     </row>
     <row r="183">
@@ -10359,10 +10359,10 @@
         <v>1.58</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1769</v>
+        <v>1.1924</v>
       </c>
       <c r="J183" t="n">
-        <v>29.4225</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="184">
@@ -10399,10 +10399,10 @@
         <v>1.3</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7289</v>
+        <v>0.7096</v>
       </c>
       <c r="J184" t="n">
-        <v>18.2225</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="185">
@@ -10439,10 +10439,10 @@
         <v>1.29</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7089</v>
+        <v>0.6886</v>
       </c>
       <c r="J185" t="n">
-        <v>17.7225</v>
+        <v>17.215</v>
       </c>
     </row>
     <row r="186">
@@ -10479,10 +10479,10 @@
         <v>1.04</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1071</v>
+        <v>0.0819</v>
       </c>
       <c r="J186" t="n">
-        <v>2.6775</v>
+        <v>2.0475</v>
       </c>
     </row>
     <row r="187">
@@ -10519,10 +10519,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.235</v>
+        <v>-1.895</v>
       </c>
     </row>
     <row r="188">
@@ -10559,10 +10559,10 @@
         <v>0.8</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2329</v>
+        <v>-0.2162</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.8225</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="189">
@@ -10599,10 +10599,10 @@
         <v>0.8</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2329</v>
+        <v>-0.2162</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.8225</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="190">
@@ -10639,10 +10639,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2885</v>
+        <v>-0.2717</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.2125</v>
+        <v>-6.7925</v>
       </c>
     </row>
     <row r="191">
@@ -10679,10 +10679,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3888</v>
+        <v>-0.3765</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.4125</v>
       </c>
     </row>
     <row r="192">
@@ -10719,10 +10719,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0385</v>
+        <v>1.0155</v>
       </c>
       <c r="J192" t="n">
-        <v>31.155</v>
+        <v>30.465</v>
       </c>
     </row>
     <row r="193">
@@ -10759,10 +10759,10 @@
         <v>1.2</v>
       </c>
       <c r="I193" t="n">
-        <v>0.425</v>
+        <v>0.3678</v>
       </c>
       <c r="J193" t="n">
-        <v>12.75</v>
+        <v>11.034</v>
       </c>
     </row>
     <row r="194">
@@ -10799,10 +10799,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3205</v>
+        <v>0.2691</v>
       </c>
       <c r="J194" t="n">
-        <v>9.615</v>
+        <v>8.073</v>
       </c>
     </row>
     <row r="195">
@@ -10839,10 +10839,10 @@
         <v>0.73</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3233</v>
+        <v>-0.3071</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.699</v>
+        <v>-9.212999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10879,10 +10879,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5173</v>
+        <v>-0.522</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.519</v>
+        <v>-15.66</v>
       </c>
     </row>
     <row r="197">
@@ -10919,10 +10919,10 @@
         <v>1.54</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1881</v>
+        <v>1.2052</v>
       </c>
       <c r="J197" t="n">
-        <v>35.643</v>
+        <v>36.156</v>
       </c>
     </row>
     <row r="198">
@@ -10959,10 +10959,10 @@
         <v>1.12</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3753</v>
+        <v>0.336</v>
       </c>
       <c r="J198" t="n">
-        <v>11.259</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="199">
@@ -10999,10 +10999,10 @@
         <v>1.02</v>
       </c>
       <c r="I199" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0688</v>
       </c>
       <c r="J199" t="n">
-        <v>2.607</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="200">
@@ -11039,10 +11039,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3862</v>
+        <v>-0.3433</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.586</v>
+        <v>-10.299</v>
       </c>
     </row>
     <row r="201">
@@ -11079,10 +11079,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.412</v>
+        <v>-0.3691</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.36</v>
+        <v>-11.073</v>
       </c>
     </row>
     <row r="202">
@@ -11119,10 +11119,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0144</v>
+        <v>0.0237</v>
       </c>
       <c r="J202" t="n">
-        <v>0.3024</v>
+        <v>0.4977</v>
       </c>
     </row>
     <row r="203">
@@ -11159,10 +11159,10 @@
         <v>0.79</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2393</v>
+        <v>-0.2236</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.0253</v>
+        <v>-4.6956</v>
       </c>
     </row>
     <row r="204">
@@ -11199,10 +11199,10 @@
         <v>0.7</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3219</v>
+        <v>-0.3066</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.7599</v>
+        <v>-6.4386</v>
       </c>
     </row>
     <row r="205">
@@ -11239,10 +11239,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3309</v>
+        <v>-0.3159</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.9489</v>
+        <v>-6.6339</v>
       </c>
     </row>
     <row r="206">
@@ -11279,10 +11279,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4384</v>
+        <v>-0.4303</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.2064</v>
+        <v>-9.036300000000001</v>
       </c>
     </row>
     <row r="207">
@@ -11319,10 +11319,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2897</v>
+        <v>1.309</v>
       </c>
       <c r="J207" t="n">
-        <v>27.0837</v>
+        <v>27.489</v>
       </c>
     </row>
     <row r="208">
@@ -11359,10 +11359,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0715</v>
+        <v>1.0839</v>
       </c>
       <c r="J208" t="n">
-        <v>22.5015</v>
+        <v>22.7619</v>
       </c>
     </row>
     <row r="209">
@@ -11399,10 +11399,10 @@
         <v>1.45</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9998</v>
+        <v>1.0031</v>
       </c>
       <c r="J209" t="n">
-        <v>20.9958</v>
+        <v>21.0651</v>
       </c>
     </row>
     <row r="210">
@@ -11439,10 +11439,10 @@
         <v>1.44</v>
       </c>
       <c r="I210" t="n">
-        <v>0.984</v>
+        <v>0.9851</v>
       </c>
       <c r="J210" t="n">
-        <v>20.664</v>
+        <v>20.6871</v>
       </c>
     </row>
     <row r="211">
@@ -11479,10 +11479,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3288</v>
+        <v>-0.2944</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.9048</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="212">
@@ -11519,10 +11519,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0653</v>
+        <v>1.0746</v>
       </c>
       <c r="J212" t="n">
-        <v>31.959</v>
+        <v>32.238</v>
       </c>
     </row>
     <row r="213">
@@ -11559,10 +11559,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9135</v>
       </c>
       <c r="J213" t="n">
-        <v>27.837</v>
+        <v>27.405</v>
       </c>
     </row>
     <row r="214">
@@ -11599,10 +11599,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1261</v>
+        <v>0.1024</v>
       </c>
       <c r="J214" t="n">
-        <v>3.783</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="215">
@@ -11639,10 +11639,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4589</v>
+        <v>-0.4163</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.767</v>
+        <v>-12.489</v>
       </c>
     </row>
     <row r="216">
@@ -11679,10 +11679,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9281</v>
+        <v>-0.9176</v>
       </c>
       <c r="J216" t="n">
-        <v>-27.843</v>
+        <v>-27.528</v>
       </c>
     </row>
     <row r="217">
@@ -11719,10 +11719,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5354</v>
+        <v>0.4757</v>
       </c>
       <c r="J217" t="n">
-        <v>16.062</v>
+        <v>14.271</v>
       </c>
     </row>
     <row r="218">
@@ -11759,10 +11759,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2242</v>
+        <v>0.182</v>
       </c>
       <c r="J218" t="n">
-        <v>6.726</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="219">
@@ -11799,10 +11799,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1191</v>
+        <v>0.0914</v>
       </c>
       <c r="J219" t="n">
-        <v>3.573</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="220">
@@ -11839,10 +11839,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0625</v>
+        <v>-0.0489</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.875</v>
+        <v>-1.467</v>
       </c>
     </row>
     <row r="221">
@@ -11879,10 +11879,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1285</v>
+        <v>-0.1094</v>
       </c>
       <c r="J221" t="n">
-        <v>-3.855</v>
+        <v>-3.282</v>
       </c>
     </row>
     <row r="222">
@@ -11919,10 +11919,10 @@
         <v>1.6</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2023</v>
+        <v>1.2185</v>
       </c>
       <c r="J222" t="n">
-        <v>26.4506</v>
+        <v>26.807</v>
       </c>
     </row>
     <row r="223">
@@ -11959,10 +11959,10 @@
         <v>1.59</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1894</v>
+        <v>1.2053</v>
       </c>
       <c r="J223" t="n">
-        <v>26.1668</v>
+        <v>26.5166</v>
       </c>
     </row>
     <row r="224">
@@ -11999,10 +11999,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8067</v>
+        <v>0.7919</v>
       </c>
       <c r="J224" t="n">
-        <v>17.7474</v>
+        <v>17.4218</v>
       </c>
     </row>
     <row r="225">
@@ -12039,10 +12039,10 @@
         <v>1.29</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7087</v>
+        <v>0.6884</v>
       </c>
       <c r="J225" t="n">
-        <v>15.5914</v>
+        <v>15.1448</v>
       </c>
     </row>
     <row r="226">
@@ -12079,10 +12079,10 @@
         <v>1.13</v>
       </c>
       <c r="I226" t="n">
-        <v>0.356</v>
+        <v>0.3239</v>
       </c>
       <c r="J226" t="n">
-        <v>7.832</v>
+        <v>7.1258</v>
       </c>
     </row>
     <row r="227">
@@ -12119,10 +12119,10 @@
         <v>1.14</v>
       </c>
       <c r="I227" t="n">
-        <v>0.399</v>
+        <v>0.3536</v>
       </c>
       <c r="J227" t="n">
-        <v>8.778</v>
+        <v>7.7792</v>
       </c>
     </row>
     <row r="228">
@@ -12159,10 +12159,10 @@
         <v>0.78</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2515</v>
+        <v>-0.2347</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.533</v>
+        <v>-5.1634</v>
       </c>
     </row>
     <row r="229">
@@ -12199,10 +12199,10 @@
         <v>0.76</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2697</v>
+        <v>-0.2529</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.9334</v>
+        <v>-5.5638</v>
       </c>
     </row>
     <row r="230">
@@ -12239,10 +12239,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2789</v>
+        <v>-0.2621</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.1358</v>
+        <v>-5.7662</v>
       </c>
     </row>
     <row r="231">
@@ -12279,10 +12279,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5462</v>
+        <v>-0.5515</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.0164</v>
+        <v>-12.133</v>
       </c>
     </row>
     <row r="232">
@@ -12319,10 +12319,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2089</v>
+        <v>1.2241</v>
       </c>
       <c r="J232" t="n">
-        <v>27.8047</v>
+        <v>28.1543</v>
       </c>
     </row>
     <row r="233">
@@ -12359,10 +12359,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7408</v>
+        <v>0.7169</v>
       </c>
       <c r="J233" t="n">
-        <v>17.0384</v>
+        <v>16.4887</v>
       </c>
     </row>
     <row r="234">
@@ -12399,10 +12399,10 @@
         <v>1.24</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6212</v>
+        <v>0.5928</v>
       </c>
       <c r="J234" t="n">
-        <v>14.2876</v>
+        <v>13.6344</v>
       </c>
     </row>
     <row r="235">
@@ -12439,10 +12439,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4453</v>
+        <v>0.4132</v>
       </c>
       <c r="J235" t="n">
-        <v>10.2419</v>
+        <v>9.5036</v>
       </c>
     </row>
     <row r="236">
@@ -12479,10 +12479,10 @@
         <v>1.1</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2975</v>
+        <v>0.2659</v>
       </c>
       <c r="J236" t="n">
-        <v>6.8425</v>
+        <v>6.1157</v>
       </c>
     </row>
     <row r="237">
@@ -12519,10 +12519,10 @@
         <v>0.98</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0157</v>
+        <v>-0.0077</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.3611</v>
+        <v>-0.1771</v>
       </c>
     </row>
     <row r="238">
@@ -12559,10 +12559,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2225</v>
+        <v>-0.2061</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.1175</v>
+        <v>-4.7403</v>
       </c>
     </row>
     <row r="239">
@@ -12599,10 +12599,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.242</v>
+        <v>-0.2253</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.566</v>
+        <v>-5.1819</v>
       </c>
     </row>
     <row r="240">
@@ -12639,10 +12639,10 @@
         <v>0.72</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3063</v>
+        <v>-0.29</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.0449</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="241">
@@ -12679,10 +12679,10 @@
         <v>0.57</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4415</v>
+        <v>-0.4337</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.1545</v>
+        <v>-9.975099999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12719,10 +12719,10 @@
         <v>1.33</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8217</v>
+        <v>0.7977</v>
       </c>
       <c r="J242" t="n">
-        <v>24.651</v>
+        <v>23.931</v>
       </c>
     </row>
     <row r="243">
@@ -12759,10 +12759,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6989</v>
+        <v>0.6675</v>
       </c>
       <c r="J243" t="n">
-        <v>20.967</v>
+        <v>20.025</v>
       </c>
     </row>
     <row r="244">
@@ -12799,10 +12799,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3913</v>
+        <v>0.3554</v>
       </c>
       <c r="J244" t="n">
-        <v>11.739</v>
+        <v>10.662</v>
       </c>
     </row>
     <row r="245">
@@ -12839,10 +12839,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.29</v>
+        <v>0.2569</v>
       </c>
       <c r="J245" t="n">
-        <v>8.699999999999999</v>
+        <v>7.707</v>
       </c>
     </row>
     <row r="246">
@@ -12879,10 +12879,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.0866</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.598</v>
+        <v>-1.971</v>
       </c>
     </row>
     <row r="247">
@@ -12919,10 +12919,10 @@
         <v>0.99</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0158</v>
+        <v>-0.0112</v>
       </c>
       <c r="J247" t="n">
-        <v>-0.474</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="248">
@@ -12959,10 +12959,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0338</v>
+        <v>-0.0262</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.014</v>
+        <v>-0.786</v>
       </c>
     </row>
     <row r="249">
@@ -12999,10 +12999,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0496</v>
+        <v>-0.0399</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.488</v>
+        <v>-1.197</v>
       </c>
     </row>
     <row r="250">
@@ -13039,10 +13039,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2319</v>
+        <v>-0.2123</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.957</v>
+        <v>-6.369</v>
       </c>
     </row>
     <row r="251">
@@ -13079,10 +13079,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3462</v>
+        <v>-0.3307</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.386</v>
+        <v>-9.920999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -13119,10 +13119,10 @@
         <v>1.99</v>
       </c>
       <c r="I252" t="n">
-        <v>1.647</v>
+        <v>1.6899</v>
       </c>
       <c r="J252" t="n">
-        <v>29.646</v>
+        <v>30.4182</v>
       </c>
     </row>
     <row r="253">
@@ -13159,10 +13159,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1956</v>
+        <v>1.216</v>
       </c>
       <c r="J253" t="n">
-        <v>21.5208</v>
+        <v>21.888</v>
       </c>
     </row>
     <row r="254">
@@ -13199,10 +13199,10 @@
         <v>1.58</v>
       </c>
       <c r="I254" t="n">
-        <v>1.1588</v>
+        <v>1.1788</v>
       </c>
       <c r="J254" t="n">
-        <v>20.8584</v>
+        <v>21.2184</v>
       </c>
     </row>
     <row r="255">
@@ -13239,10 +13239,10 @@
         <v>1.46</v>
       </c>
       <c r="I255" t="n">
-        <v>1.0018</v>
+        <v>1.0121</v>
       </c>
       <c r="J255" t="n">
-        <v>18.0324</v>
+        <v>18.2178</v>
       </c>
     </row>
     <row r="256">
@@ -13279,10 +13279,10 @@
         <v>1.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3079</v>
+        <v>0.2731</v>
       </c>
       <c r="J256" t="n">
-        <v>5.5422</v>
+        <v>4.9158</v>
       </c>
     </row>
     <row r="257">
@@ -13319,10 +13319,10 @@
         <v>0.77</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2367</v>
+        <v>-0.2221</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.2606</v>
+        <v>-3.9978</v>
       </c>
     </row>
     <row r="258">
@@ -13359,10 +13359,10 @@
         <v>0.73</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2774</v>
+        <v>-0.2648</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.9932</v>
+        <v>-4.7664</v>
       </c>
     </row>
     <row r="259">
@@ -13399,10 +13399,10 @@
         <v>0.64</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3619</v>
+        <v>-0.3524</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.5142</v>
+        <v>-6.3432</v>
       </c>
     </row>
     <row r="260">
@@ -13439,10 +13439,10 @@
         <v>0.51</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.474</v>
+        <v>-0.4696</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.532</v>
+        <v>-8.4528</v>
       </c>
     </row>
     <row r="261">
@@ -13479,10 +13479,10 @@
         <v>0.44</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5356</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.6408</v>
+        <v>-9.680400000000001</v>
       </c>
     </row>
     <row r="262">
@@ -13519,10 +13519,10 @@
         <v>1.43</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9949</v>
+        <v>0.9915</v>
       </c>
       <c r="J262" t="n">
-        <v>25.8674</v>
+        <v>25.779</v>
       </c>
     </row>
     <row r="263">
@@ -13559,10 +13559,10 @@
         <v>1.36</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8665</v>
+        <v>0.8476</v>
       </c>
       <c r="J263" t="n">
-        <v>22.529</v>
+        <v>22.0376</v>
       </c>
     </row>
     <row r="264">
@@ -13599,10 +13599,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8469</v>
+        <v>0.8267</v>
       </c>
       <c r="J264" t="n">
-        <v>22.0194</v>
+        <v>21.4942</v>
       </c>
     </row>
     <row r="265">
@@ -13639,10 +13639,10 @@
         <v>1.24</v>
       </c>
       <c r="I265" t="n">
-        <v>0.626</v>
+        <v>0.5952</v>
       </c>
       <c r="J265" t="n">
-        <v>16.276</v>
+        <v>15.4752</v>
       </c>
     </row>
     <row r="266">
@@ -13679,10 +13679,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7199</v>
+        <v>-0.6934</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.7174</v>
+        <v>-18.0284</v>
       </c>
     </row>
     <row r="267">
@@ -13719,10 +13719,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6835</v>
+        <v>0.6277</v>
       </c>
       <c r="J267" t="n">
-        <v>17.771</v>
+        <v>16.3202</v>
       </c>
     </row>
     <row r="268">
@@ -13759,10 +13759,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.152</v>
+        <v>0.1168</v>
       </c>
       <c r="J268" t="n">
-        <v>3.952</v>
+        <v>3.0368</v>
       </c>
     </row>
     <row r="269">
@@ -13799,10 +13799,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0842</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.1892</v>
+        <v>-1.7966</v>
       </c>
     </row>
     <row r="270">
@@ -13839,10 +13839,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.097</v>
+        <v>-0.0808</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.522</v>
+        <v>-2.1008</v>
       </c>
     </row>
     <row r="271">
@@ -13879,10 +13879,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4525</v>
+        <v>-0.4477</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.765</v>
+        <v>-11.6402</v>
       </c>
     </row>
     <row r="272">
@@ -13919,10 +13919,10 @@
         <v>1.99</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6506</v>
+        <v>1.6938</v>
       </c>
       <c r="J272" t="n">
-        <v>33.012</v>
+        <v>33.876</v>
       </c>
     </row>
     <row r="273">
@@ -13959,10 +13959,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3075</v>
+        <v>1.3301</v>
       </c>
       <c r="J273" t="n">
-        <v>26.15</v>
+        <v>26.602</v>
       </c>
     </row>
     <row r="274">
@@ -13999,10 +13999,10 @@
         <v>1.6</v>
       </c>
       <c r="I274" t="n">
-        <v>1.185</v>
+        <v>1.2047</v>
       </c>
       <c r="J274" t="n">
-        <v>23.7</v>
+        <v>24.094</v>
       </c>
     </row>
     <row r="275">
@@ -14039,10 +14039,10 @@
         <v>1.41</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9202</v>
+        <v>0.9193</v>
       </c>
       <c r="J275" t="n">
-        <v>18.404</v>
+        <v>18.386</v>
       </c>
     </row>
     <row r="276">
@@ -14079,10 +14079,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2556</v>
+        <v>-0.2296</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.112</v>
+        <v>-4.592</v>
       </c>
     </row>
     <row r="277">
@@ -14119,10 +14119,10 @@
         <v>0.82</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1801</v>
+        <v>-0.1621</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.602</v>
+        <v>-3.242</v>
       </c>
     </row>
     <row r="278">
@@ -14159,10 +14159,10 @@
         <v>0.75</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2549</v>
+        <v>-0.2412</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.098</v>
+        <v>-4.824</v>
       </c>
     </row>
     <row r="279">
@@ -14199,10 +14199,10 @@
         <v>0.67</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3332</v>
+        <v>-0.3232</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.664</v>
+        <v>-6.464</v>
       </c>
     </row>
     <row r="280">
@@ -14239,10 +14239,10 @@
         <v>0.4</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5694</v>
+        <v>-0.5762</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.388</v>
+        <v>-11.524</v>
       </c>
     </row>
     <row r="281">
@@ -14279,10 +14279,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5694</v>
+        <v>-0.5762</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.388</v>
+        <v>-11.524</v>
       </c>
     </row>
     <row r="282">
@@ -14319,10 +14319,10 @@
         <v>0.78</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.2209</v>
+        <v>-0.205</v>
       </c>
       <c r="J282" t="n">
-        <v>-4.418</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="283">
@@ -14359,10 +14359,10 @@
         <v>0.66</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.3408</v>
+        <v>-0.3314</v>
       </c>
       <c r="J283" t="n">
-        <v>-6.816</v>
+        <v>-6.628</v>
       </c>
     </row>
     <row r="284">
@@ -14399,10 +14399,10 @@
         <v>0.65</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.35</v>
+        <v>-0.341</v>
       </c>
       <c r="J284" t="n">
-        <v>-7</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="285">
@@ -14439,10 +14439,10 @@
         <v>0.53</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4535</v>
+        <v>-0.4479</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.07</v>
+        <v>-8.958</v>
       </c>
     </row>
     <row r="286">
@@ -14479,10 +14479,10 @@
         <v>0.37</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5945</v>
+        <v>-0.6049</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.89</v>
+        <v>-12.098</v>
       </c>
     </row>
     <row r="287">
@@ -14519,10 +14519,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2584</v>
+        <v>1.2772</v>
       </c>
       <c r="J287" t="n">
-        <v>25.168</v>
+        <v>25.544</v>
       </c>
     </row>
     <row r="288">
@@ -14559,10 +14559,10 @@
         <v>1.47</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0257</v>
+        <v>1.0345</v>
       </c>
       <c r="J288" t="n">
-        <v>20.514</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="289">
@@ -14599,10 +14599,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0111</v>
+        <v>1.0179</v>
       </c>
       <c r="J289" t="n">
-        <v>20.222</v>
+        <v>20.358</v>
       </c>
     </row>
     <row r="290">
@@ -14639,10 +14639,10 @@
         <v>1.32</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7617</v>
+        <v>0.746</v>
       </c>
       <c r="J290" t="n">
-        <v>15.234</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="291">
@@ -14679,10 +14679,10 @@
         <v>1.29</v>
       </c>
       <c r="I291" t="n">
-        <v>0.702</v>
+        <v>0.6827</v>
       </c>
       <c r="J291" t="n">
-        <v>14.04</v>
+        <v>13.654</v>
       </c>
     </row>
     <row r="292">
@@ -14719,10 +14719,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6415</v>
+        <v>0.5831</v>
       </c>
       <c r="J292" t="n">
-        <v>19.245</v>
+        <v>17.493</v>
       </c>
     </row>
     <row r="293">
@@ -14759,10 +14759,10 @@
         <v>1.19</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4143</v>
+        <v>0.3574</v>
       </c>
       <c r="J293" t="n">
-        <v>12.429</v>
+        <v>10.722</v>
       </c>
     </row>
     <row r="294">
@@ -14799,10 +14799,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0258</v>
+        <v>-0.0184</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.774</v>
+        <v>-0.552</v>
       </c>
     </row>
     <row r="295">
@@ -14839,10 +14839,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1478</v>
+        <v>-0.1281</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.434</v>
+        <v>-3.843</v>
       </c>
     </row>
     <row r="296">
@@ -14879,10 +14879,10 @@
         <v>0.64</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4028</v>
+        <v>-0.3929</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.084</v>
+        <v>-11.787</v>
       </c>
     </row>
     <row r="297">
@@ -14919,10 +14919,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2324</v>
+        <v>1.2487</v>
       </c>
       <c r="J297" t="n">
-        <v>36.972</v>
+        <v>37.461</v>
       </c>
     </row>
     <row r="298">
@@ -14959,10 +14959,10 @@
         <v>1.25</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6463</v>
+        <v>0.6161</v>
       </c>
       <c r="J298" t="n">
-        <v>19.389</v>
+        <v>18.483</v>
       </c>
     </row>
     <row r="299">
@@ -14999,10 +14999,10 @@
         <v>1.19</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5204</v>
+        <v>0.4874</v>
       </c>
       <c r="J299" t="n">
-        <v>15.612</v>
+        <v>14.622</v>
       </c>
     </row>
     <row r="300">
@@ -15039,10 +15039,10 @@
         <v>1.11</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3312</v>
+        <v>0.2985</v>
       </c>
       <c r="J300" t="n">
-        <v>9.936</v>
+        <v>8.955</v>
       </c>
     </row>
     <row r="301">
@@ -15079,10 +15079,10 @@
         <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.0388</v>
+        <v>-0.0334</v>
       </c>
       <c r="J301" t="n">
-        <v>-1.164</v>
+        <v>-1.002</v>
       </c>
     </row>
     <row r="302">
@@ -15119,10 +15119,10 @@
         <v>1.52</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1118</v>
+        <v>1.1244</v>
       </c>
       <c r="J302" t="n">
-        <v>27.795</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="303">
@@ -15159,10 +15159,10 @@
         <v>1.34</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8153</v>
+        <v>0.7966</v>
       </c>
       <c r="J303" t="n">
-        <v>20.3825</v>
+        <v>19.915</v>
       </c>
     </row>
     <row r="304">
@@ -15199,10 +15199,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7388</v>
+        <v>0.716</v>
       </c>
       <c r="J304" t="n">
-        <v>18.47</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="305">
@@ -15239,10 +15239,10 @@
         <v>1.21</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5541</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J305" t="n">
-        <v>13.8525</v>
+        <v>13.1175</v>
       </c>
     </row>
     <row r="306">
@@ -15279,10 +15279,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3941</v>
+        <v>0.362</v>
       </c>
       <c r="J306" t="n">
-        <v>9.852499999999999</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="307">
@@ -15319,10 +15319,10 @@
         <v>1.35</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7284</v>
+        <v>0.6835</v>
       </c>
       <c r="J307" t="n">
-        <v>18.21</v>
+        <v>17.0875</v>
       </c>
     </row>
     <row r="308">
@@ -15359,10 +15359,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2293</v>
+        <v>-0.2102</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.7325</v>
+        <v>-5.255</v>
       </c>
     </row>
     <row r="309">
@@ -15399,10 +15399,10 @@
         <v>0.78</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2586</v>
+        <v>-0.2396</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.465</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="310">
@@ -15439,10 +15439,10 @@
         <v>0.73</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3062</v>
+        <v>-0.2886</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.655</v>
+        <v>-7.215</v>
       </c>
     </row>
     <row r="311">
@@ -15479,10 +15479,10 @@
         <v>0.63</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3977</v>
+        <v>-0.3861</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.942500000000001</v>
+        <v>-9.6525</v>
       </c>
     </row>
     <row r="312">
@@ -15519,10 +15519,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5209</v>
+        <v>0.4697</v>
       </c>
       <c r="J312" t="n">
-        <v>13.5434</v>
+        <v>12.2122</v>
       </c>
     </row>
     <row r="313">
@@ -15559,10 +15559,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1068</v>
+        <v>0.081</v>
       </c>
       <c r="J313" t="n">
-        <v>2.7768</v>
+        <v>2.106</v>
       </c>
     </row>
     <row r="314">
@@ -15599,10 +15599,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2272</v>
+        <v>-0.2087</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.9072</v>
+        <v>-5.4262</v>
       </c>
     </row>
     <row r="315">
@@ -15639,10 +15639,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3951</v>
+        <v>-0.3832</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.2726</v>
+        <v>-9.963200000000001</v>
       </c>
     </row>
     <row r="316">
@@ -15679,10 +15679,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5092</v>
+        <v>-0.51</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.2392</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="317">
@@ -15719,10 +15719,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.318</v>
+        <v>1.3386</v>
       </c>
       <c r="J317" t="n">
-        <v>34.268</v>
+        <v>34.8036</v>
       </c>
     </row>
     <row r="318">
@@ -15759,10 +15759,10 @@
         <v>1.49</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0794</v>
+        <v>1.0891</v>
       </c>
       <c r="J318" t="n">
-        <v>28.0644</v>
+        <v>28.3166</v>
       </c>
     </row>
     <row r="319">
@@ -15799,10 +15799,10 @@
         <v>1.32</v>
       </c>
       <c r="I319" t="n">
-        <v>0.7831</v>
+        <v>0.7601</v>
       </c>
       <c r="J319" t="n">
-        <v>20.3606</v>
+        <v>19.7626</v>
       </c>
     </row>
     <row r="320">
@@ -15839,10 +15839,10 @@
         <v>1.05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.16</v>
+        <v>0.1341</v>
       </c>
       <c r="J320" t="n">
-        <v>4.16</v>
+        <v>3.4866</v>
       </c>
     </row>
     <row r="321">
@@ -15879,10 +15879,10 @@
         <v>0.75</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7462</v>
+        <v>-0.7226</v>
       </c>
       <c r="J321" t="n">
-        <v>-19.4012</v>
+        <v>-18.7876</v>
       </c>
     </row>
     <row r="322">
@@ -15919,10 +15919,10 @@
         <v>0.9</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.06</v>
+        <v>-0.0279</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.14</v>
+        <v>-0.5301</v>
       </c>
     </row>
     <row r="323">
@@ -15959,10 +15959,10 @@
         <v>0.64</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.349</v>
+        <v>-0.3411</v>
       </c>
       <c r="J323" t="n">
-        <v>-6.631</v>
+        <v>-6.4809</v>
       </c>
     </row>
     <row r="324">
@@ -15999,10 +15999,10 @@
         <v>0.5</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.4718</v>
+        <v>-0.4688</v>
       </c>
       <c r="J324" t="n">
-        <v>-8.9642</v>
+        <v>-8.9072</v>
       </c>
     </row>
     <row r="325">
@@ -16039,10 +16039,10 @@
         <v>0.5</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4718</v>
+        <v>-0.4688</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.9642</v>
+        <v>-8.9072</v>
       </c>
     </row>
     <row r="326">
@@ -16079,10 +16079,10 @@
         <v>0.19</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7887</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.2215</v>
+        <v>-14.9853</v>
       </c>
     </row>
     <row r="327">
@@ -16119,10 +16119,10 @@
         <v>2.38</v>
       </c>
       <c r="I327" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J327" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="328">
@@ -16159,10 +16159,10 @@
         <v>2.03</v>
       </c>
       <c r="I328" t="n">
-        <v>1.6811</v>
+        <v>1.7272</v>
       </c>
       <c r="J328" t="n">
-        <v>31.9409</v>
+        <v>32.8168</v>
       </c>
     </row>
     <row r="329">
@@ -16199,10 +16199,10 @@
         <v>1.56</v>
       </c>
       <c r="I329" t="n">
-        <v>1.1302</v>
+        <v>1.1522</v>
       </c>
       <c r="J329" t="n">
-        <v>21.4738</v>
+        <v>21.8918</v>
       </c>
     </row>
     <row r="330">
@@ -16239,10 +16239,10 @@
         <v>1.13</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3238</v>
+        <v>0.2879</v>
       </c>
       <c r="J330" t="n">
-        <v>6.1522</v>
+        <v>5.4701</v>
       </c>
     </row>
     <row r="331">
@@ -16279,10 +16279,10 @@
         <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.0953</v>
+        <v>-0.0992</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.8107</v>
+        <v>-1.8848</v>
       </c>
     </row>
     <row r="332">
@@ -16319,10 +16319,10 @@
         <v>1.36</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8711</v>
+        <v>0.8519</v>
       </c>
       <c r="J332" t="n">
-        <v>26.133</v>
+        <v>25.557</v>
       </c>
     </row>
     <row r="333">
@@ -16359,10 +16359,10 @@
         <v>1.33</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8119</v>
+        <v>0.7885</v>
       </c>
       <c r="J333" t="n">
-        <v>24.357</v>
+        <v>23.655</v>
       </c>
     </row>
     <row r="334">
@@ -16399,10 +16399,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6078</v>
+        <v>0.5752</v>
       </c>
       <c r="J334" t="n">
-        <v>18.234</v>
+        <v>17.256</v>
       </c>
     </row>
     <row r="335">
@@ -16439,10 +16439,10 @@
         <v>1.11</v>
       </c>
       <c r="I335" t="n">
-        <v>0.335</v>
+        <v>0.3018</v>
       </c>
       <c r="J335" t="n">
-        <v>10.05</v>
+        <v>9.054</v>
       </c>
     </row>
     <row r="336">
@@ -16479,10 +16479,10 @@
         <v>1</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0346</v>
+        <v>-0.0291</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.038</v>
+        <v>-0.873</v>
       </c>
     </row>
     <row r="337">
@@ -16519,10 +16519,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0434</v>
+        <v>-0.0342</v>
       </c>
       <c r="J337" t="n">
-        <v>-1.302</v>
+        <v>-1.026</v>
       </c>
     </row>
     <row r="338">
@@ -16559,10 +16559,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0856</v>
+        <v>-0.0726</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.568</v>
+        <v>-2.178</v>
       </c>
     </row>
     <row r="339">
@@ -16599,10 +16599,10 @@
         <v>0.88</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1568</v>
+        <v>-0.14</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.704</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="340">
@@ -16639,10 +16639,10 @@
         <v>0.79</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.247</v>
+        <v>-0.2283</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.41</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="341">
@@ -16679,10 +16679,10 @@
         <v>0.62</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4045</v>
+        <v>-0.3934</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.135</v>
+        <v>-11.802</v>
       </c>
     </row>
     <row r="342">
@@ -16719,10 +16719,10 @@
         <v>1.81</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5388</v>
+        <v>1.5833</v>
       </c>
       <c r="J342" t="n">
-        <v>43.0864</v>
+        <v>44.3324</v>
       </c>
     </row>
     <row r="343">
@@ -16759,10 +16759,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3952</v>
+        <v>0.3574</v>
       </c>
       <c r="J343" t="n">
-        <v>11.0656</v>
+        <v>10.0072</v>
       </c>
     </row>
     <row r="344">
@@ -16799,10 +16799,10 @@
         <v>1</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.02</v>
+        <v>-0.0149</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.4172</v>
       </c>
     </row>
     <row r="345">
@@ -16839,10 +16839,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3393</v>
+        <v>-0.2974</v>
       </c>
       <c r="J345" t="n">
-        <v>-9.500400000000001</v>
+        <v>-8.327199999999999</v>
       </c>
     </row>
     <row r="346">
@@ -16879,10 +16879,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6801</v>
+        <v>-0.6479</v>
       </c>
       <c r="J346" t="n">
-        <v>-19.0428</v>
+        <v>-18.1412</v>
       </c>
     </row>
     <row r="347">
@@ -16919,10 +16919,10 @@
         <v>1.18</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4011</v>
+        <v>0.3447</v>
       </c>
       <c r="J347" t="n">
-        <v>11.2308</v>
+        <v>9.6516</v>
       </c>
     </row>
     <row r="348">
@@ -16959,10 +16959,10 @@
         <v>1.14</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J348" t="n">
-        <v>9.2316</v>
+        <v>7.756</v>
       </c>
     </row>
     <row r="349">
@@ -16999,10 +16999,10 @@
         <v>1.07</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1929</v>
+        <v>0.1527</v>
       </c>
       <c r="J349" t="n">
-        <v>5.4012</v>
+        <v>4.2756</v>
       </c>
     </row>
     <row r="350">
@@ -17039,10 +17039,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2112</v>
+        <v>-0.1906</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.9136</v>
+        <v>-5.3368</v>
       </c>
     </row>
     <row r="351">
@@ -17079,10 +17079,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3191</v>
+        <v>-0.3023</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.934799999999999</v>
+        <v>-8.464399999999999</v>
       </c>
     </row>
     <row r="352">
@@ -17119,10 +17119,10 @@
         <v>1.34</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7438</v>
+        <v>0.7085</v>
       </c>
       <c r="J352" t="n">
-        <v>15.6198</v>
+        <v>14.8785</v>
       </c>
     </row>
     <row r="353">
@@ -17159,10 +17159,10 @@
         <v>0.77</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.2622</v>
+        <v>-0.2447</v>
       </c>
       <c r="J353" t="n">
-        <v>-5.5062</v>
+        <v>-5.1387</v>
       </c>
     </row>
     <row r="354">
@@ -17199,10 +17199,10 @@
         <v>0.77</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.2622</v>
+        <v>-0.2447</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.5062</v>
+        <v>-5.1387</v>
       </c>
     </row>
     <row r="355">
@@ -17239,10 +17239,10 @@
         <v>0.66</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3638</v>
+        <v>-0.3497</v>
       </c>
       <c r="J355" t="n">
-        <v>-7.6398</v>
+        <v>-7.3437</v>
       </c>
     </row>
     <row r="356">
@@ -17279,10 +17279,10 @@
         <v>0.45</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5484</v>
+        <v>-0.5543</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.5164</v>
+        <v>-11.6403</v>
       </c>
     </row>
     <row r="357">
@@ -17319,10 +17319,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3617</v>
+        <v>1.3845</v>
       </c>
       <c r="J357" t="n">
-        <v>28.5957</v>
+        <v>29.0745</v>
       </c>
     </row>
     <row r="358">
@@ -17359,10 +17359,10 @@
         <v>1.42</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9497</v>
+        <v>0.9472</v>
       </c>
       <c r="J358" t="n">
-        <v>19.9437</v>
+        <v>19.8912</v>
       </c>
     </row>
     <row r="359">
@@ -17399,10 +17399,10 @@
         <v>1.34</v>
       </c>
       <c r="I359" t="n">
-        <v>0.8037</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>16.8777</v>
+        <v>16.5858</v>
       </c>
     </row>
     <row r="360">
@@ -17439,10 +17439,10 @@
         <v>1.3</v>
       </c>
       <c r="I360" t="n">
-        <v>0.7254</v>
+        <v>0.7068</v>
       </c>
       <c r="J360" t="n">
-        <v>15.2334</v>
+        <v>14.8428</v>
       </c>
     </row>
     <row r="361">
@@ -17479,10 +17479,10 @@
         <v>1.28</v>
       </c>
       <c r="I361" t="n">
-        <v>0.6851</v>
+        <v>0.6643</v>
       </c>
       <c r="J361" t="n">
-        <v>14.3871</v>
+        <v>13.9503</v>
       </c>
     </row>
     <row r="362">
@@ -17519,10 +17519,10 @@
         <v>2.1</v>
       </c>
       <c r="I362" t="n">
-        <v>1.7559</v>
+        <v>1.8086</v>
       </c>
       <c r="J362" t="n">
-        <v>31.6062</v>
+        <v>32.5548</v>
       </c>
     </row>
     <row r="363">
@@ -17559,10 +17559,10 @@
         <v>1.98</v>
       </c>
       <c r="I363" t="n">
-        <v>1.6208</v>
+        <v>1.6625</v>
       </c>
       <c r="J363" t="n">
-        <v>29.1744</v>
+        <v>29.925</v>
       </c>
     </row>
     <row r="364">
@@ -17599,10 +17599,10 @@
         <v>1.49</v>
       </c>
       <c r="I364" t="n">
-        <v>1.037</v>
+        <v>1.0543</v>
       </c>
       <c r="J364" t="n">
-        <v>18.666</v>
+        <v>18.9774</v>
       </c>
     </row>
     <row r="365">
@@ -17639,10 +17639,10 @@
         <v>1.44</v>
       </c>
       <c r="I365" t="n">
-        <v>0.9593</v>
+        <v>0.9661</v>
       </c>
       <c r="J365" t="n">
-        <v>17.2674</v>
+        <v>17.3898</v>
       </c>
     </row>
     <row r="366">
@@ -17679,10 +17679,10 @@
         <v>1.21</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5058</v>
+        <v>0.4759</v>
       </c>
       <c r="J366" t="n">
-        <v>9.1044</v>
+        <v>8.5662</v>
       </c>
     </row>
     <row r="367">
@@ -17719,10 +17719,10 @@
         <v>0.74</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.2365</v>
+        <v>-0.2177</v>
       </c>
       <c r="J367" t="n">
-        <v>-4.257</v>
+        <v>-3.9186</v>
       </c>
     </row>
     <row r="368">
@@ -17759,10 +17759,10 @@
         <v>0.63</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.3505</v>
+        <v>-0.3429</v>
       </c>
       <c r="J368" t="n">
-        <v>-6.309</v>
+        <v>-6.1722</v>
       </c>
     </row>
     <row r="369">
@@ -17799,10 +17799,10 @@
         <v>0.5</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.4671</v>
+        <v>-0.4654</v>
       </c>
       <c r="J369" t="n">
-        <v>-8.4078</v>
+        <v>-8.3772</v>
       </c>
     </row>
     <row r="370">
@@ -17839,10 +17839,10 @@
         <v>0.39</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.5634</v>
+        <v>-0.569</v>
       </c>
       <c r="J370" t="n">
-        <v>-10.1412</v>
+        <v>-10.242</v>
       </c>
     </row>
     <row r="371">
@@ -17879,10 +17879,10 @@
         <v>0.31</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6357</v>
+        <v>-0.6518</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.4426</v>
+        <v>-11.7324</v>
       </c>
     </row>
   </sheetData>
